--- a/00_スケジュール/AWS改修スケジュール.xlsx
+++ b/00_スケジュール/AWS改修スケジュール.xlsx
@@ -386,7 +386,7 @@
       <sz val="9"/>
     </font>
   </fonts>
-  <fills count="34">
+  <fills count="38">
     <fill>
       <patternFill/>
     </fill>
@@ -568,8 +568,28 @@
         <fgColor rgb="00FFE0A0"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001E8449"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D5F5E3"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EAFAF1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="0082E0AA"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="9">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -666,6 +686,10 @@
         <color rgb="00CCCCCC"/>
       </bottom>
     </border>
+    <border>
+      <right/>
+      <bottom/>
+    </border>
   </borders>
   <cellStyleXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
@@ -677,7 +701,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="164">
+  <cellXfs count="182">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -1134,6 +1158,60 @@
     <xf numFmtId="0" fontId="25" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
     </xf>
+    <xf numFmtId="49" fontId="49" fillId="22" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="50" fillId="23" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="49" fillId="25" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="50" fillId="26" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="49" fillId="28" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="50" fillId="29" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="49" fillId="31" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="50" fillId="32" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="49" fillId="34" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="50" fillId="35" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="51" fillId="36" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="36" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="51" fillId="36" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="36" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="36" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="37" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="36" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1629,33 +1707,11 @@
       <c r="AF3" s="84" t="n"/>
     </row>
     <row r="4" ht="20" customHeight="1" s="80">
-      <c r="A4" s="98" t="inlineStr">
+      <c r="A4" s="164" t="inlineStr">
         <is>
           <t>リポジトリ統合作業（モノレポ POS-SERVER）</t>
         </is>
       </c>
-      <c r="B4" s="99" t="n"/>
-      <c r="C4" s="99" t="n"/>
-      <c r="D4" s="99" t="n"/>
-      <c r="E4" s="99" t="n"/>
-      <c r="F4" s="99" t="n"/>
-      <c r="G4" s="99" t="n"/>
-      <c r="H4" s="99" t="n"/>
-      <c r="I4" s="99" t="n"/>
-      <c r="J4" s="99" t="n"/>
-      <c r="K4" s="99" t="n"/>
-      <c r="L4" s="99" t="n"/>
-      <c r="M4" s="99" t="n"/>
-      <c r="N4" s="99" t="n"/>
-      <c r="O4" s="99" t="n"/>
-      <c r="P4" s="99" t="n"/>
-      <c r="Q4" s="99" t="n"/>
-      <c r="R4" s="99" t="n"/>
-      <c r="S4" s="99" t="n"/>
-      <c r="T4" s="99" t="n"/>
-      <c r="U4" s="99" t="n"/>
-      <c r="V4" s="99" t="n"/>
-      <c r="W4" s="99" t="n"/>
       <c r="X4" s="84" t="n"/>
       <c r="Y4" s="84" t="n"/>
       <c r="Z4" s="84" t="n"/>
@@ -1667,33 +1723,11 @@
       <c r="AF4" s="84" t="n"/>
     </row>
     <row r="5" ht="20" customHeight="1" s="80">
-      <c r="A5" s="100" t="inlineStr">
+      <c r="A5" s="165" t="inlineStr">
         <is>
           <t>▶ Phase 1: 事前準備・モノレポ基盤構築（Day 1-2）</t>
         </is>
       </c>
-      <c r="B5" s="101" t="n"/>
-      <c r="C5" s="101" t="n"/>
-      <c r="D5" s="101" t="n"/>
-      <c r="E5" s="101" t="n"/>
-      <c r="F5" s="101" t="n"/>
-      <c r="G5" s="101" t="n"/>
-      <c r="H5" s="101" t="n"/>
-      <c r="I5" s="101" t="n"/>
-      <c r="J5" s="101" t="n"/>
-      <c r="K5" s="101" t="n"/>
-      <c r="L5" s="101" t="n"/>
-      <c r="M5" s="101" t="n"/>
-      <c r="N5" s="101" t="n"/>
-      <c r="O5" s="101" t="n"/>
-      <c r="P5" s="101" t="n"/>
-      <c r="Q5" s="101" t="n"/>
-      <c r="R5" s="101" t="n"/>
-      <c r="S5" s="101" t="n"/>
-      <c r="T5" s="101" t="n"/>
-      <c r="U5" s="101" t="n"/>
-      <c r="V5" s="101" t="n"/>
-      <c r="W5" s="101" t="n"/>
       <c r="X5" s="84" t="n"/>
       <c r="Y5" s="84" t="n"/>
       <c r="Z5" s="84" t="n"/>
@@ -2003,33 +2037,11 @@
       <c r="AF10" s="84" t="n"/>
     </row>
     <row r="11" ht="20" customHeight="1" s="80">
-      <c r="A11" s="100" t="inlineStr">
+      <c r="A11" s="165" t="inlineStr">
         <is>
           <t>▶ Phase 2: Docker/CI/CD・テスト・アーカイブ（Day 5-7）</t>
         </is>
       </c>
-      <c r="B11" s="101" t="n"/>
-      <c r="C11" s="101" t="n"/>
-      <c r="D11" s="101" t="n"/>
-      <c r="E11" s="101" t="n"/>
-      <c r="F11" s="101" t="n"/>
-      <c r="G11" s="101" t="n"/>
-      <c r="H11" s="101" t="n"/>
-      <c r="I11" s="101" t="n"/>
-      <c r="J11" s="101" t="n"/>
-      <c r="K11" s="101" t="n"/>
-      <c r="L11" s="101" t="n"/>
-      <c r="M11" s="101" t="n"/>
-      <c r="N11" s="101" t="n"/>
-      <c r="O11" s="101" t="n"/>
-      <c r="P11" s="101" t="n"/>
-      <c r="Q11" s="101" t="n"/>
-      <c r="R11" s="101" t="n"/>
-      <c r="S11" s="101" t="n"/>
-      <c r="T11" s="101" t="n"/>
-      <c r="U11" s="101" t="n"/>
-      <c r="V11" s="101" t="n"/>
-      <c r="W11" s="101" t="n"/>
       <c r="X11" s="84" t="n"/>
       <c r="Y11" s="84" t="n"/>
       <c r="Z11" s="84" t="n"/>
@@ -2269,33 +2281,11 @@
       <c r="AF15" s="84" t="n"/>
     </row>
     <row r="16" ht="20" customHeight="1" s="80">
-      <c r="A16" s="110" t="inlineStr">
+      <c r="A16" s="166" t="inlineStr">
         <is>
           <t>コード修正（動作テスト・問題点レポート KASUMI-POS-TEST-2026-001）</t>
         </is>
       </c>
-      <c r="B16" s="111" t="n"/>
-      <c r="C16" s="111" t="n"/>
-      <c r="D16" s="111" t="n"/>
-      <c r="E16" s="111" t="n"/>
-      <c r="F16" s="111" t="n"/>
-      <c r="G16" s="111" t="n"/>
-      <c r="H16" s="111" t="n"/>
-      <c r="I16" s="111" t="n"/>
-      <c r="J16" s="111" t="n"/>
-      <c r="K16" s="111" t="n"/>
-      <c r="L16" s="111" t="n"/>
-      <c r="M16" s="111" t="n"/>
-      <c r="N16" s="111" t="n"/>
-      <c r="O16" s="111" t="n"/>
-      <c r="P16" s="111" t="n"/>
-      <c r="Q16" s="111" t="n"/>
-      <c r="R16" s="111" t="n"/>
-      <c r="S16" s="111" t="n"/>
-      <c r="T16" s="111" t="n"/>
-      <c r="U16" s="111" t="n"/>
-      <c r="V16" s="111" t="n"/>
-      <c r="W16" s="111" t="n"/>
       <c r="X16" s="84" t="n"/>
       <c r="Y16" s="84" t="n"/>
       <c r="Z16" s="84" t="n"/>
@@ -2307,33 +2297,11 @@
       <c r="AF16" s="84" t="n"/>
     </row>
     <row r="17" ht="20" customHeight="1" s="80">
-      <c r="A17" s="112" t="inlineStr">
+      <c r="A17" s="167" t="inlineStr">
         <is>
           <t>▶ Phase 1: 致命的（即日対応）</t>
         </is>
       </c>
-      <c r="B17" s="113" t="n"/>
-      <c r="C17" s="113" t="n"/>
-      <c r="D17" s="113" t="n"/>
-      <c r="E17" s="113" t="n"/>
-      <c r="F17" s="113" t="n"/>
-      <c r="G17" s="113" t="n"/>
-      <c r="H17" s="113" t="n"/>
-      <c r="I17" s="113" t="n"/>
-      <c r="J17" s="113" t="n"/>
-      <c r="K17" s="113" t="n"/>
-      <c r="L17" s="113" t="n"/>
-      <c r="M17" s="113" t="n"/>
-      <c r="N17" s="113" t="n"/>
-      <c r="O17" s="113" t="n"/>
-      <c r="P17" s="113" t="n"/>
-      <c r="Q17" s="113" t="n"/>
-      <c r="R17" s="113" t="n"/>
-      <c r="S17" s="113" t="n"/>
-      <c r="T17" s="113" t="n"/>
-      <c r="U17" s="113" t="n"/>
-      <c r="V17" s="113" t="n"/>
-      <c r="W17" s="113" t="n"/>
       <c r="X17" s="84" t="n"/>
       <c r="Y17" s="84" t="n"/>
       <c r="Z17" s="84" t="n"/>
@@ -2461,33 +2429,11 @@
       <c r="AF19" s="84" t="n"/>
     </row>
     <row r="20" ht="20" customHeight="1" s="80">
-      <c r="A20" s="112" t="inlineStr">
+      <c r="A20" s="167" t="inlineStr">
         <is>
           <t>▶ Phase 2: 高優先度（1〜2週間以内）</t>
         </is>
       </c>
-      <c r="B20" s="113" t="n"/>
-      <c r="C20" s="113" t="n"/>
-      <c r="D20" s="113" t="n"/>
-      <c r="E20" s="113" t="n"/>
-      <c r="F20" s="113" t="n"/>
-      <c r="G20" s="113" t="n"/>
-      <c r="H20" s="113" t="n"/>
-      <c r="I20" s="113" t="n"/>
-      <c r="J20" s="113" t="n"/>
-      <c r="K20" s="113" t="n"/>
-      <c r="L20" s="113" t="n"/>
-      <c r="M20" s="113" t="n"/>
-      <c r="N20" s="113" t="n"/>
-      <c r="O20" s="113" t="n"/>
-      <c r="P20" s="113" t="n"/>
-      <c r="Q20" s="113" t="n"/>
-      <c r="R20" s="113" t="n"/>
-      <c r="S20" s="113" t="n"/>
-      <c r="T20" s="113" t="n"/>
-      <c r="U20" s="113" t="n"/>
-      <c r="V20" s="113" t="n"/>
-      <c r="W20" s="113" t="n"/>
       <c r="X20" s="84" t="n"/>
       <c r="Y20" s="84" t="n"/>
       <c r="Z20" s="84" t="n"/>
@@ -2673,33 +2619,11 @@
       <c r="AF23" s="84" t="n"/>
     </row>
     <row r="24" ht="20" customHeight="1" s="80">
-      <c r="A24" s="112" t="inlineStr">
+      <c r="A24" s="167" t="inlineStr">
         <is>
           <t>▶ Phase 3: 中優先度（3〜4週間以内）</t>
         </is>
       </c>
-      <c r="B24" s="113" t="n"/>
-      <c r="C24" s="113" t="n"/>
-      <c r="D24" s="113" t="n"/>
-      <c r="E24" s="113" t="n"/>
-      <c r="F24" s="113" t="n"/>
-      <c r="G24" s="113" t="n"/>
-      <c r="H24" s="113" t="n"/>
-      <c r="I24" s="113" t="n"/>
-      <c r="J24" s="113" t="n"/>
-      <c r="K24" s="113" t="n"/>
-      <c r="L24" s="113" t="n"/>
-      <c r="M24" s="113" t="n"/>
-      <c r="N24" s="113" t="n"/>
-      <c r="O24" s="113" t="n"/>
-      <c r="P24" s="113" t="n"/>
-      <c r="Q24" s="113" t="n"/>
-      <c r="R24" s="113" t="n"/>
-      <c r="S24" s="113" t="n"/>
-      <c r="T24" s="113" t="n"/>
-      <c r="U24" s="113" t="n"/>
-      <c r="V24" s="113" t="n"/>
-      <c r="W24" s="113" t="n"/>
       <c r="X24" s="84" t="n"/>
       <c r="Y24" s="84" t="n"/>
       <c r="Z24" s="84" t="n"/>
@@ -3001,33 +2925,11 @@
       <c r="AF29" s="84" t="n"/>
     </row>
     <row r="30" ht="20" customHeight="1" s="80">
-      <c r="A30" s="112" t="inlineStr">
+      <c r="A30" s="167" t="inlineStr">
         <is>
           <t>▶ Phase 4: 低優先度（2〜3ヶ月以内）</t>
         </is>
       </c>
-      <c r="B30" s="113" t="n"/>
-      <c r="C30" s="113" t="n"/>
-      <c r="D30" s="113" t="n"/>
-      <c r="E30" s="113" t="n"/>
-      <c r="F30" s="113" t="n"/>
-      <c r="G30" s="113" t="n"/>
-      <c r="H30" s="113" t="n"/>
-      <c r="I30" s="113" t="n"/>
-      <c r="J30" s="113" t="n"/>
-      <c r="K30" s="113" t="n"/>
-      <c r="L30" s="113" t="n"/>
-      <c r="M30" s="113" t="n"/>
-      <c r="N30" s="113" t="n"/>
-      <c r="O30" s="113" t="n"/>
-      <c r="P30" s="113" t="n"/>
-      <c r="Q30" s="113" t="n"/>
-      <c r="R30" s="113" t="n"/>
-      <c r="S30" s="113" t="n"/>
-      <c r="T30" s="113" t="n"/>
-      <c r="U30" s="113" t="n"/>
-      <c r="V30" s="113" t="n"/>
-      <c r="W30" s="113" t="n"/>
       <c r="X30" s="84" t="n"/>
       <c r="Y30" s="84" t="n"/>
       <c r="Z30" s="84" t="n"/>
@@ -3329,33 +3231,11 @@
       <c r="AF35" s="84" t="n"/>
     </row>
     <row r="36" ht="20" customHeight="1" s="80">
-      <c r="A36" s="115" t="inlineStr">
+      <c r="A36" s="168" t="inlineStr">
         <is>
           <t>AWS インフラ改修</t>
         </is>
       </c>
-      <c r="B36" s="116" t="n"/>
-      <c r="C36" s="116" t="n"/>
-      <c r="D36" s="116" t="n"/>
-      <c r="E36" s="116" t="n"/>
-      <c r="F36" s="116" t="n"/>
-      <c r="G36" s="116" t="n"/>
-      <c r="H36" s="116" t="n"/>
-      <c r="I36" s="116" t="n"/>
-      <c r="J36" s="116" t="n"/>
-      <c r="K36" s="116" t="n"/>
-      <c r="L36" s="116" t="n"/>
-      <c r="M36" s="116" t="n"/>
-      <c r="N36" s="116" t="n"/>
-      <c r="O36" s="116" t="n"/>
-      <c r="P36" s="116" t="n"/>
-      <c r="Q36" s="116" t="n"/>
-      <c r="R36" s="116" t="n"/>
-      <c r="S36" s="116" t="n"/>
-      <c r="T36" s="116" t="n"/>
-      <c r="U36" s="116" t="n"/>
-      <c r="V36" s="116" t="n"/>
-      <c r="W36" s="116" t="n"/>
       <c r="X36" s="84" t="n"/>
       <c r="Y36" s="84" t="n"/>
       <c r="Z36" s="84" t="n"/>
@@ -3367,33 +3247,11 @@
       <c r="AF36" s="84" t="n"/>
     </row>
     <row r="37" ht="20" customHeight="1" s="80">
-      <c r="A37" s="117" t="inlineStr">
+      <c r="A37" s="169" t="inlineStr">
         <is>
           <t>▶ ① バックアップ保持期間の変更（1日→7日以上）</t>
         </is>
       </c>
-      <c r="B37" s="118" t="n"/>
-      <c r="C37" s="118" t="n"/>
-      <c r="D37" s="118" t="n"/>
-      <c r="E37" s="118" t="n"/>
-      <c r="F37" s="118" t="n"/>
-      <c r="G37" s="118" t="n"/>
-      <c r="H37" s="118" t="n"/>
-      <c r="I37" s="118" t="n"/>
-      <c r="J37" s="118" t="n"/>
-      <c r="K37" s="118" t="n"/>
-      <c r="L37" s="118" t="n"/>
-      <c r="M37" s="118" t="n"/>
-      <c r="N37" s="118" t="n"/>
-      <c r="O37" s="118" t="n"/>
-      <c r="P37" s="118" t="n"/>
-      <c r="Q37" s="118" t="n"/>
-      <c r="R37" s="118" t="n"/>
-      <c r="S37" s="118" t="n"/>
-      <c r="T37" s="118" t="n"/>
-      <c r="U37" s="118" t="n"/>
-      <c r="V37" s="118" t="n"/>
-      <c r="W37" s="118" t="n"/>
       <c r="X37" s="84" t="n"/>
       <c r="Y37" s="84" t="n"/>
       <c r="Z37" s="84" t="n"/>
@@ -3571,33 +3429,11 @@
       <c r="AF40" s="84" t="n"/>
     </row>
     <row r="41" ht="20" customHeight="1" s="80">
-      <c r="A41" s="117" t="inlineStr">
+      <c r="A41" s="169" t="inlineStr">
         <is>
           <t>▶ ② AWS Backup 月次スナップショット設定</t>
         </is>
       </c>
-      <c r="B41" s="118" t="n"/>
-      <c r="C41" s="118" t="n"/>
-      <c r="D41" s="118" t="n"/>
-      <c r="E41" s="118" t="n"/>
-      <c r="F41" s="118" t="n"/>
-      <c r="G41" s="118" t="n"/>
-      <c r="H41" s="118" t="n"/>
-      <c r="I41" s="118" t="n"/>
-      <c r="J41" s="118" t="n"/>
-      <c r="K41" s="118" t="n"/>
-      <c r="L41" s="118" t="n"/>
-      <c r="M41" s="118" t="n"/>
-      <c r="N41" s="118" t="n"/>
-      <c r="O41" s="118" t="n"/>
-      <c r="P41" s="118" t="n"/>
-      <c r="Q41" s="118" t="n"/>
-      <c r="R41" s="118" t="n"/>
-      <c r="S41" s="118" t="n"/>
-      <c r="T41" s="118" t="n"/>
-      <c r="U41" s="118" t="n"/>
-      <c r="V41" s="118" t="n"/>
-      <c r="W41" s="118" t="n"/>
       <c r="X41" s="84" t="n"/>
       <c r="Y41" s="84" t="n"/>
       <c r="Z41" s="84" t="n"/>
@@ -3775,33 +3611,11 @@
       <c r="AF44" s="84" t="n"/>
     </row>
     <row r="45" ht="20" customHeight="1" s="80">
-      <c r="A45" s="120" t="inlineStr">
+      <c r="A45" s="170" t="inlineStr">
         <is>
           <t>AWS インフラ改修（中優先度）</t>
         </is>
       </c>
-      <c r="B45" s="121" t="n"/>
-      <c r="C45" s="121" t="n"/>
-      <c r="D45" s="121" t="n"/>
-      <c r="E45" s="121" t="n"/>
-      <c r="F45" s="121" t="n"/>
-      <c r="G45" s="121" t="n"/>
-      <c r="H45" s="121" t="n"/>
-      <c r="I45" s="121" t="n"/>
-      <c r="J45" s="121" t="n"/>
-      <c r="K45" s="121" t="n"/>
-      <c r="L45" s="121" t="n"/>
-      <c r="M45" s="121" t="n"/>
-      <c r="N45" s="121" t="n"/>
-      <c r="O45" s="121" t="n"/>
-      <c r="P45" s="121" t="n"/>
-      <c r="Q45" s="121" t="n"/>
-      <c r="R45" s="121" t="n"/>
-      <c r="S45" s="121" t="n"/>
-      <c r="T45" s="121" t="n"/>
-      <c r="U45" s="121" t="n"/>
-      <c r="V45" s="121" t="n"/>
-      <c r="W45" s="121" t="n"/>
       <c r="X45" s="84" t="n"/>
       <c r="Y45" s="84" t="n"/>
       <c r="Z45" s="84" t="n"/>
@@ -3813,33 +3627,11 @@
       <c r="AF45" s="84" t="n"/>
     </row>
     <row r="46" ht="20" customHeight="1" s="80">
-      <c r="A46" s="122" t="inlineStr">
+      <c r="A46" s="171" t="inlineStr">
         <is>
           <t>▶ ④ create-file-end-for-night DB接続先変更</t>
         </is>
       </c>
-      <c r="B46" s="123" t="n"/>
-      <c r="C46" s="123" t="n"/>
-      <c r="D46" s="123" t="n"/>
-      <c r="E46" s="123" t="n"/>
-      <c r="F46" s="123" t="n"/>
-      <c r="G46" s="123" t="n"/>
-      <c r="H46" s="123" t="n"/>
-      <c r="I46" s="123" t="n"/>
-      <c r="J46" s="123" t="n"/>
-      <c r="K46" s="123" t="n"/>
-      <c r="L46" s="123" t="n"/>
-      <c r="M46" s="123" t="n"/>
-      <c r="N46" s="123" t="n"/>
-      <c r="O46" s="123" t="n"/>
-      <c r="P46" s="123" t="n"/>
-      <c r="Q46" s="123" t="n"/>
-      <c r="R46" s="123" t="n"/>
-      <c r="S46" s="123" t="n"/>
-      <c r="T46" s="123" t="n"/>
-      <c r="U46" s="123" t="n"/>
-      <c r="V46" s="123" t="n"/>
-      <c r="W46" s="123" t="n"/>
       <c r="X46" s="84" t="n"/>
       <c r="Y46" s="84" t="n"/>
       <c r="Z46" s="84" t="n"/>
@@ -4017,33 +3809,11 @@
       <c r="AF49" s="84" t="n"/>
     </row>
     <row r="50" ht="20" customHeight="1" s="80">
-      <c r="A50" s="122" t="inlineStr">
+      <c r="A50" s="171" t="inlineStr">
         <is>
           <t>▶ ⑤ PromotionTier 同値問題（instance-2 → Tier=2）</t>
         </is>
       </c>
-      <c r="B50" s="123" t="n"/>
-      <c r="C50" s="123" t="n"/>
-      <c r="D50" s="123" t="n"/>
-      <c r="E50" s="123" t="n"/>
-      <c r="F50" s="123" t="n"/>
-      <c r="G50" s="123" t="n"/>
-      <c r="H50" s="123" t="n"/>
-      <c r="I50" s="123" t="n"/>
-      <c r="J50" s="123" t="n"/>
-      <c r="K50" s="123" t="n"/>
-      <c r="L50" s="123" t="n"/>
-      <c r="M50" s="123" t="n"/>
-      <c r="N50" s="123" t="n"/>
-      <c r="O50" s="123" t="n"/>
-      <c r="P50" s="123" t="n"/>
-      <c r="Q50" s="123" t="n"/>
-      <c r="R50" s="123" t="n"/>
-      <c r="S50" s="123" t="n"/>
-      <c r="T50" s="123" t="n"/>
-      <c r="U50" s="123" t="n"/>
-      <c r="V50" s="123" t="n"/>
-      <c r="W50" s="123" t="n"/>
       <c r="X50" s="84" t="n"/>
       <c r="Y50" s="84" t="n"/>
       <c r="Z50" s="84" t="n"/>
@@ -4167,33 +3937,11 @@
       <c r="AF52" s="84" t="n"/>
     </row>
     <row r="53" ht="20" customHeight="1" s="80">
-      <c r="A53" s="122" t="inlineStr">
+      <c r="A53" s="171" t="inlineStr">
         <is>
           <t>▶ ③ RDS インスタンスダウンサイズ（承認後実施）</t>
         </is>
       </c>
-      <c r="B53" s="123" t="n"/>
-      <c r="C53" s="123" t="n"/>
-      <c r="D53" s="123" t="n"/>
-      <c r="E53" s="123" t="n"/>
-      <c r="F53" s="123" t="n"/>
-      <c r="G53" s="123" t="n"/>
-      <c r="H53" s="123" t="n"/>
-      <c r="I53" s="123" t="n"/>
-      <c r="J53" s="123" t="n"/>
-      <c r="K53" s="123" t="n"/>
-      <c r="L53" s="123" t="n"/>
-      <c r="M53" s="123" t="n"/>
-      <c r="N53" s="123" t="n"/>
-      <c r="O53" s="123" t="n"/>
-      <c r="P53" s="123" t="n"/>
-      <c r="Q53" s="123" t="n"/>
-      <c r="R53" s="123" t="n"/>
-      <c r="S53" s="123" t="n"/>
-      <c r="T53" s="123" t="n"/>
-      <c r="U53" s="123" t="n"/>
-      <c r="V53" s="123" t="n"/>
-      <c r="W53" s="123" t="n"/>
       <c r="X53" s="84" t="n"/>
       <c r="Y53" s="84" t="n"/>
       <c r="Z53" s="84" t="n"/>
@@ -4619,33 +4367,11 @@
       <c r="AF60" s="84" t="n"/>
     </row>
     <row r="61" ht="20" customHeight="1" s="80">
-      <c r="A61" s="122" t="inlineStr">
+      <c r="A61" s="171" t="inlineStr">
         <is>
           <t>▶ ⑥ シークレット命名の改善（中長期・任意）</t>
         </is>
       </c>
-      <c r="B61" s="123" t="n"/>
-      <c r="C61" s="123" t="n"/>
-      <c r="D61" s="123" t="n"/>
-      <c r="E61" s="123" t="n"/>
-      <c r="F61" s="123" t="n"/>
-      <c r="G61" s="123" t="n"/>
-      <c r="H61" s="123" t="n"/>
-      <c r="I61" s="123" t="n"/>
-      <c r="J61" s="123" t="n"/>
-      <c r="K61" s="123" t="n"/>
-      <c r="L61" s="123" t="n"/>
-      <c r="M61" s="123" t="n"/>
-      <c r="N61" s="123" t="n"/>
-      <c r="O61" s="123" t="n"/>
-      <c r="P61" s="123" t="n"/>
-      <c r="Q61" s="123" t="n"/>
-      <c r="R61" s="123" t="n"/>
-      <c r="S61" s="123" t="n"/>
-      <c r="T61" s="123" t="n"/>
-      <c r="U61" s="123" t="n"/>
-      <c r="V61" s="123" t="n"/>
-      <c r="W61" s="123" t="n"/>
       <c r="X61" s="84" t="n"/>
       <c r="Y61" s="84" t="n"/>
       <c r="Z61" s="84" t="n"/>
@@ -4910,38 +4636,12 @@
       <c r="AE66" s="84" t="n"/>
       <c r="AF66" s="84" t="n"/>
     </row>
-    <row r="67" ht="15" customHeight="1" s="80">
-      <c r="A67" s="127" t="inlineStr">
-        <is>
-          <t>凡例:</t>
-        </is>
-      </c>
-      <c r="B67" s="128" t="inlineStr">
-        <is>
-          <t>○=予定期間  ■紫=リポジトリ統合  ■紺=コード修正  ■赤=AWS高優先  ■橙=AWS中優先</t>
-        </is>
-      </c>
-      <c r="C67" s="126" t="n"/>
-      <c r="D67" s="126" t="n"/>
-      <c r="E67" s="84" t="n"/>
-      <c r="F67" s="84" t="n"/>
-      <c r="G67" s="84" t="n"/>
-      <c r="H67" s="84" t="n"/>
-      <c r="I67" s="84" t="n"/>
-      <c r="J67" s="84" t="n"/>
-      <c r="K67" s="84" t="n"/>
-      <c r="L67" s="84" t="n"/>
-      <c r="M67" s="84" t="n"/>
-      <c r="N67" s="84" t="n"/>
-      <c r="O67" s="84" t="n"/>
-      <c r="P67" s="84" t="n"/>
-      <c r="Q67" s="84" t="n"/>
-      <c r="R67" s="84" t="n"/>
-      <c r="S67" s="84" t="n"/>
-      <c r="T67" s="84" t="n"/>
-      <c r="U67" s="84" t="n"/>
-      <c r="V67" s="84" t="n"/>
-      <c r="W67" s="84" t="n"/>
+    <row r="67" ht="20" customHeight="1" s="80">
+      <c r="A67" s="172" t="inlineStr">
+        <is>
+          <t>定期運用 — AWS月次コスト妥当性チェック</t>
+        </is>
+      </c>
       <c r="X67" s="84" t="n"/>
       <c r="Y67" s="84" t="n"/>
       <c r="Z67" s="84" t="n"/>
@@ -4952,30 +4652,12 @@
       <c r="AE67" s="84" t="n"/>
       <c r="AF67" s="84" t="n"/>
     </row>
-    <row r="68" ht="15" customHeight="1" s="80">
-      <c r="A68" s="125" t="n"/>
-      <c r="B68" s="84" t="n"/>
-      <c r="C68" s="126" t="n"/>
-      <c r="D68" s="126" t="n"/>
-      <c r="E68" s="84" t="n"/>
-      <c r="F68" s="84" t="n"/>
-      <c r="G68" s="84" t="n"/>
-      <c r="H68" s="84" t="n"/>
-      <c r="I68" s="84" t="n"/>
-      <c r="J68" s="84" t="n"/>
-      <c r="K68" s="84" t="n"/>
-      <c r="L68" s="84" t="n"/>
-      <c r="M68" s="84" t="n"/>
-      <c r="N68" s="84" t="n"/>
-      <c r="O68" s="84" t="n"/>
-      <c r="P68" s="84" t="n"/>
-      <c r="Q68" s="84" t="n"/>
-      <c r="R68" s="84" t="n"/>
-      <c r="S68" s="84" t="n"/>
-      <c r="T68" s="84" t="n"/>
-      <c r="U68" s="84" t="n"/>
-      <c r="V68" s="84" t="n"/>
-      <c r="W68" s="84" t="n"/>
+    <row r="68" ht="18" customHeight="1" s="80">
+      <c r="A68" s="173" t="inlineStr">
+        <is>
+          <t>▶ 毎月末: CloudShellでコストデータ取得・確認（40_AWS/06_コスト調査/monthly_cost_check.sh）</t>
+        </is>
+      </c>
       <c r="X68" s="84" t="n"/>
       <c r="Y68" s="84" t="n"/>
       <c r="Z68" s="84" t="n"/>
@@ -4986,30 +4668,54 @@
       <c r="AE68" s="84" t="n"/>
       <c r="AF68" s="84" t="n"/>
     </row>
-    <row r="69" ht="15" customHeight="1" s="80">
-      <c r="A69" s="125" t="n"/>
-      <c r="B69" s="84" t="n"/>
-      <c r="C69" s="126" t="n"/>
-      <c r="D69" s="126" t="n"/>
-      <c r="E69" s="84" t="n"/>
-      <c r="F69" s="84" t="n"/>
-      <c r="G69" s="84" t="n"/>
-      <c r="H69" s="84" t="n"/>
-      <c r="I69" s="84" t="n"/>
-      <c r="J69" s="84" t="n"/>
-      <c r="K69" s="84" t="n"/>
-      <c r="L69" s="84" t="n"/>
-      <c r="M69" s="84" t="n"/>
-      <c r="N69" s="84" t="n"/>
-      <c r="O69" s="84" t="n"/>
-      <c r="P69" s="84" t="n"/>
-      <c r="Q69" s="84" t="n"/>
-      <c r="R69" s="84" t="n"/>
-      <c r="S69" s="84" t="n"/>
-      <c r="T69" s="84" t="n"/>
-      <c r="U69" s="84" t="n"/>
-      <c r="V69" s="84" t="n"/>
-      <c r="W69" s="84" t="n"/>
+    <row r="69" ht="18" customHeight="1" s="80">
+      <c r="A69" s="174" t="inlineStr">
+        <is>
+          <t>M-1</t>
+        </is>
+      </c>
+      <c r="B69" s="175" t="inlineStr">
+        <is>
+          <t>3月分コスト確認（4/1〜4/3実施）</t>
+        </is>
+      </c>
+      <c r="C69" s="176" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="D69" s="176" t="n"/>
+      <c r="E69" s="177" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
+      <c r="F69" s="178" t="inlineStr">
+        <is>
+          <t>monthly_cost_check.sh実行・結果保存</t>
+        </is>
+      </c>
+      <c r="G69" s="179" t="n"/>
+      <c r="H69" s="179" t="n"/>
+      <c r="I69" s="179" t="n"/>
+      <c r="J69" s="180" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="K69" s="179" t="n"/>
+      <c r="L69" s="179" t="n"/>
+      <c r="M69" s="179" t="n"/>
+      <c r="N69" s="179" t="n"/>
+      <c r="O69" s="179" t="n"/>
+      <c r="P69" s="179" t="n"/>
+      <c r="Q69" s="179" t="n"/>
+      <c r="R69" s="179" t="n"/>
+      <c r="S69" s="179" t="n"/>
+      <c r="T69" s="179" t="n"/>
+      <c r="U69" s="179" t="n"/>
+      <c r="V69" s="179" t="n"/>
+      <c r="W69" s="179" t="n"/>
       <c r="X69" s="84" t="n"/>
       <c r="Y69" s="84" t="n"/>
       <c r="Z69" s="84" t="n"/>
@@ -5020,30 +4726,54 @@
       <c r="AE69" s="84" t="n"/>
       <c r="AF69" s="84" t="n"/>
     </row>
-    <row r="70" ht="19.5" customHeight="1" s="80">
-      <c r="A70" s="125" t="n"/>
-      <c r="B70" s="84" t="n"/>
-      <c r="C70" s="84" t="n"/>
-      <c r="D70" s="84" t="n"/>
-      <c r="E70" s="84" t="n"/>
-      <c r="F70" s="84" t="n"/>
-      <c r="G70" s="84" t="n"/>
-      <c r="H70" s="84" t="n"/>
-      <c r="I70" s="84" t="n"/>
-      <c r="J70" s="84" t="n"/>
-      <c r="K70" s="84" t="n"/>
-      <c r="L70" s="84" t="n"/>
-      <c r="M70" s="84" t="n"/>
-      <c r="N70" s="84" t="n"/>
-      <c r="O70" s="84" t="n"/>
-      <c r="P70" s="84" t="n"/>
-      <c r="Q70" s="84" t="n"/>
-      <c r="R70" s="84" t="n"/>
-      <c r="S70" s="84" t="n"/>
-      <c r="T70" s="84" t="n"/>
-      <c r="U70" s="84" t="n"/>
-      <c r="V70" s="84" t="n"/>
-      <c r="W70" s="84" t="n"/>
+    <row r="70" ht="18" customHeight="1" s="80">
+      <c r="A70" s="174" t="inlineStr">
+        <is>
+          <t>M-2</t>
+        </is>
+      </c>
+      <c r="B70" s="175" t="inlineStr">
+        <is>
+          <t>4月分コスト確認（5/1〜5/3実施）</t>
+        </is>
+      </c>
+      <c r="C70" s="181" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="D70" s="181" t="n"/>
+      <c r="E70" s="177" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
+      <c r="F70" s="178" t="inlineStr">
+        <is>
+          <t>monthly_cost_check.sh実行・結果保存</t>
+        </is>
+      </c>
+      <c r="G70" s="179" t="n"/>
+      <c r="H70" s="179" t="n"/>
+      <c r="I70" s="179" t="n"/>
+      <c r="J70" s="179" t="n"/>
+      <c r="K70" s="179" t="n"/>
+      <c r="L70" s="179" t="n"/>
+      <c r="M70" s="179" t="n"/>
+      <c r="N70" s="180" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="O70" s="179" t="n"/>
+      <c r="P70" s="179" t="n"/>
+      <c r="Q70" s="179" t="n"/>
+      <c r="R70" s="179" t="n"/>
+      <c r="S70" s="179" t="n"/>
+      <c r="T70" s="179" t="n"/>
+      <c r="U70" s="179" t="n"/>
+      <c r="V70" s="179" t="n"/>
+      <c r="W70" s="179" t="n"/>
       <c r="X70" s="84" t="n"/>
       <c r="Y70" s="84" t="n"/>
       <c r="Z70" s="84" t="n"/>
@@ -5054,30 +4784,54 @@
       <c r="AE70" s="84" t="n"/>
       <c r="AF70" s="84" t="n"/>
     </row>
-    <row r="71" ht="16.5" customHeight="1" s="80">
-      <c r="A71" s="125" t="n"/>
-      <c r="B71" s="84" t="n"/>
-      <c r="C71" s="84" t="n"/>
-      <c r="D71" s="84" t="n"/>
-      <c r="E71" s="84" t="n"/>
-      <c r="F71" s="84" t="n"/>
-      <c r="G71" s="84" t="n"/>
-      <c r="H71" s="84" t="n"/>
-      <c r="I71" s="84" t="n"/>
-      <c r="J71" s="84" t="n"/>
-      <c r="K71" s="84" t="n"/>
-      <c r="L71" s="84" t="n"/>
-      <c r="M71" s="84" t="n"/>
-      <c r="N71" s="84" t="n"/>
-      <c r="O71" s="84" t="n"/>
-      <c r="P71" s="84" t="n"/>
-      <c r="Q71" s="84" t="n"/>
-      <c r="R71" s="84" t="n"/>
-      <c r="S71" s="84" t="n"/>
-      <c r="T71" s="84" t="n"/>
-      <c r="U71" s="84" t="n"/>
-      <c r="V71" s="84" t="n"/>
-      <c r="W71" s="84" t="n"/>
+    <row r="71" ht="18" customHeight="1" s="80">
+      <c r="A71" s="174" t="inlineStr">
+        <is>
+          <t>M-3</t>
+        </is>
+      </c>
+      <c r="B71" s="175" t="inlineStr">
+        <is>
+          <t>5月分コスト確認（6/1〜6/3実施）</t>
+        </is>
+      </c>
+      <c r="C71" s="181" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="D71" s="181" t="n"/>
+      <c r="E71" s="177" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
+      <c r="F71" s="178" t="inlineStr">
+        <is>
+          <t>monthly_cost_check.sh実行・結果保存</t>
+        </is>
+      </c>
+      <c r="G71" s="179" t="n"/>
+      <c r="H71" s="179" t="n"/>
+      <c r="I71" s="179" t="n"/>
+      <c r="J71" s="179" t="n"/>
+      <c r="K71" s="179" t="n"/>
+      <c r="L71" s="179" t="n"/>
+      <c r="M71" s="179" t="n"/>
+      <c r="N71" s="179" t="n"/>
+      <c r="O71" s="179" t="n"/>
+      <c r="P71" s="179" t="n"/>
+      <c r="Q71" s="179" t="n"/>
+      <c r="R71" s="180" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="S71" s="179" t="n"/>
+      <c r="T71" s="179" t="n"/>
+      <c r="U71" s="179" t="n"/>
+      <c r="V71" s="179" t="n"/>
+      <c r="W71" s="179" t="n"/>
       <c r="X71" s="84" t="n"/>
       <c r="Y71" s="84" t="n"/>
       <c r="Z71" s="84" t="n"/>
@@ -5088,30 +4842,54 @@
       <c r="AE71" s="84" t="n"/>
       <c r="AF71" s="84" t="n"/>
     </row>
-    <row r="72" ht="16.5" customHeight="1" s="80">
-      <c r="A72" s="125" t="n"/>
-      <c r="B72" s="84" t="n"/>
-      <c r="C72" s="126" t="n"/>
-      <c r="D72" s="126" t="n"/>
-      <c r="E72" s="84" t="n"/>
-      <c r="F72" s="84" t="n"/>
-      <c r="G72" s="84" t="n"/>
-      <c r="H72" s="84" t="n"/>
-      <c r="I72" s="84" t="n"/>
-      <c r="J72" s="84" t="n"/>
-      <c r="K72" s="84" t="n"/>
-      <c r="L72" s="84" t="n"/>
-      <c r="M72" s="84" t="n"/>
-      <c r="N72" s="84" t="n"/>
-      <c r="O72" s="84" t="n"/>
-      <c r="P72" s="84" t="n"/>
-      <c r="Q72" s="84" t="n"/>
-      <c r="R72" s="84" t="n"/>
-      <c r="S72" s="84" t="n"/>
-      <c r="T72" s="84" t="n"/>
-      <c r="U72" s="84" t="n"/>
-      <c r="V72" s="84" t="n"/>
-      <c r="W72" s="84" t="n"/>
+    <row r="72" ht="18" customHeight="1" s="80">
+      <c r="A72" s="174" t="inlineStr">
+        <is>
+          <t>M-4</t>
+        </is>
+      </c>
+      <c r="B72" s="175" t="inlineStr">
+        <is>
+          <t>6月分コスト確認（7/1〜7/3実施）</t>
+        </is>
+      </c>
+      <c r="C72" s="176" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="D72" s="176" t="n"/>
+      <c r="E72" s="177" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
+      <c r="F72" s="178" t="inlineStr">
+        <is>
+          <t>monthly_cost_check.sh実行・結果保存</t>
+        </is>
+      </c>
+      <c r="G72" s="179" t="n"/>
+      <c r="H72" s="179" t="n"/>
+      <c r="I72" s="179" t="n"/>
+      <c r="J72" s="179" t="n"/>
+      <c r="K72" s="179" t="n"/>
+      <c r="L72" s="179" t="n"/>
+      <c r="M72" s="179" t="n"/>
+      <c r="N72" s="179" t="n"/>
+      <c r="O72" s="179" t="n"/>
+      <c r="P72" s="179" t="n"/>
+      <c r="Q72" s="179" t="n"/>
+      <c r="R72" s="179" t="n"/>
+      <c r="S72" s="179" t="n"/>
+      <c r="T72" s="179" t="n"/>
+      <c r="U72" s="179" t="n"/>
+      <c r="V72" s="179" t="n"/>
+      <c r="W72" s="180" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
       <c r="X72" s="84" t="n"/>
       <c r="Y72" s="84" t="n"/>
       <c r="Z72" s="84" t="n"/>
@@ -5122,30 +4900,12 @@
       <c r="AE72" s="84" t="n"/>
       <c r="AF72" s="84" t="n"/>
     </row>
-    <row r="73" ht="16.5" customHeight="1" s="80">
-      <c r="A73" s="125" t="n"/>
-      <c r="B73" s="84" t="n"/>
-      <c r="C73" s="126" t="n"/>
-      <c r="D73" s="126" t="n"/>
-      <c r="E73" s="84" t="n"/>
-      <c r="F73" s="84" t="n"/>
-      <c r="G73" s="84" t="n"/>
-      <c r="H73" s="84" t="n"/>
-      <c r="I73" s="84" t="n"/>
-      <c r="J73" s="84" t="n"/>
-      <c r="K73" s="84" t="n"/>
-      <c r="L73" s="84" t="n"/>
-      <c r="M73" s="84" t="n"/>
-      <c r="N73" s="84" t="n"/>
-      <c r="O73" s="84" t="n"/>
-      <c r="P73" s="84" t="n"/>
-      <c r="Q73" s="84" t="n"/>
-      <c r="R73" s="84" t="n"/>
-      <c r="S73" s="84" t="n"/>
-      <c r="T73" s="84" t="n"/>
-      <c r="U73" s="84" t="n"/>
-      <c r="V73" s="84" t="n"/>
-      <c r="W73" s="84" t="n"/>
+    <row r="73" ht="18" customHeight="1" s="80">
+      <c r="A73" s="173" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  確認項目: ①月間合計 ②サービス別内訳 ③RDS CPU/接続数 ④Lambda実行回数・エラー ⑤S3使用量 ⑥前月比</t>
+        </is>
+      </c>
       <c r="X73" s="84" t="n"/>
       <c r="Y73" s="84" t="n"/>
       <c r="Z73" s="84" t="n"/>
@@ -13079,10 +12839,13 @@
       <c r="AF306" s="84" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="21">
+  <mergeCells count="24">
+    <mergeCell ref="A68:W68"/>
+    <mergeCell ref="A67:W67"/>
     <mergeCell ref="A30:W30"/>
     <mergeCell ref="O2:R2"/>
     <mergeCell ref="A24:W24"/>
+    <mergeCell ref="A73:W73"/>
     <mergeCell ref="A11:W11"/>
     <mergeCell ref="A36:W36"/>
     <mergeCell ref="A1:W1"/>

--- a/00_スケジュール/AWS改修スケジュール.xlsx
+++ b/00_スケジュール/AWS改修スケジュール.xlsx
@@ -20,7 +20,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="m/d/yyyy"/>
   </numFmts>
-  <fonts count="56">
+  <fonts count="60">
     <font>
       <name val="Calibri"/>
       <charset val="1"/>
@@ -385,6 +385,27 @@
       <name val="Calibri"/>
       <sz val="9"/>
     </font>
+    <font>
+      <name val="BIZ UDPゴシック"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="BIZ UDPゴシック"/>
+      <color rgb="00000000"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="BIZ UDPゴシック"/>
+      <color rgb="00000000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="BIZ UDPゴシック"/>
+      <color rgb="00000000"/>
+      <sz val="10"/>
+    </font>
   </fonts>
   <fills count="38">
     <fill>
@@ -589,7 +610,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="14">
     <border>
       <left/>
       <right/>
@@ -690,6 +711,50 @@
       <right/>
       <bottom/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00CCCCCC"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00CCCCCC"/>
+      </right>
+      <top style="thin">
+        <color rgb="00CCCCCC"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00CCCCCC"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00CCCCCC"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00CCCCCC"/>
+      </right>
+      <top style="thin">
+        <color rgb="00CCCCCC"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00CCCCCC"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
@@ -701,7 +766,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="182">
+  <cellXfs count="189">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -1212,6 +1277,27 @@
     <xf numFmtId="0" fontId="51" fillId="36" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="56" fillId="32" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="57" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="57" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="59" fillId="33" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="57" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="57" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1488,7 +1574,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:AF306"/>
+  <dimension ref="A1:AF312"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="5.00390625" defaultRowHeight="15.75" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="7.14" customWidth="1" style="78" min="1" max="1"/>
@@ -1770,22 +1856,22 @@
           <t>○</t>
         </is>
       </c>
-      <c r="H6" s="108" t="n"/>
-      <c r="I6" s="108" t="n"/>
-      <c r="J6" s="108" t="n"/>
-      <c r="K6" s="108" t="n"/>
-      <c r="L6" s="108" t="n"/>
-      <c r="M6" s="108" t="n"/>
-      <c r="N6" s="108" t="n"/>
-      <c r="O6" s="108" t="n"/>
-      <c r="P6" s="108" t="n"/>
-      <c r="Q6" s="108" t="n"/>
-      <c r="R6" s="108" t="n"/>
-      <c r="S6" s="108" t="n"/>
-      <c r="T6" s="108" t="n"/>
-      <c r="U6" s="108" t="n"/>
-      <c r="V6" s="108" t="n"/>
-      <c r="W6" s="108" t="n"/>
+      <c r="H6" s="179" t="n"/>
+      <c r="I6" s="179" t="n"/>
+      <c r="J6" s="179" t="n"/>
+      <c r="K6" s="179" t="n"/>
+      <c r="L6" s="179" t="n"/>
+      <c r="M6" s="179" t="n"/>
+      <c r="N6" s="179" t="n"/>
+      <c r="O6" s="179" t="n"/>
+      <c r="P6" s="179" t="n"/>
+      <c r="Q6" s="179" t="n"/>
+      <c r="R6" s="179" t="n"/>
+      <c r="S6" s="179" t="n"/>
+      <c r="T6" s="179" t="n"/>
+      <c r="U6" s="179" t="n"/>
+      <c r="V6" s="179" t="n"/>
+      <c r="W6" s="179" t="n"/>
       <c r="X6" s="84" t="n"/>
       <c r="Y6" s="84" t="n"/>
       <c r="Z6" s="84" t="n"/>
@@ -1828,22 +1914,22 @@
           <t>○</t>
         </is>
       </c>
-      <c r="H7" s="108" t="n"/>
-      <c r="I7" s="108" t="n"/>
-      <c r="J7" s="108" t="n"/>
-      <c r="K7" s="108" t="n"/>
-      <c r="L7" s="108" t="n"/>
-      <c r="M7" s="108" t="n"/>
-      <c r="N7" s="108" t="n"/>
-      <c r="O7" s="108" t="n"/>
-      <c r="P7" s="108" t="n"/>
-      <c r="Q7" s="108" t="n"/>
-      <c r="R7" s="108" t="n"/>
-      <c r="S7" s="108" t="n"/>
-      <c r="T7" s="108" t="n"/>
-      <c r="U7" s="108" t="n"/>
-      <c r="V7" s="108" t="n"/>
-      <c r="W7" s="108" t="n"/>
+      <c r="H7" s="179" t="n"/>
+      <c r="I7" s="179" t="n"/>
+      <c r="J7" s="179" t="n"/>
+      <c r="K7" s="179" t="n"/>
+      <c r="L7" s="179" t="n"/>
+      <c r="M7" s="179" t="n"/>
+      <c r="N7" s="179" t="n"/>
+      <c r="O7" s="179" t="n"/>
+      <c r="P7" s="179" t="n"/>
+      <c r="Q7" s="179" t="n"/>
+      <c r="R7" s="179" t="n"/>
+      <c r="S7" s="179" t="n"/>
+      <c r="T7" s="179" t="n"/>
+      <c r="U7" s="179" t="n"/>
+      <c r="V7" s="179" t="n"/>
+      <c r="W7" s="179" t="n"/>
       <c r="X7" s="84" t="n"/>
       <c r="Y7" s="84" t="n"/>
       <c r="Z7" s="84" t="n"/>
@@ -1891,21 +1977,21 @@
           <t>○</t>
         </is>
       </c>
-      <c r="I8" s="108" t="n"/>
-      <c r="J8" s="108" t="n"/>
-      <c r="K8" s="108" t="n"/>
-      <c r="L8" s="108" t="n"/>
-      <c r="M8" s="108" t="n"/>
-      <c r="N8" s="108" t="n"/>
-      <c r="O8" s="108" t="n"/>
-      <c r="P8" s="108" t="n"/>
-      <c r="Q8" s="108" t="n"/>
-      <c r="R8" s="108" t="n"/>
-      <c r="S8" s="108" t="n"/>
-      <c r="T8" s="108" t="n"/>
-      <c r="U8" s="108" t="n"/>
-      <c r="V8" s="108" t="n"/>
-      <c r="W8" s="108" t="n"/>
+      <c r="I8" s="179" t="n"/>
+      <c r="J8" s="179" t="n"/>
+      <c r="K8" s="179" t="n"/>
+      <c r="L8" s="179" t="n"/>
+      <c r="M8" s="179" t="n"/>
+      <c r="N8" s="179" t="n"/>
+      <c r="O8" s="179" t="n"/>
+      <c r="P8" s="179" t="n"/>
+      <c r="Q8" s="179" t="n"/>
+      <c r="R8" s="179" t="n"/>
+      <c r="S8" s="179" t="n"/>
+      <c r="T8" s="179" t="n"/>
+      <c r="U8" s="179" t="n"/>
+      <c r="V8" s="179" t="n"/>
+      <c r="W8" s="179" t="n"/>
       <c r="X8" s="84" t="n"/>
       <c r="Y8" s="84" t="n"/>
       <c r="Z8" s="84" t="n"/>
@@ -1953,21 +2039,21 @@
           <t>○</t>
         </is>
       </c>
-      <c r="I9" s="108" t="n"/>
-      <c r="J9" s="108" t="n"/>
-      <c r="K9" s="108" t="n"/>
-      <c r="L9" s="108" t="n"/>
-      <c r="M9" s="108" t="n"/>
-      <c r="N9" s="108" t="n"/>
-      <c r="O9" s="108" t="n"/>
-      <c r="P9" s="108" t="n"/>
-      <c r="Q9" s="108" t="n"/>
-      <c r="R9" s="108" t="n"/>
-      <c r="S9" s="108" t="n"/>
-      <c r="T9" s="108" t="n"/>
-      <c r="U9" s="108" t="n"/>
-      <c r="V9" s="108" t="n"/>
-      <c r="W9" s="108" t="n"/>
+      <c r="I9" s="179" t="n"/>
+      <c r="J9" s="179" t="n"/>
+      <c r="K9" s="179" t="n"/>
+      <c r="L9" s="179" t="n"/>
+      <c r="M9" s="179" t="n"/>
+      <c r="N9" s="179" t="n"/>
+      <c r="O9" s="179" t="n"/>
+      <c r="P9" s="179" t="n"/>
+      <c r="Q9" s="179" t="n"/>
+      <c r="R9" s="179" t="n"/>
+      <c r="S9" s="179" t="n"/>
+      <c r="T9" s="179" t="n"/>
+      <c r="U9" s="179" t="n"/>
+      <c r="V9" s="179" t="n"/>
+      <c r="W9" s="179" t="n"/>
       <c r="X9" s="84" t="n"/>
       <c r="Y9" s="84" t="n"/>
       <c r="Z9" s="84" t="n"/>
@@ -2005,27 +2091,27 @@
           <t>production/staging 両フロント統合</t>
         </is>
       </c>
-      <c r="G10" s="108" t="n"/>
+      <c r="G10" s="179" t="n"/>
       <c r="H10" s="107" t="inlineStr">
         <is>
           <t>○</t>
         </is>
       </c>
-      <c r="I10" s="108" t="n"/>
-      <c r="J10" s="108" t="n"/>
-      <c r="K10" s="108" t="n"/>
-      <c r="L10" s="108" t="n"/>
-      <c r="M10" s="108" t="n"/>
-      <c r="N10" s="108" t="n"/>
-      <c r="O10" s="108" t="n"/>
-      <c r="P10" s="108" t="n"/>
-      <c r="Q10" s="108" t="n"/>
-      <c r="R10" s="108" t="n"/>
-      <c r="S10" s="108" t="n"/>
-      <c r="T10" s="108" t="n"/>
-      <c r="U10" s="108" t="n"/>
-      <c r="V10" s="108" t="n"/>
-      <c r="W10" s="108" t="n"/>
+      <c r="I10" s="179" t="n"/>
+      <c r="J10" s="179" t="n"/>
+      <c r="K10" s="179" t="n"/>
+      <c r="L10" s="179" t="n"/>
+      <c r="M10" s="179" t="n"/>
+      <c r="N10" s="179" t="n"/>
+      <c r="O10" s="179" t="n"/>
+      <c r="P10" s="179" t="n"/>
+      <c r="Q10" s="179" t="n"/>
+      <c r="R10" s="179" t="n"/>
+      <c r="S10" s="179" t="n"/>
+      <c r="T10" s="179" t="n"/>
+      <c r="U10" s="179" t="n"/>
+      <c r="V10" s="179" t="n"/>
+      <c r="W10" s="179" t="n"/>
       <c r="X10" s="84" t="n"/>
       <c r="Y10" s="84" t="n"/>
       <c r="Z10" s="84" t="n"/>
@@ -2075,27 +2161,27 @@
         </is>
       </c>
       <c r="F12" s="106" t="inlineStr"/>
-      <c r="G12" s="108" t="n"/>
+      <c r="G12" s="179" t="n"/>
       <c r="H12" s="107" t="inlineStr">
         <is>
           <t>○</t>
         </is>
       </c>
-      <c r="I12" s="108" t="n"/>
-      <c r="J12" s="108" t="n"/>
-      <c r="K12" s="108" t="n"/>
-      <c r="L12" s="108" t="n"/>
-      <c r="M12" s="108" t="n"/>
-      <c r="N12" s="108" t="n"/>
-      <c r="O12" s="108" t="n"/>
-      <c r="P12" s="108" t="n"/>
-      <c r="Q12" s="108" t="n"/>
-      <c r="R12" s="108" t="n"/>
-      <c r="S12" s="108" t="n"/>
-      <c r="T12" s="108" t="n"/>
-      <c r="U12" s="108" t="n"/>
-      <c r="V12" s="108" t="n"/>
-      <c r="W12" s="108" t="n"/>
+      <c r="I12" s="179" t="n"/>
+      <c r="J12" s="179" t="n"/>
+      <c r="K12" s="179" t="n"/>
+      <c r="L12" s="179" t="n"/>
+      <c r="M12" s="179" t="n"/>
+      <c r="N12" s="179" t="n"/>
+      <c r="O12" s="179" t="n"/>
+      <c r="P12" s="179" t="n"/>
+      <c r="Q12" s="179" t="n"/>
+      <c r="R12" s="179" t="n"/>
+      <c r="S12" s="179" t="n"/>
+      <c r="T12" s="179" t="n"/>
+      <c r="U12" s="179" t="n"/>
+      <c r="V12" s="179" t="n"/>
+      <c r="W12" s="179" t="n"/>
       <c r="X12" s="84" t="n"/>
       <c r="Y12" s="84" t="n"/>
       <c r="Z12" s="84" t="n"/>
@@ -2133,27 +2219,27 @@
           <t>.github/workflows/ci.yml</t>
         </is>
       </c>
-      <c r="G13" s="108" t="n"/>
+      <c r="G13" s="179" t="n"/>
       <c r="H13" s="107" t="inlineStr">
         <is>
           <t>○</t>
         </is>
       </c>
-      <c r="I13" s="108" t="n"/>
-      <c r="J13" s="108" t="n"/>
-      <c r="K13" s="108" t="n"/>
-      <c r="L13" s="108" t="n"/>
-      <c r="M13" s="108" t="n"/>
-      <c r="N13" s="108" t="n"/>
-      <c r="O13" s="108" t="n"/>
-      <c r="P13" s="108" t="n"/>
-      <c r="Q13" s="108" t="n"/>
-      <c r="R13" s="108" t="n"/>
-      <c r="S13" s="108" t="n"/>
-      <c r="T13" s="108" t="n"/>
-      <c r="U13" s="108" t="n"/>
-      <c r="V13" s="108" t="n"/>
-      <c r="W13" s="108" t="n"/>
+      <c r="I13" s="179" t="n"/>
+      <c r="J13" s="179" t="n"/>
+      <c r="K13" s="179" t="n"/>
+      <c r="L13" s="179" t="n"/>
+      <c r="M13" s="179" t="n"/>
+      <c r="N13" s="179" t="n"/>
+      <c r="O13" s="179" t="n"/>
+      <c r="P13" s="179" t="n"/>
+      <c r="Q13" s="179" t="n"/>
+      <c r="R13" s="179" t="n"/>
+      <c r="S13" s="179" t="n"/>
+      <c r="T13" s="179" t="n"/>
+      <c r="U13" s="179" t="n"/>
+      <c r="V13" s="179" t="n"/>
+      <c r="W13" s="179" t="n"/>
       <c r="X13" s="84" t="n"/>
       <c r="Y13" s="84" t="n"/>
       <c r="Z13" s="84" t="n"/>
@@ -2191,27 +2277,27 @@
           <t>STG環境で確認</t>
         </is>
       </c>
-      <c r="G14" s="108" t="n"/>
-      <c r="H14" s="108" t="n"/>
+      <c r="G14" s="179" t="n"/>
+      <c r="H14" s="179" t="n"/>
       <c r="I14" s="107" t="inlineStr">
         <is>
           <t>○</t>
         </is>
       </c>
-      <c r="J14" s="108" t="n"/>
-      <c r="K14" s="108" t="n"/>
-      <c r="L14" s="108" t="n"/>
-      <c r="M14" s="108" t="n"/>
-      <c r="N14" s="108" t="n"/>
-      <c r="O14" s="108" t="n"/>
-      <c r="P14" s="108" t="n"/>
-      <c r="Q14" s="108" t="n"/>
-      <c r="R14" s="108" t="n"/>
-      <c r="S14" s="108" t="n"/>
-      <c r="T14" s="108" t="n"/>
-      <c r="U14" s="108" t="n"/>
-      <c r="V14" s="108" t="n"/>
-      <c r="W14" s="108" t="n"/>
+      <c r="J14" s="179" t="n"/>
+      <c r="K14" s="179" t="n"/>
+      <c r="L14" s="179" t="n"/>
+      <c r="M14" s="179" t="n"/>
+      <c r="N14" s="179" t="n"/>
+      <c r="O14" s="179" t="n"/>
+      <c r="P14" s="179" t="n"/>
+      <c r="Q14" s="179" t="n"/>
+      <c r="R14" s="179" t="n"/>
+      <c r="S14" s="179" t="n"/>
+      <c r="T14" s="179" t="n"/>
+      <c r="U14" s="179" t="n"/>
+      <c r="V14" s="179" t="n"/>
+      <c r="W14" s="179" t="n"/>
       <c r="X14" s="84" t="n"/>
       <c r="Y14" s="84" t="n"/>
       <c r="Z14" s="84" t="n"/>
@@ -2249,27 +2335,27 @@
           <t>GitHub: Archive設定</t>
         </is>
       </c>
-      <c r="G15" s="108" t="n"/>
-      <c r="H15" s="108" t="n"/>
+      <c r="G15" s="179" t="n"/>
+      <c r="H15" s="179" t="n"/>
       <c r="I15" s="107" t="inlineStr">
         <is>
           <t>○</t>
         </is>
       </c>
-      <c r="J15" s="108" t="n"/>
-      <c r="K15" s="108" t="n"/>
-      <c r="L15" s="108" t="n"/>
-      <c r="M15" s="108" t="n"/>
-      <c r="N15" s="108" t="n"/>
-      <c r="O15" s="108" t="n"/>
-      <c r="P15" s="108" t="n"/>
-      <c r="Q15" s="108" t="n"/>
-      <c r="R15" s="108" t="n"/>
-      <c r="S15" s="108" t="n"/>
-      <c r="T15" s="108" t="n"/>
-      <c r="U15" s="108" t="n"/>
-      <c r="V15" s="108" t="n"/>
-      <c r="W15" s="108" t="n"/>
+      <c r="J15" s="179" t="n"/>
+      <c r="K15" s="179" t="n"/>
+      <c r="L15" s="179" t="n"/>
+      <c r="M15" s="179" t="n"/>
+      <c r="N15" s="179" t="n"/>
+      <c r="O15" s="179" t="n"/>
+      <c r="P15" s="179" t="n"/>
+      <c r="Q15" s="179" t="n"/>
+      <c r="R15" s="179" t="n"/>
+      <c r="S15" s="179" t="n"/>
+      <c r="T15" s="179" t="n"/>
+      <c r="U15" s="179" t="n"/>
+      <c r="V15" s="179" t="n"/>
+      <c r="W15" s="179" t="n"/>
       <c r="X15" s="84" t="n"/>
       <c r="Y15" s="84" t="n"/>
       <c r="Z15" s="84" t="n"/>
@@ -2344,22 +2430,22 @@
           <t>○</t>
         </is>
       </c>
-      <c r="H18" s="108" t="n"/>
-      <c r="I18" s="108" t="n"/>
-      <c r="J18" s="108" t="n"/>
-      <c r="K18" s="108" t="n"/>
-      <c r="L18" s="108" t="n"/>
-      <c r="M18" s="108" t="n"/>
-      <c r="N18" s="108" t="n"/>
-      <c r="O18" s="108" t="n"/>
-      <c r="P18" s="108" t="n"/>
-      <c r="Q18" s="108" t="n"/>
-      <c r="R18" s="108" t="n"/>
-      <c r="S18" s="108" t="n"/>
-      <c r="T18" s="108" t="n"/>
-      <c r="U18" s="108" t="n"/>
-      <c r="V18" s="108" t="n"/>
-      <c r="W18" s="108" t="n"/>
+      <c r="H18" s="179" t="n"/>
+      <c r="I18" s="179" t="n"/>
+      <c r="J18" s="179" t="n"/>
+      <c r="K18" s="179" t="n"/>
+      <c r="L18" s="179" t="n"/>
+      <c r="M18" s="179" t="n"/>
+      <c r="N18" s="179" t="n"/>
+      <c r="O18" s="179" t="n"/>
+      <c r="P18" s="179" t="n"/>
+      <c r="Q18" s="179" t="n"/>
+      <c r="R18" s="179" t="n"/>
+      <c r="S18" s="179" t="n"/>
+      <c r="T18" s="179" t="n"/>
+      <c r="U18" s="179" t="n"/>
+      <c r="V18" s="179" t="n"/>
+      <c r="W18" s="179" t="n"/>
       <c r="X18" s="84" t="n"/>
       <c r="Y18" s="84" t="n"/>
       <c r="Z18" s="84" t="n"/>
@@ -2402,22 +2488,22 @@
           <t>○</t>
         </is>
       </c>
-      <c r="H19" s="108" t="n"/>
-      <c r="I19" s="108" t="n"/>
-      <c r="J19" s="108" t="n"/>
-      <c r="K19" s="108" t="n"/>
-      <c r="L19" s="108" t="n"/>
-      <c r="M19" s="108" t="n"/>
-      <c r="N19" s="108" t="n"/>
-      <c r="O19" s="108" t="n"/>
-      <c r="P19" s="108" t="n"/>
-      <c r="Q19" s="108" t="n"/>
-      <c r="R19" s="108" t="n"/>
-      <c r="S19" s="108" t="n"/>
-      <c r="T19" s="108" t="n"/>
-      <c r="U19" s="108" t="n"/>
-      <c r="V19" s="108" t="n"/>
-      <c r="W19" s="108" t="n"/>
+      <c r="H19" s="179" t="n"/>
+      <c r="I19" s="179" t="n"/>
+      <c r="J19" s="179" t="n"/>
+      <c r="K19" s="179" t="n"/>
+      <c r="L19" s="179" t="n"/>
+      <c r="M19" s="179" t="n"/>
+      <c r="N19" s="179" t="n"/>
+      <c r="O19" s="179" t="n"/>
+      <c r="P19" s="179" t="n"/>
+      <c r="Q19" s="179" t="n"/>
+      <c r="R19" s="179" t="n"/>
+      <c r="S19" s="179" t="n"/>
+      <c r="T19" s="179" t="n"/>
+      <c r="U19" s="179" t="n"/>
+      <c r="V19" s="179" t="n"/>
+      <c r="W19" s="179" t="n"/>
       <c r="X19" s="84" t="n"/>
       <c r="Y19" s="84" t="n"/>
       <c r="Z19" s="84" t="n"/>
@@ -2467,7 +2553,7 @@
         </is>
       </c>
       <c r="F21" s="106" t="inlineStr"/>
-      <c r="G21" s="108" t="n"/>
+      <c r="G21" s="179" t="n"/>
       <c r="H21" s="114" t="inlineStr">
         <is>
           <t>○</t>
@@ -2478,20 +2564,20 @@
           <t>○</t>
         </is>
       </c>
-      <c r="J21" s="108" t="n"/>
-      <c r="K21" s="108" t="n"/>
-      <c r="L21" s="108" t="n"/>
-      <c r="M21" s="108" t="n"/>
-      <c r="N21" s="108" t="n"/>
-      <c r="O21" s="108" t="n"/>
-      <c r="P21" s="108" t="n"/>
-      <c r="Q21" s="108" t="n"/>
-      <c r="R21" s="108" t="n"/>
-      <c r="S21" s="108" t="n"/>
-      <c r="T21" s="108" t="n"/>
-      <c r="U21" s="108" t="n"/>
-      <c r="V21" s="108" t="n"/>
-      <c r="W21" s="108" t="n"/>
+      <c r="J21" s="179" t="n"/>
+      <c r="K21" s="179" t="n"/>
+      <c r="L21" s="179" t="n"/>
+      <c r="M21" s="179" t="n"/>
+      <c r="N21" s="179" t="n"/>
+      <c r="O21" s="179" t="n"/>
+      <c r="P21" s="179" t="n"/>
+      <c r="Q21" s="179" t="n"/>
+      <c r="R21" s="179" t="n"/>
+      <c r="S21" s="179" t="n"/>
+      <c r="T21" s="179" t="n"/>
+      <c r="U21" s="179" t="n"/>
+      <c r="V21" s="179" t="n"/>
+      <c r="W21" s="179" t="n"/>
       <c r="X21" s="84" t="n"/>
       <c r="Y21" s="84" t="n"/>
       <c r="Z21" s="84" t="n"/>
@@ -2525,7 +2611,7 @@
         </is>
       </c>
       <c r="F22" s="106" t="inlineStr"/>
-      <c r="G22" s="108" t="n"/>
+      <c r="G22" s="179" t="n"/>
       <c r="H22" s="114" t="inlineStr">
         <is>
           <t>○</t>
@@ -2536,20 +2622,20 @@
           <t>○</t>
         </is>
       </c>
-      <c r="J22" s="108" t="n"/>
-      <c r="K22" s="108" t="n"/>
-      <c r="L22" s="108" t="n"/>
-      <c r="M22" s="108" t="n"/>
-      <c r="N22" s="108" t="n"/>
-      <c r="O22" s="108" t="n"/>
-      <c r="P22" s="108" t="n"/>
-      <c r="Q22" s="108" t="n"/>
-      <c r="R22" s="108" t="n"/>
-      <c r="S22" s="108" t="n"/>
-      <c r="T22" s="108" t="n"/>
-      <c r="U22" s="108" t="n"/>
-      <c r="V22" s="108" t="n"/>
-      <c r="W22" s="108" t="n"/>
+      <c r="J22" s="179" t="n"/>
+      <c r="K22" s="179" t="n"/>
+      <c r="L22" s="179" t="n"/>
+      <c r="M22" s="179" t="n"/>
+      <c r="N22" s="179" t="n"/>
+      <c r="O22" s="179" t="n"/>
+      <c r="P22" s="179" t="n"/>
+      <c r="Q22" s="179" t="n"/>
+      <c r="R22" s="179" t="n"/>
+      <c r="S22" s="179" t="n"/>
+      <c r="T22" s="179" t="n"/>
+      <c r="U22" s="179" t="n"/>
+      <c r="V22" s="179" t="n"/>
+      <c r="W22" s="179" t="n"/>
       <c r="X22" s="84" t="n"/>
       <c r="Y22" s="84" t="n"/>
       <c r="Z22" s="84" t="n"/>
@@ -2583,7 +2669,7 @@
         </is>
       </c>
       <c r="F23" s="106" t="inlineStr"/>
-      <c r="G23" s="108" t="n"/>
+      <c r="G23" s="179" t="n"/>
       <c r="H23" s="114" t="inlineStr">
         <is>
           <t>○</t>
@@ -2594,20 +2680,20 @@
           <t>○</t>
         </is>
       </c>
-      <c r="J23" s="108" t="n"/>
-      <c r="K23" s="108" t="n"/>
-      <c r="L23" s="108" t="n"/>
-      <c r="M23" s="108" t="n"/>
-      <c r="N23" s="108" t="n"/>
-      <c r="O23" s="108" t="n"/>
-      <c r="P23" s="108" t="n"/>
-      <c r="Q23" s="108" t="n"/>
-      <c r="R23" s="108" t="n"/>
-      <c r="S23" s="108" t="n"/>
-      <c r="T23" s="108" t="n"/>
-      <c r="U23" s="108" t="n"/>
-      <c r="V23" s="108" t="n"/>
-      <c r="W23" s="108" t="n"/>
+      <c r="J23" s="179" t="n"/>
+      <c r="K23" s="179" t="n"/>
+      <c r="L23" s="179" t="n"/>
+      <c r="M23" s="179" t="n"/>
+      <c r="N23" s="179" t="n"/>
+      <c r="O23" s="179" t="n"/>
+      <c r="P23" s="179" t="n"/>
+      <c r="Q23" s="179" t="n"/>
+      <c r="R23" s="179" t="n"/>
+      <c r="S23" s="179" t="n"/>
+      <c r="T23" s="179" t="n"/>
+      <c r="U23" s="179" t="n"/>
+      <c r="V23" s="179" t="n"/>
+      <c r="W23" s="179" t="n"/>
       <c r="X23" s="84" t="n"/>
       <c r="Y23" s="84" t="n"/>
       <c r="Z23" s="84" t="n"/>
@@ -2657,8 +2743,8 @@
         </is>
       </c>
       <c r="F25" s="106" t="inlineStr"/>
-      <c r="G25" s="108" t="n"/>
-      <c r="H25" s="108" t="n"/>
+      <c r="G25" s="179" t="n"/>
+      <c r="H25" s="179" t="n"/>
       <c r="I25" s="114" t="inlineStr">
         <is>
           <t>○</t>
@@ -2669,19 +2755,19 @@
           <t>○</t>
         </is>
       </c>
-      <c r="K25" s="108" t="n"/>
-      <c r="L25" s="108" t="n"/>
-      <c r="M25" s="108" t="n"/>
-      <c r="N25" s="108" t="n"/>
-      <c r="O25" s="108" t="n"/>
-      <c r="P25" s="108" t="n"/>
-      <c r="Q25" s="108" t="n"/>
-      <c r="R25" s="108" t="n"/>
-      <c r="S25" s="108" t="n"/>
-      <c r="T25" s="108" t="n"/>
-      <c r="U25" s="108" t="n"/>
-      <c r="V25" s="108" t="n"/>
-      <c r="W25" s="108" t="n"/>
+      <c r="K25" s="179" t="n"/>
+      <c r="L25" s="179" t="n"/>
+      <c r="M25" s="179" t="n"/>
+      <c r="N25" s="179" t="n"/>
+      <c r="O25" s="179" t="n"/>
+      <c r="P25" s="179" t="n"/>
+      <c r="Q25" s="179" t="n"/>
+      <c r="R25" s="179" t="n"/>
+      <c r="S25" s="179" t="n"/>
+      <c r="T25" s="179" t="n"/>
+      <c r="U25" s="179" t="n"/>
+      <c r="V25" s="179" t="n"/>
+      <c r="W25" s="179" t="n"/>
       <c r="X25" s="84" t="n"/>
       <c r="Y25" s="84" t="n"/>
       <c r="Z25" s="84" t="n"/>
@@ -2715,9 +2801,9 @@
         </is>
       </c>
       <c r="F26" s="106" t="inlineStr"/>
-      <c r="G26" s="108" t="n"/>
-      <c r="H26" s="108" t="n"/>
-      <c r="I26" s="108" t="n"/>
+      <c r="G26" s="179" t="n"/>
+      <c r="H26" s="179" t="n"/>
+      <c r="I26" s="179" t="n"/>
       <c r="J26" s="114" t="inlineStr">
         <is>
           <t>○</t>
@@ -2728,18 +2814,18 @@
           <t>○</t>
         </is>
       </c>
-      <c r="L26" s="108" t="n"/>
-      <c r="M26" s="108" t="n"/>
-      <c r="N26" s="108" t="n"/>
-      <c r="O26" s="108" t="n"/>
-      <c r="P26" s="108" t="n"/>
-      <c r="Q26" s="108" t="n"/>
-      <c r="R26" s="108" t="n"/>
-      <c r="S26" s="108" t="n"/>
-      <c r="T26" s="108" t="n"/>
-      <c r="U26" s="108" t="n"/>
-      <c r="V26" s="108" t="n"/>
-      <c r="W26" s="108" t="n"/>
+      <c r="L26" s="179" t="n"/>
+      <c r="M26" s="179" t="n"/>
+      <c r="N26" s="179" t="n"/>
+      <c r="O26" s="179" t="n"/>
+      <c r="P26" s="179" t="n"/>
+      <c r="Q26" s="179" t="n"/>
+      <c r="R26" s="179" t="n"/>
+      <c r="S26" s="179" t="n"/>
+      <c r="T26" s="179" t="n"/>
+      <c r="U26" s="179" t="n"/>
+      <c r="V26" s="179" t="n"/>
+      <c r="W26" s="179" t="n"/>
       <c r="X26" s="84" t="n"/>
       <c r="Y26" s="84" t="n"/>
       <c r="Z26" s="84" t="n"/>
@@ -2773,9 +2859,9 @@
         </is>
       </c>
       <c r="F27" s="106" t="inlineStr"/>
-      <c r="G27" s="108" t="n"/>
-      <c r="H27" s="108" t="n"/>
-      <c r="I27" s="108" t="n"/>
+      <c r="G27" s="179" t="n"/>
+      <c r="H27" s="179" t="n"/>
+      <c r="I27" s="179" t="n"/>
       <c r="J27" s="114" t="inlineStr">
         <is>
           <t>○</t>
@@ -2786,18 +2872,18 @@
           <t>○</t>
         </is>
       </c>
-      <c r="L27" s="108" t="n"/>
-      <c r="M27" s="108" t="n"/>
-      <c r="N27" s="108" t="n"/>
-      <c r="O27" s="108" t="n"/>
-      <c r="P27" s="108" t="n"/>
-      <c r="Q27" s="108" t="n"/>
-      <c r="R27" s="108" t="n"/>
-      <c r="S27" s="108" t="n"/>
-      <c r="T27" s="108" t="n"/>
-      <c r="U27" s="108" t="n"/>
-      <c r="V27" s="108" t="n"/>
-      <c r="W27" s="108" t="n"/>
+      <c r="L27" s="179" t="n"/>
+      <c r="M27" s="179" t="n"/>
+      <c r="N27" s="179" t="n"/>
+      <c r="O27" s="179" t="n"/>
+      <c r="P27" s="179" t="n"/>
+      <c r="Q27" s="179" t="n"/>
+      <c r="R27" s="179" t="n"/>
+      <c r="S27" s="179" t="n"/>
+      <c r="T27" s="179" t="n"/>
+      <c r="U27" s="179" t="n"/>
+      <c r="V27" s="179" t="n"/>
+      <c r="W27" s="179" t="n"/>
       <c r="X27" s="84" t="n"/>
       <c r="Y27" s="84" t="n"/>
       <c r="Z27" s="84" t="n"/>
@@ -2831,9 +2917,9 @@
         </is>
       </c>
       <c r="F28" s="106" t="inlineStr"/>
-      <c r="G28" s="108" t="n"/>
-      <c r="H28" s="108" t="n"/>
-      <c r="I28" s="108" t="n"/>
+      <c r="G28" s="179" t="n"/>
+      <c r="H28" s="179" t="n"/>
+      <c r="I28" s="179" t="n"/>
       <c r="J28" s="114" t="inlineStr">
         <is>
           <t>○</t>
@@ -2844,18 +2930,18 @@
           <t>○</t>
         </is>
       </c>
-      <c r="L28" s="108" t="n"/>
-      <c r="M28" s="108" t="n"/>
-      <c r="N28" s="108" t="n"/>
-      <c r="O28" s="108" t="n"/>
-      <c r="P28" s="108" t="n"/>
-      <c r="Q28" s="108" t="n"/>
-      <c r="R28" s="108" t="n"/>
-      <c r="S28" s="108" t="n"/>
-      <c r="T28" s="108" t="n"/>
-      <c r="U28" s="108" t="n"/>
-      <c r="V28" s="108" t="n"/>
-      <c r="W28" s="108" t="n"/>
+      <c r="L28" s="179" t="n"/>
+      <c r="M28" s="179" t="n"/>
+      <c r="N28" s="179" t="n"/>
+      <c r="O28" s="179" t="n"/>
+      <c r="P28" s="179" t="n"/>
+      <c r="Q28" s="179" t="n"/>
+      <c r="R28" s="179" t="n"/>
+      <c r="S28" s="179" t="n"/>
+      <c r="T28" s="179" t="n"/>
+      <c r="U28" s="179" t="n"/>
+      <c r="V28" s="179" t="n"/>
+      <c r="W28" s="179" t="n"/>
       <c r="X28" s="84" t="n"/>
       <c r="Y28" s="84" t="n"/>
       <c r="Z28" s="84" t="n"/>
@@ -2889,9 +2975,9 @@
         </is>
       </c>
       <c r="F29" s="106" t="inlineStr"/>
-      <c r="G29" s="108" t="n"/>
-      <c r="H29" s="108" t="n"/>
-      <c r="I29" s="108" t="n"/>
+      <c r="G29" s="179" t="n"/>
+      <c r="H29" s="179" t="n"/>
+      <c r="I29" s="179" t="n"/>
       <c r="J29" s="114" t="inlineStr">
         <is>
           <t>○</t>
@@ -2902,18 +2988,18 @@
           <t>○</t>
         </is>
       </c>
-      <c r="L29" s="108" t="n"/>
-      <c r="M29" s="108" t="n"/>
-      <c r="N29" s="108" t="n"/>
-      <c r="O29" s="108" t="n"/>
-      <c r="P29" s="108" t="n"/>
-      <c r="Q29" s="108" t="n"/>
-      <c r="R29" s="108" t="n"/>
-      <c r="S29" s="108" t="n"/>
-      <c r="T29" s="108" t="n"/>
-      <c r="U29" s="108" t="n"/>
-      <c r="V29" s="108" t="n"/>
-      <c r="W29" s="108" t="n"/>
+      <c r="L29" s="179" t="n"/>
+      <c r="M29" s="179" t="n"/>
+      <c r="N29" s="179" t="n"/>
+      <c r="O29" s="179" t="n"/>
+      <c r="P29" s="179" t="n"/>
+      <c r="Q29" s="179" t="n"/>
+      <c r="R29" s="179" t="n"/>
+      <c r="S29" s="179" t="n"/>
+      <c r="T29" s="179" t="n"/>
+      <c r="U29" s="179" t="n"/>
+      <c r="V29" s="179" t="n"/>
+      <c r="W29" s="179" t="n"/>
       <c r="X29" s="84" t="n"/>
       <c r="Y29" s="84" t="n"/>
       <c r="Z29" s="84" t="n"/>
@@ -2963,14 +3049,14 @@
         </is>
       </c>
       <c r="F31" s="106" t="inlineStr"/>
-      <c r="G31" s="108" t="n"/>
-      <c r="H31" s="108" t="n"/>
-      <c r="I31" s="108" t="n"/>
-      <c r="J31" s="108" t="n"/>
-      <c r="K31" s="108" t="n"/>
-      <c r="L31" s="108" t="n"/>
-      <c r="M31" s="108" t="n"/>
-      <c r="N31" s="108" t="n"/>
+      <c r="G31" s="179" t="n"/>
+      <c r="H31" s="179" t="n"/>
+      <c r="I31" s="179" t="n"/>
+      <c r="J31" s="179" t="n"/>
+      <c r="K31" s="179" t="n"/>
+      <c r="L31" s="179" t="n"/>
+      <c r="M31" s="179" t="n"/>
+      <c r="N31" s="179" t="n"/>
       <c r="O31" s="114" t="inlineStr">
         <is>
           <t>○</t>
@@ -2981,13 +3067,13 @@
           <t>○</t>
         </is>
       </c>
-      <c r="Q31" s="108" t="n"/>
-      <c r="R31" s="108" t="n"/>
-      <c r="S31" s="108" t="n"/>
-      <c r="T31" s="108" t="n"/>
-      <c r="U31" s="108" t="n"/>
-      <c r="V31" s="108" t="n"/>
-      <c r="W31" s="108" t="n"/>
+      <c r="Q31" s="179" t="n"/>
+      <c r="R31" s="179" t="n"/>
+      <c r="S31" s="179" t="n"/>
+      <c r="T31" s="179" t="n"/>
+      <c r="U31" s="179" t="n"/>
+      <c r="V31" s="179" t="n"/>
+      <c r="W31" s="179" t="n"/>
       <c r="X31" s="84" t="n"/>
       <c r="Y31" s="84" t="n"/>
       <c r="Z31" s="84" t="n"/>
@@ -3021,14 +3107,14 @@
         </is>
       </c>
       <c r="F32" s="106" t="inlineStr"/>
-      <c r="G32" s="108" t="n"/>
-      <c r="H32" s="108" t="n"/>
-      <c r="I32" s="108" t="n"/>
-      <c r="J32" s="108" t="n"/>
-      <c r="K32" s="108" t="n"/>
-      <c r="L32" s="108" t="n"/>
-      <c r="M32" s="108" t="n"/>
-      <c r="N32" s="108" t="n"/>
+      <c r="G32" s="179" t="n"/>
+      <c r="H32" s="179" t="n"/>
+      <c r="I32" s="179" t="n"/>
+      <c r="J32" s="179" t="n"/>
+      <c r="K32" s="179" t="n"/>
+      <c r="L32" s="179" t="n"/>
+      <c r="M32" s="179" t="n"/>
+      <c r="N32" s="179" t="n"/>
       <c r="O32" s="114" t="inlineStr">
         <is>
           <t>○</t>
@@ -3039,13 +3125,13 @@
           <t>○</t>
         </is>
       </c>
-      <c r="Q32" s="108" t="n"/>
-      <c r="R32" s="108" t="n"/>
-      <c r="S32" s="108" t="n"/>
-      <c r="T32" s="108" t="n"/>
-      <c r="U32" s="108" t="n"/>
-      <c r="V32" s="108" t="n"/>
-      <c r="W32" s="108" t="n"/>
+      <c r="Q32" s="179" t="n"/>
+      <c r="R32" s="179" t="n"/>
+      <c r="S32" s="179" t="n"/>
+      <c r="T32" s="179" t="n"/>
+      <c r="U32" s="179" t="n"/>
+      <c r="V32" s="179" t="n"/>
+      <c r="W32" s="179" t="n"/>
       <c r="X32" s="84" t="n"/>
       <c r="Y32" s="84" t="n"/>
       <c r="Z32" s="84" t="n"/>
@@ -3079,16 +3165,16 @@
         </is>
       </c>
       <c r="F33" s="106" t="inlineStr"/>
-      <c r="G33" s="108" t="n"/>
-      <c r="H33" s="108" t="n"/>
-      <c r="I33" s="108" t="n"/>
-      <c r="J33" s="108" t="n"/>
-      <c r="K33" s="108" t="n"/>
-      <c r="L33" s="108" t="n"/>
-      <c r="M33" s="108" t="n"/>
-      <c r="N33" s="108" t="n"/>
-      <c r="O33" s="108" t="n"/>
-      <c r="P33" s="108" t="n"/>
+      <c r="G33" s="179" t="n"/>
+      <c r="H33" s="179" t="n"/>
+      <c r="I33" s="179" t="n"/>
+      <c r="J33" s="179" t="n"/>
+      <c r="K33" s="179" t="n"/>
+      <c r="L33" s="179" t="n"/>
+      <c r="M33" s="179" t="n"/>
+      <c r="N33" s="179" t="n"/>
+      <c r="O33" s="179" t="n"/>
+      <c r="P33" s="179" t="n"/>
       <c r="Q33" s="114" t="inlineStr">
         <is>
           <t>○</t>
@@ -3099,11 +3185,11 @@
           <t>○</t>
         </is>
       </c>
-      <c r="S33" s="108" t="n"/>
-      <c r="T33" s="108" t="n"/>
-      <c r="U33" s="108" t="n"/>
-      <c r="V33" s="108" t="n"/>
-      <c r="W33" s="108" t="n"/>
+      <c r="S33" s="179" t="n"/>
+      <c r="T33" s="179" t="n"/>
+      <c r="U33" s="179" t="n"/>
+      <c r="V33" s="179" t="n"/>
+      <c r="W33" s="179" t="n"/>
       <c r="X33" s="84" t="n"/>
       <c r="Y33" s="84" t="n"/>
       <c r="Z33" s="84" t="n"/>
@@ -3137,16 +3223,16 @@
         </is>
       </c>
       <c r="F34" s="106" t="inlineStr"/>
-      <c r="G34" s="108" t="n"/>
-      <c r="H34" s="108" t="n"/>
-      <c r="I34" s="108" t="n"/>
-      <c r="J34" s="108" t="n"/>
-      <c r="K34" s="108" t="n"/>
-      <c r="L34" s="108" t="n"/>
-      <c r="M34" s="108" t="n"/>
-      <c r="N34" s="108" t="n"/>
-      <c r="O34" s="108" t="n"/>
-      <c r="P34" s="108" t="n"/>
+      <c r="G34" s="179" t="n"/>
+      <c r="H34" s="179" t="n"/>
+      <c r="I34" s="179" t="n"/>
+      <c r="J34" s="179" t="n"/>
+      <c r="K34" s="179" t="n"/>
+      <c r="L34" s="179" t="n"/>
+      <c r="M34" s="179" t="n"/>
+      <c r="N34" s="179" t="n"/>
+      <c r="O34" s="179" t="n"/>
+      <c r="P34" s="179" t="n"/>
       <c r="Q34" s="114" t="inlineStr">
         <is>
           <t>○</t>
@@ -3157,11 +3243,11 @@
           <t>○</t>
         </is>
       </c>
-      <c r="S34" s="108" t="n"/>
-      <c r="T34" s="108" t="n"/>
-      <c r="U34" s="108" t="n"/>
-      <c r="V34" s="108" t="n"/>
-      <c r="W34" s="108" t="n"/>
+      <c r="S34" s="179" t="n"/>
+      <c r="T34" s="179" t="n"/>
+      <c r="U34" s="179" t="n"/>
+      <c r="V34" s="179" t="n"/>
+      <c r="W34" s="179" t="n"/>
       <c r="X34" s="84" t="n"/>
       <c r="Y34" s="84" t="n"/>
       <c r="Z34" s="84" t="n"/>
@@ -3195,18 +3281,18 @@
         </is>
       </c>
       <c r="F35" s="106" t="inlineStr"/>
-      <c r="G35" s="108" t="n"/>
-      <c r="H35" s="108" t="n"/>
-      <c r="I35" s="108" t="n"/>
-      <c r="J35" s="108" t="n"/>
-      <c r="K35" s="108" t="n"/>
-      <c r="L35" s="108" t="n"/>
-      <c r="M35" s="108" t="n"/>
-      <c r="N35" s="108" t="n"/>
-      <c r="O35" s="108" t="n"/>
-      <c r="P35" s="108" t="n"/>
-      <c r="Q35" s="108" t="n"/>
-      <c r="R35" s="108" t="n"/>
+      <c r="G35" s="179" t="n"/>
+      <c r="H35" s="179" t="n"/>
+      <c r="I35" s="179" t="n"/>
+      <c r="J35" s="179" t="n"/>
+      <c r="K35" s="179" t="n"/>
+      <c r="L35" s="179" t="n"/>
+      <c r="M35" s="179" t="n"/>
+      <c r="N35" s="179" t="n"/>
+      <c r="O35" s="179" t="n"/>
+      <c r="P35" s="179" t="n"/>
+      <c r="Q35" s="179" t="n"/>
+      <c r="R35" s="179" t="n"/>
       <c r="S35" s="114" t="inlineStr">
         <is>
           <t>○</t>
@@ -3217,9 +3303,9 @@
           <t>○</t>
         </is>
       </c>
-      <c r="U35" s="108" t="n"/>
-      <c r="V35" s="108" t="n"/>
-      <c r="W35" s="108" t="n"/>
+      <c r="U35" s="179" t="n"/>
+      <c r="V35" s="179" t="n"/>
+      <c r="W35" s="179" t="n"/>
       <c r="X35" s="84" t="n"/>
       <c r="Y35" s="84" t="n"/>
       <c r="Z35" s="84" t="n"/>
@@ -3290,22 +3376,22 @@
           <t>○</t>
         </is>
       </c>
-      <c r="H38" s="108" t="n"/>
-      <c r="I38" s="108" t="n"/>
-      <c r="J38" s="108" t="n"/>
-      <c r="K38" s="108" t="n"/>
-      <c r="L38" s="108" t="n"/>
-      <c r="M38" s="108" t="n"/>
-      <c r="N38" s="108" t="n"/>
-      <c r="O38" s="108" t="n"/>
-      <c r="P38" s="108" t="n"/>
-      <c r="Q38" s="108" t="n"/>
-      <c r="R38" s="108" t="n"/>
-      <c r="S38" s="108" t="n"/>
-      <c r="T38" s="108" t="n"/>
-      <c r="U38" s="108" t="n"/>
-      <c r="V38" s="108" t="n"/>
-      <c r="W38" s="108" t="n"/>
+      <c r="H38" s="179" t="n"/>
+      <c r="I38" s="179" t="n"/>
+      <c r="J38" s="179" t="n"/>
+      <c r="K38" s="179" t="n"/>
+      <c r="L38" s="179" t="n"/>
+      <c r="M38" s="179" t="n"/>
+      <c r="N38" s="179" t="n"/>
+      <c r="O38" s="179" t="n"/>
+      <c r="P38" s="179" t="n"/>
+      <c r="Q38" s="179" t="n"/>
+      <c r="R38" s="179" t="n"/>
+      <c r="S38" s="179" t="n"/>
+      <c r="T38" s="179" t="n"/>
+      <c r="U38" s="179" t="n"/>
+      <c r="V38" s="179" t="n"/>
+      <c r="W38" s="179" t="n"/>
       <c r="X38" s="84" t="n"/>
       <c r="Y38" s="84" t="n"/>
       <c r="Z38" s="84" t="n"/>
@@ -3348,22 +3434,22 @@
           <t>○</t>
         </is>
       </c>
-      <c r="H39" s="108" t="n"/>
-      <c r="I39" s="108" t="n"/>
-      <c r="J39" s="108" t="n"/>
-      <c r="K39" s="108" t="n"/>
-      <c r="L39" s="108" t="n"/>
-      <c r="M39" s="108" t="n"/>
-      <c r="N39" s="108" t="n"/>
-      <c r="O39" s="108" t="n"/>
-      <c r="P39" s="108" t="n"/>
-      <c r="Q39" s="108" t="n"/>
-      <c r="R39" s="108" t="n"/>
-      <c r="S39" s="108" t="n"/>
-      <c r="T39" s="108" t="n"/>
-      <c r="U39" s="108" t="n"/>
-      <c r="V39" s="108" t="n"/>
-      <c r="W39" s="108" t="n"/>
+      <c r="H39" s="179" t="n"/>
+      <c r="I39" s="179" t="n"/>
+      <c r="J39" s="179" t="n"/>
+      <c r="K39" s="179" t="n"/>
+      <c r="L39" s="179" t="n"/>
+      <c r="M39" s="179" t="n"/>
+      <c r="N39" s="179" t="n"/>
+      <c r="O39" s="179" t="n"/>
+      <c r="P39" s="179" t="n"/>
+      <c r="Q39" s="179" t="n"/>
+      <c r="R39" s="179" t="n"/>
+      <c r="S39" s="179" t="n"/>
+      <c r="T39" s="179" t="n"/>
+      <c r="U39" s="179" t="n"/>
+      <c r="V39" s="179" t="n"/>
+      <c r="W39" s="179" t="n"/>
       <c r="X39" s="84" t="n"/>
       <c r="Y39" s="84" t="n"/>
       <c r="Z39" s="84" t="n"/>
@@ -3397,27 +3483,27 @@
         </is>
       </c>
       <c r="F40" s="106" t="inlineStr"/>
-      <c r="G40" s="108" t="n"/>
+      <c r="G40" s="179" t="n"/>
       <c r="H40" s="119" t="inlineStr">
         <is>
           <t>○</t>
         </is>
       </c>
-      <c r="I40" s="108" t="n"/>
-      <c r="J40" s="108" t="n"/>
-      <c r="K40" s="108" t="n"/>
-      <c r="L40" s="108" t="n"/>
-      <c r="M40" s="108" t="n"/>
-      <c r="N40" s="108" t="n"/>
-      <c r="O40" s="108" t="n"/>
-      <c r="P40" s="108" t="n"/>
-      <c r="Q40" s="108" t="n"/>
-      <c r="R40" s="108" t="n"/>
-      <c r="S40" s="108" t="n"/>
-      <c r="T40" s="108" t="n"/>
-      <c r="U40" s="108" t="n"/>
-      <c r="V40" s="108" t="n"/>
-      <c r="W40" s="108" t="n"/>
+      <c r="I40" s="179" t="n"/>
+      <c r="J40" s="179" t="n"/>
+      <c r="K40" s="179" t="n"/>
+      <c r="L40" s="179" t="n"/>
+      <c r="M40" s="179" t="n"/>
+      <c r="N40" s="179" t="n"/>
+      <c r="O40" s="179" t="n"/>
+      <c r="P40" s="179" t="n"/>
+      <c r="Q40" s="179" t="n"/>
+      <c r="R40" s="179" t="n"/>
+      <c r="S40" s="179" t="n"/>
+      <c r="T40" s="179" t="n"/>
+      <c r="U40" s="179" t="n"/>
+      <c r="V40" s="179" t="n"/>
+      <c r="W40" s="179" t="n"/>
       <c r="X40" s="84" t="n"/>
       <c r="Y40" s="84" t="n"/>
       <c r="Z40" s="84" t="n"/>
@@ -3471,27 +3557,27 @@
           <t>月次自動保持ルール作成</t>
         </is>
       </c>
-      <c r="G42" s="108" t="n"/>
+      <c r="G42" s="179" t="n"/>
       <c r="H42" s="119" t="inlineStr">
         <is>
           <t>○</t>
         </is>
       </c>
-      <c r="I42" s="108" t="n"/>
-      <c r="J42" s="108" t="n"/>
-      <c r="K42" s="108" t="n"/>
-      <c r="L42" s="108" t="n"/>
-      <c r="M42" s="108" t="n"/>
-      <c r="N42" s="108" t="n"/>
-      <c r="O42" s="108" t="n"/>
-      <c r="P42" s="108" t="n"/>
-      <c r="Q42" s="108" t="n"/>
-      <c r="R42" s="108" t="n"/>
-      <c r="S42" s="108" t="n"/>
-      <c r="T42" s="108" t="n"/>
-      <c r="U42" s="108" t="n"/>
-      <c r="V42" s="108" t="n"/>
-      <c r="W42" s="108" t="n"/>
+      <c r="I42" s="179" t="n"/>
+      <c r="J42" s="179" t="n"/>
+      <c r="K42" s="179" t="n"/>
+      <c r="L42" s="179" t="n"/>
+      <c r="M42" s="179" t="n"/>
+      <c r="N42" s="179" t="n"/>
+      <c r="O42" s="179" t="n"/>
+      <c r="P42" s="179" t="n"/>
+      <c r="Q42" s="179" t="n"/>
+      <c r="R42" s="179" t="n"/>
+      <c r="S42" s="179" t="n"/>
+      <c r="T42" s="179" t="n"/>
+      <c r="U42" s="179" t="n"/>
+      <c r="V42" s="179" t="n"/>
+      <c r="W42" s="179" t="n"/>
       <c r="X42" s="84" t="n"/>
       <c r="Y42" s="84" t="n"/>
       <c r="Z42" s="84" t="n"/>
@@ -3525,27 +3611,27 @@
         </is>
       </c>
       <c r="F43" s="106" t="inlineStr"/>
-      <c r="G43" s="108" t="n"/>
-      <c r="H43" s="108" t="n"/>
+      <c r="G43" s="179" t="n"/>
+      <c r="H43" s="179" t="n"/>
       <c r="I43" s="119" t="inlineStr">
         <is>
           <t>○</t>
         </is>
       </c>
-      <c r="J43" s="108" t="n"/>
-      <c r="K43" s="108" t="n"/>
-      <c r="L43" s="108" t="n"/>
-      <c r="M43" s="108" t="n"/>
-      <c r="N43" s="108" t="n"/>
-      <c r="O43" s="108" t="n"/>
-      <c r="P43" s="108" t="n"/>
-      <c r="Q43" s="108" t="n"/>
-      <c r="R43" s="108" t="n"/>
-      <c r="S43" s="108" t="n"/>
-      <c r="T43" s="108" t="n"/>
-      <c r="U43" s="108" t="n"/>
-      <c r="V43" s="108" t="n"/>
-      <c r="W43" s="108" t="n"/>
+      <c r="J43" s="179" t="n"/>
+      <c r="K43" s="179" t="n"/>
+      <c r="L43" s="179" t="n"/>
+      <c r="M43" s="179" t="n"/>
+      <c r="N43" s="179" t="n"/>
+      <c r="O43" s="179" t="n"/>
+      <c r="P43" s="179" t="n"/>
+      <c r="Q43" s="179" t="n"/>
+      <c r="R43" s="179" t="n"/>
+      <c r="S43" s="179" t="n"/>
+      <c r="T43" s="179" t="n"/>
+      <c r="U43" s="179" t="n"/>
+      <c r="V43" s="179" t="n"/>
+      <c r="W43" s="179" t="n"/>
       <c r="X43" s="84" t="n"/>
       <c r="Y43" s="84" t="n"/>
       <c r="Z43" s="84" t="n"/>
@@ -3579,27 +3665,27 @@
         </is>
       </c>
       <c r="F44" s="106" t="inlineStr"/>
-      <c r="G44" s="108" t="n"/>
-      <c r="H44" s="108" t="n"/>
-      <c r="I44" s="108" t="n"/>
+      <c r="G44" s="179" t="n"/>
+      <c r="H44" s="179" t="n"/>
+      <c r="I44" s="179" t="n"/>
       <c r="J44" s="119" t="inlineStr">
         <is>
           <t>○</t>
         </is>
       </c>
-      <c r="K44" s="108" t="n"/>
-      <c r="L44" s="108" t="n"/>
-      <c r="M44" s="108" t="n"/>
-      <c r="N44" s="108" t="n"/>
-      <c r="O44" s="108" t="n"/>
-      <c r="P44" s="108" t="n"/>
-      <c r="Q44" s="108" t="n"/>
-      <c r="R44" s="108" t="n"/>
-      <c r="S44" s="108" t="n"/>
-      <c r="T44" s="108" t="n"/>
-      <c r="U44" s="108" t="n"/>
-      <c r="V44" s="108" t="n"/>
-      <c r="W44" s="108" t="n"/>
+      <c r="K44" s="179" t="n"/>
+      <c r="L44" s="179" t="n"/>
+      <c r="M44" s="179" t="n"/>
+      <c r="N44" s="179" t="n"/>
+      <c r="O44" s="179" t="n"/>
+      <c r="P44" s="179" t="n"/>
+      <c r="Q44" s="179" t="n"/>
+      <c r="R44" s="179" t="n"/>
+      <c r="S44" s="179" t="n"/>
+      <c r="T44" s="179" t="n"/>
+      <c r="U44" s="179" t="n"/>
+      <c r="V44" s="179" t="n"/>
+      <c r="W44" s="179" t="n"/>
       <c r="X44" s="84" t="n"/>
       <c r="Y44" s="84" t="n"/>
       <c r="Z44" s="84" t="n"/>
@@ -3670,22 +3756,22 @@
           <t>○</t>
         </is>
       </c>
-      <c r="H47" s="108" t="n"/>
-      <c r="I47" s="108" t="n"/>
-      <c r="J47" s="108" t="n"/>
-      <c r="K47" s="108" t="n"/>
-      <c r="L47" s="108" t="n"/>
-      <c r="M47" s="108" t="n"/>
-      <c r="N47" s="108" t="n"/>
-      <c r="O47" s="108" t="n"/>
-      <c r="P47" s="108" t="n"/>
-      <c r="Q47" s="108" t="n"/>
-      <c r="R47" s="108" t="n"/>
-      <c r="S47" s="108" t="n"/>
-      <c r="T47" s="108" t="n"/>
-      <c r="U47" s="108" t="n"/>
-      <c r="V47" s="108" t="n"/>
-      <c r="W47" s="108" t="n"/>
+      <c r="H47" s="179" t="n"/>
+      <c r="I47" s="179" t="n"/>
+      <c r="J47" s="179" t="n"/>
+      <c r="K47" s="179" t="n"/>
+      <c r="L47" s="179" t="n"/>
+      <c r="M47" s="179" t="n"/>
+      <c r="N47" s="179" t="n"/>
+      <c r="O47" s="179" t="n"/>
+      <c r="P47" s="179" t="n"/>
+      <c r="Q47" s="179" t="n"/>
+      <c r="R47" s="179" t="n"/>
+      <c r="S47" s="179" t="n"/>
+      <c r="T47" s="179" t="n"/>
+      <c r="U47" s="179" t="n"/>
+      <c r="V47" s="179" t="n"/>
+      <c r="W47" s="179" t="n"/>
       <c r="X47" s="84" t="n"/>
       <c r="Y47" s="84" t="n"/>
       <c r="Z47" s="84" t="n"/>
@@ -3728,22 +3814,22 @@
           <t>○</t>
         </is>
       </c>
-      <c r="H48" s="108" t="n"/>
-      <c r="I48" s="108" t="n"/>
-      <c r="J48" s="108" t="n"/>
-      <c r="K48" s="108" t="n"/>
-      <c r="L48" s="108" t="n"/>
-      <c r="M48" s="108" t="n"/>
-      <c r="N48" s="108" t="n"/>
-      <c r="O48" s="108" t="n"/>
-      <c r="P48" s="108" t="n"/>
-      <c r="Q48" s="108" t="n"/>
-      <c r="R48" s="108" t="n"/>
-      <c r="S48" s="108" t="n"/>
-      <c r="T48" s="108" t="n"/>
-      <c r="U48" s="108" t="n"/>
-      <c r="V48" s="108" t="n"/>
-      <c r="W48" s="108" t="n"/>
+      <c r="H48" s="179" t="n"/>
+      <c r="I48" s="179" t="n"/>
+      <c r="J48" s="179" t="n"/>
+      <c r="K48" s="179" t="n"/>
+      <c r="L48" s="179" t="n"/>
+      <c r="M48" s="179" t="n"/>
+      <c r="N48" s="179" t="n"/>
+      <c r="O48" s="179" t="n"/>
+      <c r="P48" s="179" t="n"/>
+      <c r="Q48" s="179" t="n"/>
+      <c r="R48" s="179" t="n"/>
+      <c r="S48" s="179" t="n"/>
+      <c r="T48" s="179" t="n"/>
+      <c r="U48" s="179" t="n"/>
+      <c r="V48" s="179" t="n"/>
+      <c r="W48" s="179" t="n"/>
       <c r="X48" s="84" t="n"/>
       <c r="Y48" s="84" t="n"/>
       <c r="Z48" s="84" t="n"/>
@@ -3777,27 +3863,27 @@
         </is>
       </c>
       <c r="F49" s="106" t="inlineStr"/>
-      <c r="G49" s="108" t="n"/>
+      <c r="G49" s="179" t="n"/>
       <c r="H49" s="124" t="inlineStr">
         <is>
           <t>○</t>
         </is>
       </c>
-      <c r="I49" s="108" t="n"/>
-      <c r="J49" s="108" t="n"/>
-      <c r="K49" s="108" t="n"/>
-      <c r="L49" s="108" t="n"/>
-      <c r="M49" s="108" t="n"/>
-      <c r="N49" s="108" t="n"/>
-      <c r="O49" s="108" t="n"/>
-      <c r="P49" s="108" t="n"/>
-      <c r="Q49" s="108" t="n"/>
-      <c r="R49" s="108" t="n"/>
-      <c r="S49" s="108" t="n"/>
-      <c r="T49" s="108" t="n"/>
-      <c r="U49" s="108" t="n"/>
-      <c r="V49" s="108" t="n"/>
-      <c r="W49" s="108" t="n"/>
+      <c r="I49" s="179" t="n"/>
+      <c r="J49" s="179" t="n"/>
+      <c r="K49" s="179" t="n"/>
+      <c r="L49" s="179" t="n"/>
+      <c r="M49" s="179" t="n"/>
+      <c r="N49" s="179" t="n"/>
+      <c r="O49" s="179" t="n"/>
+      <c r="P49" s="179" t="n"/>
+      <c r="Q49" s="179" t="n"/>
+      <c r="R49" s="179" t="n"/>
+      <c r="S49" s="179" t="n"/>
+      <c r="T49" s="179" t="n"/>
+      <c r="U49" s="179" t="n"/>
+      <c r="V49" s="179" t="n"/>
+      <c r="W49" s="179" t="n"/>
       <c r="X49" s="84" t="n"/>
       <c r="Y49" s="84" t="n"/>
       <c r="Z49" s="84" t="n"/>
@@ -3851,27 +3937,27 @@
           <t>フェイルオーバー動作に影響なし</t>
         </is>
       </c>
-      <c r="G51" s="108" t="n"/>
+      <c r="G51" s="179" t="n"/>
       <c r="H51" s="124" t="inlineStr">
         <is>
           <t>○</t>
         </is>
       </c>
-      <c r="I51" s="108" t="n"/>
-      <c r="J51" s="108" t="n"/>
-      <c r="K51" s="108" t="n"/>
-      <c r="L51" s="108" t="n"/>
-      <c r="M51" s="108" t="n"/>
-      <c r="N51" s="108" t="n"/>
-      <c r="O51" s="108" t="n"/>
-      <c r="P51" s="108" t="n"/>
-      <c r="Q51" s="108" t="n"/>
-      <c r="R51" s="108" t="n"/>
-      <c r="S51" s="108" t="n"/>
-      <c r="T51" s="108" t="n"/>
-      <c r="U51" s="108" t="n"/>
-      <c r="V51" s="108" t="n"/>
-      <c r="W51" s="108" t="n"/>
+      <c r="I51" s="179" t="n"/>
+      <c r="J51" s="179" t="n"/>
+      <c r="K51" s="179" t="n"/>
+      <c r="L51" s="179" t="n"/>
+      <c r="M51" s="179" t="n"/>
+      <c r="N51" s="179" t="n"/>
+      <c r="O51" s="179" t="n"/>
+      <c r="P51" s="179" t="n"/>
+      <c r="Q51" s="179" t="n"/>
+      <c r="R51" s="179" t="n"/>
+      <c r="S51" s="179" t="n"/>
+      <c r="T51" s="179" t="n"/>
+      <c r="U51" s="179" t="n"/>
+      <c r="V51" s="179" t="n"/>
+      <c r="W51" s="179" t="n"/>
       <c r="X51" s="84" t="n"/>
       <c r="Y51" s="84" t="n"/>
       <c r="Z51" s="84" t="n"/>
@@ -3905,27 +3991,27 @@
         </is>
       </c>
       <c r="F52" s="106" t="inlineStr"/>
-      <c r="G52" s="108" t="n"/>
+      <c r="G52" s="179" t="n"/>
       <c r="H52" s="124" t="inlineStr">
         <is>
           <t>○</t>
         </is>
       </c>
-      <c r="I52" s="108" t="n"/>
-      <c r="J52" s="108" t="n"/>
-      <c r="K52" s="108" t="n"/>
-      <c r="L52" s="108" t="n"/>
-      <c r="M52" s="108" t="n"/>
-      <c r="N52" s="108" t="n"/>
-      <c r="O52" s="108" t="n"/>
-      <c r="P52" s="108" t="n"/>
-      <c r="Q52" s="108" t="n"/>
-      <c r="R52" s="108" t="n"/>
-      <c r="S52" s="108" t="n"/>
-      <c r="T52" s="108" t="n"/>
-      <c r="U52" s="108" t="n"/>
-      <c r="V52" s="108" t="n"/>
-      <c r="W52" s="108" t="n"/>
+      <c r="I52" s="179" t="n"/>
+      <c r="J52" s="179" t="n"/>
+      <c r="K52" s="179" t="n"/>
+      <c r="L52" s="179" t="n"/>
+      <c r="M52" s="179" t="n"/>
+      <c r="N52" s="179" t="n"/>
+      <c r="O52" s="179" t="n"/>
+      <c r="P52" s="179" t="n"/>
+      <c r="Q52" s="179" t="n"/>
+      <c r="R52" s="179" t="n"/>
+      <c r="S52" s="179" t="n"/>
+      <c r="T52" s="179" t="n"/>
+      <c r="U52" s="179" t="n"/>
+      <c r="V52" s="179" t="n"/>
+      <c r="W52" s="179" t="n"/>
       <c r="X52" s="84" t="n"/>
       <c r="Y52" s="84" t="n"/>
       <c r="Z52" s="84" t="n"/>
@@ -3937,367 +4023,178 @@
       <c r="AF52" s="84" t="n"/>
     </row>
     <row r="53" ht="20" customHeight="1" s="80">
-      <c r="A53" s="171" t="inlineStr">
+      <c r="A53" s="182" t="inlineStr">
+        <is>
+          <t>▶ ⑦ Transfer Family コスト削減（OC系・SH系 スケジュール停止）</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="18" customHeight="1" s="80">
+      <c r="A54" s="183" t="inlineStr">
+        <is>
+          <t>T-1</t>
+        </is>
+      </c>
+      <c r="B54" s="184" t="inlineStr">
+        <is>
+          <t>承認依頼・顧客確認書提出</t>
+        </is>
+      </c>
+      <c r="C54" s="183" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="E54" s="183" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
+      <c r="F54" s="185" t="inlineStr">
+        <is>
+          <t>改修指示書 20260308-003 使用</t>
+        </is>
+      </c>
+      <c r="G54" s="186" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="18" customHeight="1" s="80">
+      <c r="A55" s="183" t="inlineStr">
+        <is>
+          <t>T-2</t>
+        </is>
+      </c>
+      <c r="B55" s="184" t="inlineStr">
+        <is>
+          <t>承認取得</t>
+        </is>
+      </c>
+      <c r="C55" s="183" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="E55" s="183" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
+      <c r="F55" s="185" t="inlineStr">
+        <is>
+          <t>カスミ様・BIPROGY様・SHARP様</t>
+        </is>
+      </c>
+      <c r="H55" s="186" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="18" customHeight="1" s="80">
+      <c r="A56" s="183" t="inlineStr">
+        <is>
+          <t>T-3</t>
+        </is>
+      </c>
+      <c r="B56" s="184" t="inlineStr">
+        <is>
+          <t>Lambda 関数作成（ksm-posprd-lmd-function-tf-schedule）</t>
+        </is>
+      </c>
+      <c r="C56" s="183" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="E56" s="183" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
+      <c r="F56" s="185" t="inlineStr">
+        <is>
+          <t>Python 3.13, start/stop 権限付与</t>
+        </is>
+      </c>
+      <c r="I56" s="186" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="18" customHeight="1" s="80">
+      <c r="A57" s="183" t="inlineStr">
+        <is>
+          <t>T-4</t>
+        </is>
+      </c>
+      <c r="B57" s="184" t="inlineStr">
+        <is>
+          <t>EventBridge 起動・停止ルール作成（cron 2本）</t>
+        </is>
+      </c>
+      <c r="C57" s="183" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="E57" s="183" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
+      <c r="F57" s="185" t="inlineStr">
+        <is>
+          <t>起動=JST 20:00 / 停止=JST 07:00</t>
+        </is>
+      </c>
+      <c r="I57" s="186" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="18" customHeight="1" s="80">
+      <c r="A58" s="183" t="inlineStr">
+        <is>
+          <t>T-5</t>
+        </is>
+      </c>
+      <c r="B58" s="184" t="inlineStr">
+        <is>
+          <t>動作テスト・コスト削減効果確認</t>
+        </is>
+      </c>
+      <c r="C58" s="183" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="E58" s="183" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
+      <c r="F58" s="185" t="inlineStr">
+        <is>
+          <t>削減効果確認（▲$234/月）</t>
+        </is>
+      </c>
+      <c r="J58" s="186" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="20" customHeight="1" s="80">
+      <c r="A59" s="171" t="inlineStr">
         <is>
           <t>▶ ③ RDS インスタンスダウンサイズ（承認後実施）</t>
         </is>
       </c>
-      <c r="X53" s="84" t="n"/>
-      <c r="Y53" s="84" t="n"/>
-      <c r="Z53" s="84" t="n"/>
-      <c r="AA53" s="84" t="n"/>
-      <c r="AB53" s="84" t="n"/>
-      <c r="AC53" s="84" t="n"/>
-      <c r="AD53" s="84" t="n"/>
-      <c r="AE53" s="84" t="n"/>
-      <c r="AF53" s="84" t="n"/>
-    </row>
-    <row r="54" ht="18" customHeight="1" s="80">
-      <c r="A54" s="102" t="inlineStr">
-        <is>
-          <t>E-1</t>
-        </is>
-      </c>
-      <c r="B54" s="103" t="inlineStr">
-        <is>
-          <t>承認依頼資料作成・提出</t>
-        </is>
-      </c>
-      <c r="C54" s="109" t="inlineStr">
-        <is>
-          <t>2026-03-20</t>
-        </is>
-      </c>
-      <c r="D54" s="109" t="n"/>
-      <c r="E54" s="105" t="inlineStr">
-        <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="F54" s="106" t="inlineStr">
-        <is>
-          <t>06_コスト調査レポート使用</t>
-        </is>
-      </c>
-      <c r="G54" s="108" t="n"/>
-      <c r="H54" s="124" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="I54" s="124" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="J54" s="108" t="n"/>
-      <c r="K54" s="108" t="n"/>
-      <c r="L54" s="108" t="n"/>
-      <c r="M54" s="108" t="n"/>
-      <c r="N54" s="108" t="n"/>
-      <c r="O54" s="108" t="n"/>
-      <c r="P54" s="108" t="n"/>
-      <c r="Q54" s="108" t="n"/>
-      <c r="R54" s="108" t="n"/>
-      <c r="S54" s="108" t="n"/>
-      <c r="T54" s="108" t="n"/>
-      <c r="U54" s="108" t="n"/>
-      <c r="V54" s="108" t="n"/>
-      <c r="W54" s="108" t="n"/>
-      <c r="X54" s="84" t="n"/>
-      <c r="Y54" s="84" t="n"/>
-      <c r="Z54" s="84" t="n"/>
-      <c r="AA54" s="84" t="n"/>
-      <c r="AB54" s="84" t="n"/>
-      <c r="AC54" s="84" t="n"/>
-      <c r="AD54" s="84" t="n"/>
-      <c r="AE54" s="84" t="n"/>
-      <c r="AF54" s="84" t="n"/>
-    </row>
-    <row r="55" ht="18" customHeight="1" s="80">
-      <c r="A55" s="102" t="inlineStr">
-        <is>
-          <t>E-2</t>
-        </is>
-      </c>
-      <c r="B55" s="103" t="inlineStr">
-        <is>
-          <t>承認取得</t>
-        </is>
-      </c>
-      <c r="C55" s="109" t="inlineStr">
-        <is>
-          <t>2026-03-27</t>
-        </is>
-      </c>
-      <c r="D55" s="109" t="n"/>
-      <c r="E55" s="105" t="inlineStr">
-        <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="F55" s="106" t="inlineStr">
-        <is>
-          <t>カスミ様・BIPROGY様</t>
-        </is>
-      </c>
-      <c r="G55" s="108" t="n"/>
-      <c r="H55" s="108" t="n"/>
-      <c r="I55" s="124" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="J55" s="124" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="K55" s="108" t="n"/>
-      <c r="L55" s="108" t="n"/>
-      <c r="M55" s="108" t="n"/>
-      <c r="N55" s="108" t="n"/>
-      <c r="O55" s="108" t="n"/>
-      <c r="P55" s="108" t="n"/>
-      <c r="Q55" s="108" t="n"/>
-      <c r="R55" s="108" t="n"/>
-      <c r="S55" s="108" t="n"/>
-      <c r="T55" s="108" t="n"/>
-      <c r="U55" s="108" t="n"/>
-      <c r="V55" s="108" t="n"/>
-      <c r="W55" s="108" t="n"/>
-      <c r="X55" s="84" t="n"/>
-      <c r="Y55" s="84" t="n"/>
-      <c r="Z55" s="84" t="n"/>
-      <c r="AA55" s="84" t="n"/>
-      <c r="AB55" s="84" t="n"/>
-      <c r="AC55" s="84" t="n"/>
-      <c r="AD55" s="84" t="n"/>
-      <c r="AE55" s="84" t="n"/>
-      <c r="AF55" s="84" t="n"/>
-    </row>
-    <row r="56" ht="18" customHeight="1" s="80">
-      <c r="A56" s="102" t="inlineStr">
-        <is>
-          <t>E-3</t>
-        </is>
-      </c>
-      <c r="B56" s="103" t="inlineStr">
-        <is>
-          <t>ダウンサイズ手順書・ロールバック計画作成</t>
-        </is>
-      </c>
-      <c r="C56" s="109" t="inlineStr">
-        <is>
-          <t>2026-04-06</t>
-        </is>
-      </c>
-      <c r="D56" s="109" t="n"/>
-      <c r="E56" s="105" t="inlineStr">
-        <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="F56" s="106" t="inlineStr"/>
-      <c r="G56" s="108" t="n"/>
-      <c r="H56" s="108" t="n"/>
-      <c r="I56" s="108" t="n"/>
-      <c r="J56" s="108" t="n"/>
-      <c r="K56" s="124" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="L56" s="108" t="n"/>
-      <c r="M56" s="108" t="n"/>
-      <c r="N56" s="108" t="n"/>
-      <c r="O56" s="108" t="n"/>
-      <c r="P56" s="108" t="n"/>
-      <c r="Q56" s="108" t="n"/>
-      <c r="R56" s="108" t="n"/>
-      <c r="S56" s="108" t="n"/>
-      <c r="T56" s="108" t="n"/>
-      <c r="U56" s="108" t="n"/>
-      <c r="V56" s="108" t="n"/>
-      <c r="W56" s="108" t="n"/>
-      <c r="X56" s="84" t="n"/>
-      <c r="Y56" s="84" t="n"/>
-      <c r="Z56" s="84" t="n"/>
-      <c r="AA56" s="84" t="n"/>
-      <c r="AB56" s="84" t="n"/>
-      <c r="AC56" s="84" t="n"/>
-      <c r="AD56" s="84" t="n"/>
-      <c r="AE56" s="84" t="n"/>
-      <c r="AF56" s="84" t="n"/>
-    </row>
-    <row r="57" ht="18" customHeight="1" s="80">
-      <c r="A57" s="102" t="inlineStr">
-        <is>
-          <t>E-4</t>
-        </is>
-      </c>
-      <c r="B57" s="103" t="inlineStr">
-        <is>
-          <t>instance-2（Reader）ダウンサイズ実施</t>
-        </is>
-      </c>
-      <c r="C57" s="109" t="inlineStr">
-        <is>
-          <t>2026-04-13</t>
-        </is>
-      </c>
-      <c r="D57" s="109" t="n"/>
-      <c r="E57" s="105" t="inlineStr">
-        <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="F57" s="106" t="inlineStr">
-        <is>
-          <t>メンテナンス時間帯に実施</t>
-        </is>
-      </c>
-      <c r="G57" s="108" t="n"/>
-      <c r="H57" s="108" t="n"/>
-      <c r="I57" s="108" t="n"/>
-      <c r="J57" s="108" t="n"/>
-      <c r="K57" s="108" t="n"/>
-      <c r="L57" s="124" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="M57" s="108" t="n"/>
-      <c r="N57" s="108" t="n"/>
-      <c r="O57" s="108" t="n"/>
-      <c r="P57" s="108" t="n"/>
-      <c r="Q57" s="108" t="n"/>
-      <c r="R57" s="108" t="n"/>
-      <c r="S57" s="108" t="n"/>
-      <c r="T57" s="108" t="n"/>
-      <c r="U57" s="108" t="n"/>
-      <c r="V57" s="108" t="n"/>
-      <c r="W57" s="108" t="n"/>
-      <c r="X57" s="84" t="n"/>
-      <c r="Y57" s="84" t="n"/>
-      <c r="Z57" s="84" t="n"/>
-      <c r="AA57" s="84" t="n"/>
-      <c r="AB57" s="84" t="n"/>
-      <c r="AC57" s="84" t="n"/>
-      <c r="AD57" s="84" t="n"/>
-      <c r="AE57" s="84" t="n"/>
-      <c r="AF57" s="84" t="n"/>
-    </row>
-    <row r="58" ht="18" customHeight="1" s="80">
-      <c r="A58" s="102" t="inlineStr">
-        <is>
-          <t>E-5</t>
-        </is>
-      </c>
-      <c r="B58" s="103" t="inlineStr">
-        <is>
-          <t>動作確認・メトリクス監視（1週間）</t>
-        </is>
-      </c>
-      <c r="C58" s="104" t="inlineStr">
-        <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-      <c r="D58" s="104" t="n"/>
-      <c r="E58" s="105" t="inlineStr">
-        <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="F58" s="106" t="inlineStr">
-        <is>
-          <t>CPU/接続数/IOPSモニタリング</t>
-        </is>
-      </c>
-      <c r="G58" s="108" t="n"/>
-      <c r="H58" s="108" t="n"/>
-      <c r="I58" s="108" t="n"/>
-      <c r="J58" s="108" t="n"/>
-      <c r="K58" s="108" t="n"/>
-      <c r="L58" s="124" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="M58" s="124" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="N58" s="108" t="n"/>
-      <c r="O58" s="108" t="n"/>
-      <c r="P58" s="108" t="n"/>
-      <c r="Q58" s="108" t="n"/>
-      <c r="R58" s="108" t="n"/>
-      <c r="S58" s="108" t="n"/>
-      <c r="T58" s="108" t="n"/>
-      <c r="U58" s="108" t="n"/>
-      <c r="V58" s="108" t="n"/>
-      <c r="W58" s="108" t="n"/>
-      <c r="X58" s="84" t="n"/>
-      <c r="Y58" s="84" t="n"/>
-      <c r="Z58" s="84" t="n"/>
-      <c r="AA58" s="84" t="n"/>
-      <c r="AB58" s="84" t="n"/>
-      <c r="AC58" s="84" t="n"/>
-      <c r="AD58" s="84" t="n"/>
-      <c r="AE58" s="84" t="n"/>
-      <c r="AF58" s="84" t="n"/>
-    </row>
-    <row r="59" ht="18" customHeight="1" s="80">
-      <c r="A59" s="102" t="inlineStr">
-        <is>
-          <t>E-6</t>
-        </is>
-      </c>
-      <c r="B59" s="103" t="inlineStr">
-        <is>
-          <t>instance-1（Writer）ダウンサイズ実施</t>
-        </is>
-      </c>
-      <c r="C59" s="109" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-      <c r="D59" s="109" t="n"/>
-      <c r="E59" s="105" t="inlineStr">
-        <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="F59" s="106" t="inlineStr">
-        <is>
-          <t>Reader安定確認後に実施</t>
-        </is>
-      </c>
-      <c r="G59" s="108" t="n"/>
-      <c r="H59" s="108" t="n"/>
-      <c r="I59" s="108" t="n"/>
-      <c r="J59" s="108" t="n"/>
-      <c r="K59" s="108" t="n"/>
-      <c r="L59" s="108" t="n"/>
-      <c r="M59" s="108" t="n"/>
-      <c r="N59" s="124" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="O59" s="108" t="n"/>
-      <c r="P59" s="108" t="n"/>
-      <c r="Q59" s="108" t="n"/>
-      <c r="R59" s="108" t="n"/>
-      <c r="S59" s="108" t="n"/>
-      <c r="T59" s="108" t="n"/>
-      <c r="U59" s="108" t="n"/>
-      <c r="V59" s="108" t="n"/>
-      <c r="W59" s="108" t="n"/>
       <c r="X59" s="84" t="n"/>
       <c r="Y59" s="84" t="n"/>
       <c r="Z59" s="84" t="n"/>
@@ -4311,17 +4208,17 @@
     <row r="60" ht="18" customHeight="1" s="80">
       <c r="A60" s="102" t="inlineStr">
         <is>
-          <t>E-7</t>
+          <t>E-1</t>
         </is>
       </c>
       <c r="B60" s="103" t="inlineStr">
         <is>
-          <t>最終動作確認・完了報告</t>
+          <t>承認依頼資料作成・提出</t>
         </is>
       </c>
       <c r="C60" s="109" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="D60" s="109" t="n"/>
@@ -4332,30 +4229,34 @@
       </c>
       <c r="F60" s="106" t="inlineStr">
         <is>
-          <t>削減効果確認($1,369/月)</t>
-        </is>
-      </c>
-      <c r="G60" s="108" t="n"/>
-      <c r="H60" s="108" t="n"/>
-      <c r="I60" s="108" t="n"/>
-      <c r="J60" s="108" t="n"/>
-      <c r="K60" s="108" t="n"/>
-      <c r="L60" s="108" t="n"/>
-      <c r="M60" s="108" t="n"/>
-      <c r="N60" s="124" t="inlineStr">
+          <t>06_コスト調査レポート使用</t>
+        </is>
+      </c>
+      <c r="G60" s="179" t="n"/>
+      <c r="H60" s="124" t="inlineStr">
         <is>
           <t>○</t>
         </is>
       </c>
-      <c r="O60" s="108" t="n"/>
-      <c r="P60" s="108" t="n"/>
-      <c r="Q60" s="108" t="n"/>
-      <c r="R60" s="108" t="n"/>
-      <c r="S60" s="108" t="n"/>
-      <c r="T60" s="108" t="n"/>
-      <c r="U60" s="108" t="n"/>
-      <c r="V60" s="108" t="n"/>
-      <c r="W60" s="108" t="n"/>
+      <c r="I60" s="124" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="J60" s="179" t="n"/>
+      <c r="K60" s="179" t="n"/>
+      <c r="L60" s="179" t="n"/>
+      <c r="M60" s="179" t="n"/>
+      <c r="N60" s="179" t="n"/>
+      <c r="O60" s="179" t="n"/>
+      <c r="P60" s="179" t="n"/>
+      <c r="Q60" s="179" t="n"/>
+      <c r="R60" s="179" t="n"/>
+      <c r="S60" s="179" t="n"/>
+      <c r="T60" s="179" t="n"/>
+      <c r="U60" s="179" t="n"/>
+      <c r="V60" s="179" t="n"/>
+      <c r="W60" s="179" t="n"/>
       <c r="X60" s="84" t="n"/>
       <c r="Y60" s="84" t="n"/>
       <c r="Z60" s="84" t="n"/>
@@ -4366,10 +4267,35 @@
       <c r="AE60" s="84" t="n"/>
       <c r="AF60" s="84" t="n"/>
     </row>
-    <row r="61" ht="20" customHeight="1" s="80">
-      <c r="A61" s="171" t="inlineStr">
-        <is>
-          <t>▶ ⑥ シークレット命名の改善（中長期・任意）</t>
+    <row r="61" ht="18" customHeight="1" s="80">
+      <c r="A61" s="187" t="inlineStr">
+        <is>
+          <t>E-2</t>
+        </is>
+      </c>
+      <c r="B61" s="184" t="inlineStr">
+        <is>
+          <t>承認取得</t>
+        </is>
+      </c>
+      <c r="C61" s="183" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="E61" s="183" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
+      <c r="F61" s="188" t="inlineStr">
+        <is>
+          <t>カスミ様・BIPROGY様</t>
+        </is>
+      </c>
+      <c r="H61" s="186" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="X61" s="84" t="n"/>
@@ -4385,17 +4311,17 @@
     <row r="62" ht="18" customHeight="1" s="80">
       <c r="A62" s="102" t="inlineStr">
         <is>
-          <t>G-1</t>
+          <t>E-3</t>
         </is>
       </c>
       <c r="B62" s="103" t="inlineStr">
         <is>
-          <t>影響範囲調査（全Lambda・ECS参照確認）</t>
+          <t>ダウンサイズ手順書・ロールバック計画作成</t>
         </is>
       </c>
       <c r="C62" s="109" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="D62" s="109" t="n"/>
@@ -4405,27 +4331,27 @@
         </is>
       </c>
       <c r="F62" s="106" t="inlineStr"/>
-      <c r="G62" s="108" t="n"/>
-      <c r="H62" s="108" t="n"/>
-      <c r="I62" s="108" t="n"/>
-      <c r="J62" s="108" t="n"/>
-      <c r="K62" s="108" t="n"/>
-      <c r="L62" s="108" t="n"/>
-      <c r="M62" s="108" t="n"/>
-      <c r="N62" s="108" t="n"/>
-      <c r="O62" s="108" t="n"/>
-      <c r="P62" s="124" t="inlineStr">
+      <c r="G62" s="179" t="n"/>
+      <c r="H62" s="179" t="n"/>
+      <c r="I62" s="179" t="n"/>
+      <c r="J62" s="179" t="n"/>
+      <c r="K62" s="124" t="inlineStr">
         <is>
           <t>○</t>
         </is>
       </c>
-      <c r="Q62" s="108" t="n"/>
-      <c r="R62" s="108" t="n"/>
-      <c r="S62" s="108" t="n"/>
-      <c r="T62" s="108" t="n"/>
-      <c r="U62" s="108" t="n"/>
-      <c r="V62" s="108" t="n"/>
-      <c r="W62" s="108" t="n"/>
+      <c r="L62" s="179" t="n"/>
+      <c r="M62" s="179" t="n"/>
+      <c r="N62" s="179" t="n"/>
+      <c r="O62" s="179" t="n"/>
+      <c r="P62" s="179" t="n"/>
+      <c r="Q62" s="179" t="n"/>
+      <c r="R62" s="179" t="n"/>
+      <c r="S62" s="179" t="n"/>
+      <c r="T62" s="179" t="n"/>
+      <c r="U62" s="179" t="n"/>
+      <c r="V62" s="179" t="n"/>
+      <c r="W62" s="179" t="n"/>
       <c r="X62" s="84" t="n"/>
       <c r="Y62" s="84" t="n"/>
       <c r="Z62" s="84" t="n"/>
@@ -4439,17 +4365,17 @@
     <row r="63" ht="18" customHeight="1" s="80">
       <c r="A63" s="102" t="inlineStr">
         <is>
-          <t>G-2</t>
+          <t>E-4</t>
         </is>
       </c>
       <c r="B63" s="103" t="inlineStr">
         <is>
-          <t>変更計画・移行手順書作成</t>
+          <t>instance-2（Reader）ダウンサイズ実施</t>
         </is>
       </c>
       <c r="C63" s="109" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="D63" s="109" t="n"/>
@@ -4458,28 +4384,32 @@
           <t>未着手</t>
         </is>
       </c>
-      <c r="F63" s="106" t="inlineStr"/>
-      <c r="G63" s="108" t="n"/>
-      <c r="H63" s="108" t="n"/>
-      <c r="I63" s="108" t="n"/>
-      <c r="J63" s="108" t="n"/>
-      <c r="K63" s="108" t="n"/>
-      <c r="L63" s="108" t="n"/>
-      <c r="M63" s="108" t="n"/>
-      <c r="N63" s="108" t="n"/>
-      <c r="O63" s="108" t="n"/>
-      <c r="P63" s="108" t="n"/>
-      <c r="Q63" s="124" t="inlineStr">
+      <c r="F63" s="106" t="inlineStr">
+        <is>
+          <t>メンテナンス時間帯に実施</t>
+        </is>
+      </c>
+      <c r="G63" s="179" t="n"/>
+      <c r="H63" s="179" t="n"/>
+      <c r="I63" s="179" t="n"/>
+      <c r="J63" s="179" t="n"/>
+      <c r="K63" s="179" t="n"/>
+      <c r="L63" s="124" t="inlineStr">
         <is>
           <t>○</t>
         </is>
       </c>
-      <c r="R63" s="108" t="n"/>
-      <c r="S63" s="108" t="n"/>
-      <c r="T63" s="108" t="n"/>
-      <c r="U63" s="108" t="n"/>
-      <c r="V63" s="108" t="n"/>
-      <c r="W63" s="108" t="n"/>
+      <c r="M63" s="179" t="n"/>
+      <c r="N63" s="179" t="n"/>
+      <c r="O63" s="179" t="n"/>
+      <c r="P63" s="179" t="n"/>
+      <c r="Q63" s="179" t="n"/>
+      <c r="R63" s="179" t="n"/>
+      <c r="S63" s="179" t="n"/>
+      <c r="T63" s="179" t="n"/>
+      <c r="U63" s="179" t="n"/>
+      <c r="V63" s="179" t="n"/>
+      <c r="W63" s="179" t="n"/>
       <c r="X63" s="84" t="n"/>
       <c r="Y63" s="84" t="n"/>
       <c r="Z63" s="84" t="n"/>
@@ -4493,17 +4423,17 @@
     <row r="64" ht="18" customHeight="1" s="80">
       <c r="A64" s="102" t="inlineStr">
         <is>
-          <t>G-3</t>
+          <t>E-5</t>
         </is>
       </c>
       <c r="B64" s="103" t="inlineStr">
         <is>
-          <t>新シークレット作成・並行稼働確認</t>
+          <t>動作確認・メトリクス監視（1週間）</t>
         </is>
       </c>
       <c r="C64" s="104" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="D64" s="104" t="n"/>
@@ -4512,28 +4442,36 @@
           <t>未着手</t>
         </is>
       </c>
-      <c r="F64" s="106" t="inlineStr"/>
-      <c r="G64" s="108" t="n"/>
-      <c r="H64" s="108" t="n"/>
-      <c r="I64" s="108" t="n"/>
-      <c r="J64" s="108" t="n"/>
-      <c r="K64" s="108" t="n"/>
-      <c r="L64" s="108" t="n"/>
-      <c r="M64" s="108" t="n"/>
-      <c r="N64" s="108" t="n"/>
-      <c r="O64" s="108" t="n"/>
-      <c r="P64" s="108" t="n"/>
-      <c r="Q64" s="108" t="n"/>
-      <c r="R64" s="124" t="inlineStr">
+      <c r="F64" s="106" t="inlineStr">
+        <is>
+          <t>CPU/接続数/IOPSモニタリング</t>
+        </is>
+      </c>
+      <c r="G64" s="179" t="n"/>
+      <c r="H64" s="179" t="n"/>
+      <c r="I64" s="179" t="n"/>
+      <c r="J64" s="179" t="n"/>
+      <c r="K64" s="179" t="n"/>
+      <c r="L64" s="124" t="inlineStr">
         <is>
           <t>○</t>
         </is>
       </c>
-      <c r="S64" s="108" t="n"/>
-      <c r="T64" s="108" t="n"/>
-      <c r="U64" s="108" t="n"/>
-      <c r="V64" s="108" t="n"/>
-      <c r="W64" s="108" t="n"/>
+      <c r="M64" s="124" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="N64" s="179" t="n"/>
+      <c r="O64" s="179" t="n"/>
+      <c r="P64" s="179" t="n"/>
+      <c r="Q64" s="179" t="n"/>
+      <c r="R64" s="179" t="n"/>
+      <c r="S64" s="179" t="n"/>
+      <c r="T64" s="179" t="n"/>
+      <c r="U64" s="179" t="n"/>
+      <c r="V64" s="179" t="n"/>
+      <c r="W64" s="179" t="n"/>
       <c r="X64" s="84" t="n"/>
       <c r="Y64" s="84" t="n"/>
       <c r="Z64" s="84" t="n"/>
@@ -4547,17 +4485,17 @@
     <row r="65" ht="18" customHeight="1" s="80">
       <c r="A65" s="102" t="inlineStr">
         <is>
-          <t>G-4</t>
+          <t>E-6</t>
         </is>
       </c>
       <c r="B65" s="103" t="inlineStr">
         <is>
-          <t>旧シークレット削除・完了</t>
+          <t>instance-1（Writer）ダウンサイズ実施</t>
         </is>
       </c>
       <c r="C65" s="109" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="D65" s="109" t="n"/>
@@ -4566,32 +4504,32 @@
           <t>未着手</t>
         </is>
       </c>
-      <c r="F65" s="106" t="inlineStr"/>
-      <c r="G65" s="108" t="n"/>
-      <c r="H65" s="108" t="n"/>
-      <c r="I65" s="108" t="n"/>
-      <c r="J65" s="108" t="n"/>
-      <c r="K65" s="108" t="n"/>
-      <c r="L65" s="108" t="n"/>
-      <c r="M65" s="108" t="n"/>
-      <c r="N65" s="108" t="n"/>
-      <c r="O65" s="108" t="n"/>
-      <c r="P65" s="108" t="n"/>
-      <c r="Q65" s="108" t="n"/>
-      <c r="R65" s="108" t="n"/>
-      <c r="S65" s="124" t="inlineStr">
+      <c r="F65" s="106" t="inlineStr">
+        <is>
+          <t>Reader安定確認後に実施</t>
+        </is>
+      </c>
+      <c r="G65" s="179" t="n"/>
+      <c r="H65" s="179" t="n"/>
+      <c r="I65" s="179" t="n"/>
+      <c r="J65" s="179" t="n"/>
+      <c r="K65" s="179" t="n"/>
+      <c r="L65" s="179" t="n"/>
+      <c r="M65" s="179" t="n"/>
+      <c r="N65" s="124" t="inlineStr">
         <is>
           <t>○</t>
         </is>
       </c>
-      <c r="T65" s="124" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="U65" s="108" t="n"/>
-      <c r="V65" s="108" t="n"/>
-      <c r="W65" s="108" t="n"/>
+      <c r="O65" s="179" t="n"/>
+      <c r="P65" s="179" t="n"/>
+      <c r="Q65" s="179" t="n"/>
+      <c r="R65" s="179" t="n"/>
+      <c r="S65" s="179" t="n"/>
+      <c r="T65" s="179" t="n"/>
+      <c r="U65" s="179" t="n"/>
+      <c r="V65" s="179" t="n"/>
+      <c r="W65" s="179" t="n"/>
       <c r="X65" s="84" t="n"/>
       <c r="Y65" s="84" t="n"/>
       <c r="Z65" s="84" t="n"/>
@@ -4603,29 +4541,53 @@
       <c r="AF65" s="84" t="n"/>
     </row>
     <row r="66" ht="15" customHeight="1" s="80">
-      <c r="A66" s="125" t="n"/>
-      <c r="B66" s="84" t="n"/>
-      <c r="C66" s="126" t="n"/>
-      <c r="D66" s="126" t="n"/>
-      <c r="E66" s="84" t="n"/>
-      <c r="F66" s="84" t="n"/>
-      <c r="G66" s="84" t="n"/>
-      <c r="H66" s="84" t="n"/>
-      <c r="I66" s="84" t="n"/>
-      <c r="J66" s="84" t="n"/>
-      <c r="K66" s="84" t="n"/>
-      <c r="L66" s="84" t="n"/>
-      <c r="M66" s="84" t="n"/>
-      <c r="N66" s="84" t="n"/>
-      <c r="O66" s="84" t="n"/>
-      <c r="P66" s="84" t="n"/>
-      <c r="Q66" s="84" t="n"/>
-      <c r="R66" s="84" t="n"/>
-      <c r="S66" s="84" t="n"/>
-      <c r="T66" s="84" t="n"/>
-      <c r="U66" s="84" t="n"/>
-      <c r="V66" s="84" t="n"/>
-      <c r="W66" s="84" t="n"/>
+      <c r="A66" s="102" t="inlineStr">
+        <is>
+          <t>E-7</t>
+        </is>
+      </c>
+      <c r="B66" s="103" t="inlineStr">
+        <is>
+          <t>最終動作確認・完了報告</t>
+        </is>
+      </c>
+      <c r="C66" s="109" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="D66" s="109" t="n"/>
+      <c r="E66" s="105" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
+      <c r="F66" s="106" t="inlineStr">
+        <is>
+          <t>削減効果確認($1,369/月)</t>
+        </is>
+      </c>
+      <c r="G66" s="179" t="n"/>
+      <c r="H66" s="179" t="n"/>
+      <c r="I66" s="179" t="n"/>
+      <c r="J66" s="179" t="n"/>
+      <c r="K66" s="179" t="n"/>
+      <c r="L66" s="179" t="n"/>
+      <c r="M66" s="179" t="n"/>
+      <c r="N66" s="124" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="O66" s="179" t="n"/>
+      <c r="P66" s="179" t="n"/>
+      <c r="Q66" s="179" t="n"/>
+      <c r="R66" s="179" t="n"/>
+      <c r="S66" s="179" t="n"/>
+      <c r="T66" s="179" t="n"/>
+      <c r="U66" s="179" t="n"/>
+      <c r="V66" s="179" t="n"/>
+      <c r="W66" s="179" t="n"/>
       <c r="X66" s="84" t="n"/>
       <c r="Y66" s="84" t="n"/>
       <c r="Z66" s="84" t="n"/>
@@ -4637,9 +4599,9 @@
       <c r="AF66" s="84" t="n"/>
     </row>
     <row r="67" ht="20" customHeight="1" s="80">
-      <c r="A67" s="172" t="inlineStr">
-        <is>
-          <t>定期運用 — AWS月次コスト妥当性チェック</t>
+      <c r="A67" s="171" t="inlineStr">
+        <is>
+          <t>▶ ⑥ シークレット命名の改善（中長期・任意）</t>
         </is>
       </c>
       <c r="X67" s="84" t="n"/>
@@ -4653,9 +4615,30 @@
       <c r="AF67" s="84" t="n"/>
     </row>
     <row r="68" ht="18" customHeight="1" s="80">
-      <c r="A68" s="173" t="inlineStr">
-        <is>
-          <t>▶ 毎月末: CloudShellでコストデータ取得・確認（40_AWS/06_コスト調査/monthly_cost_check.sh）</t>
+      <c r="A68" s="187" t="inlineStr">
+        <is>
+          <t>G-1</t>
+        </is>
+      </c>
+      <c r="B68" s="184" t="inlineStr">
+        <is>
+          <t>影響範囲調査（全Lambda・ECS参照確認）</t>
+        </is>
+      </c>
+      <c r="C68" s="183" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="E68" s="183" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
+      <c r="F68" s="188" t="n"/>
+      <c r="P68" s="186" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="X68" s="84" t="n"/>
@@ -4669,47 +4652,43 @@
       <c r="AF68" s="84" t="n"/>
     </row>
     <row r="69" ht="18" customHeight="1" s="80">
-      <c r="A69" s="174" t="inlineStr">
-        <is>
-          <t>M-1</t>
-        </is>
-      </c>
-      <c r="B69" s="175" t="inlineStr">
-        <is>
-          <t>3月分コスト確認（4/1〜4/3実施）</t>
-        </is>
-      </c>
-      <c r="C69" s="176" t="inlineStr">
-        <is>
-          <t>2026-04-03</t>
-        </is>
-      </c>
-      <c r="D69" s="176" t="n"/>
-      <c r="E69" s="177" t="inlineStr">
+      <c r="A69" s="102" t="inlineStr">
+        <is>
+          <t>G-2</t>
+        </is>
+      </c>
+      <c r="B69" s="103" t="inlineStr">
+        <is>
+          <t>変更計画・移行手順書作成</t>
+        </is>
+      </c>
+      <c r="C69" s="109" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="D69" s="109" t="n"/>
+      <c r="E69" s="105" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
       </c>
-      <c r="F69" s="178" t="inlineStr">
-        <is>
-          <t>monthly_cost_check.sh実行・結果保存</t>
-        </is>
-      </c>
+      <c r="F69" s="106" t="inlineStr"/>
       <c r="G69" s="179" t="n"/>
       <c r="H69" s="179" t="n"/>
       <c r="I69" s="179" t="n"/>
-      <c r="J69" s="180" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
+      <c r="J69" s="179" t="n"/>
       <c r="K69" s="179" t="n"/>
       <c r="L69" s="179" t="n"/>
       <c r="M69" s="179" t="n"/>
       <c r="N69" s="179" t="n"/>
       <c r="O69" s="179" t="n"/>
       <c r="P69" s="179" t="n"/>
-      <c r="Q69" s="179" t="n"/>
+      <c r="Q69" s="124" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
       <c r="R69" s="179" t="n"/>
       <c r="S69" s="179" t="n"/>
       <c r="T69" s="179" t="n"/>
@@ -4727,32 +4706,28 @@
       <c r="AF69" s="84" t="n"/>
     </row>
     <row r="70" ht="18" customHeight="1" s="80">
-      <c r="A70" s="174" t="inlineStr">
-        <is>
-          <t>M-2</t>
-        </is>
-      </c>
-      <c r="B70" s="175" t="inlineStr">
-        <is>
-          <t>4月分コスト確認（5/1〜5/3実施）</t>
-        </is>
-      </c>
-      <c r="C70" s="181" t="inlineStr">
-        <is>
-          <t>2026-05-03</t>
-        </is>
-      </c>
-      <c r="D70" s="181" t="n"/>
-      <c r="E70" s="177" t="inlineStr">
+      <c r="A70" s="102" t="inlineStr">
+        <is>
+          <t>G-3</t>
+        </is>
+      </c>
+      <c r="B70" s="103" t="inlineStr">
+        <is>
+          <t>新シークレット作成・並行稼働確認</t>
+        </is>
+      </c>
+      <c r="C70" s="104" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="D70" s="104" t="n"/>
+      <c r="E70" s="105" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
       </c>
-      <c r="F70" s="178" t="inlineStr">
-        <is>
-          <t>monthly_cost_check.sh実行・結果保存</t>
-        </is>
-      </c>
+      <c r="F70" s="106" t="inlineStr"/>
       <c r="G70" s="179" t="n"/>
       <c r="H70" s="179" t="n"/>
       <c r="I70" s="179" t="n"/>
@@ -4760,15 +4735,15 @@
       <c r="K70" s="179" t="n"/>
       <c r="L70" s="179" t="n"/>
       <c r="M70" s="179" t="n"/>
-      <c r="N70" s="180" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
+      <c r="N70" s="179" t="n"/>
       <c r="O70" s="179" t="n"/>
       <c r="P70" s="179" t="n"/>
       <c r="Q70" s="179" t="n"/>
-      <c r="R70" s="179" t="n"/>
+      <c r="R70" s="124" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
       <c r="S70" s="179" t="n"/>
       <c r="T70" s="179" t="n"/>
       <c r="U70" s="179" t="n"/>
@@ -4785,32 +4760,28 @@
       <c r="AF70" s="84" t="n"/>
     </row>
     <row r="71" ht="18" customHeight="1" s="80">
-      <c r="A71" s="174" t="inlineStr">
-        <is>
-          <t>M-3</t>
-        </is>
-      </c>
-      <c r="B71" s="175" t="inlineStr">
-        <is>
-          <t>5月分コスト確認（6/1〜6/3実施）</t>
-        </is>
-      </c>
-      <c r="C71" s="181" t="inlineStr">
-        <is>
-          <t>2026-06-03</t>
-        </is>
-      </c>
-      <c r="D71" s="181" t="n"/>
-      <c r="E71" s="177" t="inlineStr">
+      <c r="A71" s="102" t="inlineStr">
+        <is>
+          <t>G-4</t>
+        </is>
+      </c>
+      <c r="B71" s="103" t="inlineStr">
+        <is>
+          <t>旧シークレット削除・完了</t>
+        </is>
+      </c>
+      <c r="C71" s="109" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="D71" s="109" t="n"/>
+      <c r="E71" s="105" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
       </c>
-      <c r="F71" s="178" t="inlineStr">
-        <is>
-          <t>monthly_cost_check.sh実行・結果保存</t>
-        </is>
-      </c>
+      <c r="F71" s="106" t="inlineStr"/>
       <c r="G71" s="179" t="n"/>
       <c r="H71" s="179" t="n"/>
       <c r="I71" s="179" t="n"/>
@@ -4822,13 +4793,17 @@
       <c r="O71" s="179" t="n"/>
       <c r="P71" s="179" t="n"/>
       <c r="Q71" s="179" t="n"/>
-      <c r="R71" s="180" t="inlineStr">
+      <c r="R71" s="179" t="n"/>
+      <c r="S71" s="124" t="inlineStr">
         <is>
           <t>○</t>
         </is>
       </c>
-      <c r="S71" s="179" t="n"/>
-      <c r="T71" s="179" t="n"/>
+      <c r="T71" s="124" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
       <c r="U71" s="179" t="n"/>
       <c r="V71" s="179" t="n"/>
       <c r="W71" s="179" t="n"/>
@@ -4843,53 +4818,29 @@
       <c r="AF71" s="84" t="n"/>
     </row>
     <row r="72" ht="18" customHeight="1" s="80">
-      <c r="A72" s="174" t="inlineStr">
-        <is>
-          <t>M-4</t>
-        </is>
-      </c>
-      <c r="B72" s="175" t="inlineStr">
-        <is>
-          <t>6月分コスト確認（7/1〜7/3実施）</t>
-        </is>
-      </c>
-      <c r="C72" s="176" t="inlineStr">
-        <is>
-          <t>2026-07-03</t>
-        </is>
-      </c>
-      <c r="D72" s="176" t="n"/>
-      <c r="E72" s="177" t="inlineStr">
-        <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="F72" s="178" t="inlineStr">
-        <is>
-          <t>monthly_cost_check.sh実行・結果保存</t>
-        </is>
-      </c>
-      <c r="G72" s="179" t="n"/>
-      <c r="H72" s="179" t="n"/>
-      <c r="I72" s="179" t="n"/>
-      <c r="J72" s="179" t="n"/>
-      <c r="K72" s="179" t="n"/>
-      <c r="L72" s="179" t="n"/>
-      <c r="M72" s="179" t="n"/>
-      <c r="N72" s="179" t="n"/>
-      <c r="O72" s="179" t="n"/>
-      <c r="P72" s="179" t="n"/>
-      <c r="Q72" s="179" t="n"/>
-      <c r="R72" s="179" t="n"/>
-      <c r="S72" s="179" t="n"/>
-      <c r="T72" s="179" t="n"/>
-      <c r="U72" s="179" t="n"/>
-      <c r="V72" s="179" t="n"/>
-      <c r="W72" s="180" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
+      <c r="A72" s="125" t="n"/>
+      <c r="B72" s="84" t="n"/>
+      <c r="C72" s="126" t="n"/>
+      <c r="D72" s="126" t="n"/>
+      <c r="E72" s="84" t="n"/>
+      <c r="F72" s="84" t="n"/>
+      <c r="G72" s="84" t="n"/>
+      <c r="H72" s="84" t="n"/>
+      <c r="I72" s="84" t="n"/>
+      <c r="J72" s="84" t="n"/>
+      <c r="K72" s="84" t="n"/>
+      <c r="L72" s="84" t="n"/>
+      <c r="M72" s="84" t="n"/>
+      <c r="N72" s="84" t="n"/>
+      <c r="O72" s="84" t="n"/>
+      <c r="P72" s="84" t="n"/>
+      <c r="Q72" s="84" t="n"/>
+      <c r="R72" s="84" t="n"/>
+      <c r="S72" s="84" t="n"/>
+      <c r="T72" s="84" t="n"/>
+      <c r="U72" s="84" t="n"/>
+      <c r="V72" s="84" t="n"/>
+      <c r="W72" s="84" t="n"/>
       <c r="X72" s="84" t="n"/>
       <c r="Y72" s="84" t="n"/>
       <c r="Z72" s="84" t="n"/>
@@ -4901,9 +4852,9 @@
       <c r="AF72" s="84" t="n"/>
     </row>
     <row r="73" ht="18" customHeight="1" s="80">
-      <c r="A73" s="173" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  確認項目: ①月間合計 ②サービス別内訳 ③RDS CPU/接続数 ④Lambda実行回数・エラー ⑤S3使用量 ⑥前月比</t>
+      <c r="A73" s="172" t="inlineStr">
+        <is>
+          <t>定期運用 — AWS月次コスト妥当性チェック</t>
         </is>
       </c>
       <c r="X73" s="84" t="n"/>
@@ -4917,29 +4868,11 @@
       <c r="AF73" s="84" t="n"/>
     </row>
     <row r="74" ht="16.5" customHeight="1" s="80">
-      <c r="A74" s="125" t="n"/>
-      <c r="B74" s="84" t="n"/>
-      <c r="C74" s="126" t="n"/>
-      <c r="D74" s="126" t="n"/>
-      <c r="E74" s="84" t="n"/>
-      <c r="F74" s="84" t="n"/>
-      <c r="G74" s="84" t="n"/>
-      <c r="H74" s="84" t="n"/>
-      <c r="I74" s="84" t="n"/>
-      <c r="J74" s="84" t="n"/>
-      <c r="K74" s="84" t="n"/>
-      <c r="L74" s="84" t="n"/>
-      <c r="M74" s="84" t="n"/>
-      <c r="N74" s="84" t="n"/>
-      <c r="O74" s="84" t="n"/>
-      <c r="P74" s="84" t="n"/>
-      <c r="Q74" s="84" t="n"/>
-      <c r="R74" s="84" t="n"/>
-      <c r="S74" s="84" t="n"/>
-      <c r="T74" s="84" t="n"/>
-      <c r="U74" s="84" t="n"/>
-      <c r="V74" s="84" t="n"/>
-      <c r="W74" s="84" t="n"/>
+      <c r="A74" s="173" t="inlineStr">
+        <is>
+          <t>▶ 毎月末: CloudShellでコストデータ取得・確認（40_AWS/06_コスト調査/monthly_cost_check.sh）</t>
+        </is>
+      </c>
       <c r="X74" s="84" t="n"/>
       <c r="Y74" s="84" t="n"/>
       <c r="Z74" s="84" t="n"/>
@@ -4951,29 +4884,53 @@
       <c r="AF74" s="84" t="n"/>
     </row>
     <row r="75" ht="16.5" customHeight="1" s="80">
-      <c r="A75" s="125" t="n"/>
-      <c r="B75" s="84" t="n"/>
-      <c r="C75" s="126" t="n"/>
-      <c r="D75" s="126" t="n"/>
-      <c r="E75" s="84" t="n"/>
-      <c r="F75" s="84" t="n"/>
-      <c r="G75" s="84" t="n"/>
-      <c r="H75" s="84" t="n"/>
-      <c r="I75" s="84" t="n"/>
-      <c r="J75" s="84" t="n"/>
-      <c r="K75" s="84" t="n"/>
-      <c r="L75" s="84" t="n"/>
-      <c r="M75" s="84" t="n"/>
-      <c r="N75" s="84" t="n"/>
-      <c r="O75" s="84" t="n"/>
-      <c r="P75" s="84" t="n"/>
-      <c r="Q75" s="84" t="n"/>
-      <c r="R75" s="84" t="n"/>
-      <c r="S75" s="84" t="n"/>
-      <c r="T75" s="84" t="n"/>
-      <c r="U75" s="84" t="n"/>
-      <c r="V75" s="84" t="n"/>
-      <c r="W75" s="84" t="n"/>
+      <c r="A75" s="174" t="inlineStr">
+        <is>
+          <t>M-1</t>
+        </is>
+      </c>
+      <c r="B75" s="175" t="inlineStr">
+        <is>
+          <t>3月分コスト確認（4/1〜4/3実施）</t>
+        </is>
+      </c>
+      <c r="C75" s="176" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="D75" s="176" t="n"/>
+      <c r="E75" s="177" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
+      <c r="F75" s="178" t="inlineStr">
+        <is>
+          <t>monthly_cost_check.sh実行・結果保存</t>
+        </is>
+      </c>
+      <c r="G75" s="179" t="n"/>
+      <c r="H75" s="179" t="n"/>
+      <c r="I75" s="179" t="n"/>
+      <c r="J75" s="180" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="K75" s="179" t="n"/>
+      <c r="L75" s="179" t="n"/>
+      <c r="M75" s="179" t="n"/>
+      <c r="N75" s="179" t="n"/>
+      <c r="O75" s="179" t="n"/>
+      <c r="P75" s="179" t="n"/>
+      <c r="Q75" s="179" t="n"/>
+      <c r="R75" s="179" t="n"/>
+      <c r="S75" s="179" t="n"/>
+      <c r="T75" s="179" t="n"/>
+      <c r="U75" s="179" t="n"/>
+      <c r="V75" s="179" t="n"/>
+      <c r="W75" s="179" t="n"/>
       <c r="X75" s="84" t="n"/>
       <c r="Y75" s="84" t="n"/>
       <c r="Z75" s="84" t="n"/>
@@ -4985,29 +4942,53 @@
       <c r="AF75" s="84" t="n"/>
     </row>
     <row r="76" ht="16.5" customHeight="1" s="80">
-      <c r="A76" s="125" t="n"/>
-      <c r="B76" s="84" t="n"/>
-      <c r="C76" s="126" t="n"/>
-      <c r="D76" s="126" t="n"/>
-      <c r="E76" s="84" t="n"/>
-      <c r="F76" s="84" t="n"/>
-      <c r="G76" s="84" t="n"/>
-      <c r="H76" s="84" t="n"/>
-      <c r="I76" s="84" t="n"/>
-      <c r="J76" s="84" t="n"/>
-      <c r="K76" s="84" t="n"/>
-      <c r="L76" s="84" t="n"/>
-      <c r="M76" s="84" t="n"/>
-      <c r="N76" s="84" t="n"/>
-      <c r="O76" s="84" t="n"/>
-      <c r="P76" s="84" t="n"/>
-      <c r="Q76" s="84" t="n"/>
-      <c r="R76" s="84" t="n"/>
-      <c r="S76" s="84" t="n"/>
-      <c r="T76" s="84" t="n"/>
-      <c r="U76" s="84" t="n"/>
-      <c r="V76" s="84" t="n"/>
-      <c r="W76" s="84" t="n"/>
+      <c r="A76" s="174" t="inlineStr">
+        <is>
+          <t>M-2</t>
+        </is>
+      </c>
+      <c r="B76" s="175" t="inlineStr">
+        <is>
+          <t>4月分コスト確認（5/1〜5/3実施）</t>
+        </is>
+      </c>
+      <c r="C76" s="181" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="D76" s="181" t="n"/>
+      <c r="E76" s="177" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
+      <c r="F76" s="178" t="inlineStr">
+        <is>
+          <t>monthly_cost_check.sh実行・結果保存</t>
+        </is>
+      </c>
+      <c r="G76" s="179" t="n"/>
+      <c r="H76" s="179" t="n"/>
+      <c r="I76" s="179" t="n"/>
+      <c r="J76" s="179" t="n"/>
+      <c r="K76" s="179" t="n"/>
+      <c r="L76" s="179" t="n"/>
+      <c r="M76" s="179" t="n"/>
+      <c r="N76" s="180" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="O76" s="179" t="n"/>
+      <c r="P76" s="179" t="n"/>
+      <c r="Q76" s="179" t="n"/>
+      <c r="R76" s="179" t="n"/>
+      <c r="S76" s="179" t="n"/>
+      <c r="T76" s="179" t="n"/>
+      <c r="U76" s="179" t="n"/>
+      <c r="V76" s="179" t="n"/>
+      <c r="W76" s="179" t="n"/>
       <c r="X76" s="84" t="n"/>
       <c r="Y76" s="84" t="n"/>
       <c r="Z76" s="84" t="n"/>
@@ -5019,29 +5000,53 @@
       <c r="AF76" s="84" t="n"/>
     </row>
     <row r="77" ht="16.5" customHeight="1" s="80">
-      <c r="A77" s="125" t="n"/>
-      <c r="B77" s="84" t="n"/>
-      <c r="C77" s="126" t="n"/>
-      <c r="D77" s="126" t="n"/>
-      <c r="E77" s="84" t="n"/>
-      <c r="F77" s="84" t="n"/>
-      <c r="G77" s="84" t="n"/>
-      <c r="H77" s="84" t="n"/>
-      <c r="I77" s="84" t="n"/>
-      <c r="J77" s="84" t="n"/>
-      <c r="K77" s="84" t="n"/>
-      <c r="L77" s="84" t="n"/>
-      <c r="M77" s="84" t="n"/>
-      <c r="N77" s="84" t="n"/>
-      <c r="O77" s="84" t="n"/>
-      <c r="P77" s="84" t="n"/>
-      <c r="Q77" s="84" t="n"/>
-      <c r="R77" s="84" t="n"/>
-      <c r="S77" s="84" t="n"/>
-      <c r="T77" s="84" t="n"/>
-      <c r="U77" s="84" t="n"/>
-      <c r="V77" s="84" t="n"/>
-      <c r="W77" s="84" t="n"/>
+      <c r="A77" s="174" t="inlineStr">
+        <is>
+          <t>M-3</t>
+        </is>
+      </c>
+      <c r="B77" s="175" t="inlineStr">
+        <is>
+          <t>5月分コスト確認（6/1〜6/3実施）</t>
+        </is>
+      </c>
+      <c r="C77" s="181" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="D77" s="181" t="n"/>
+      <c r="E77" s="177" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
+      <c r="F77" s="178" t="inlineStr">
+        <is>
+          <t>monthly_cost_check.sh実行・結果保存</t>
+        </is>
+      </c>
+      <c r="G77" s="179" t="n"/>
+      <c r="H77" s="179" t="n"/>
+      <c r="I77" s="179" t="n"/>
+      <c r="J77" s="179" t="n"/>
+      <c r="K77" s="179" t="n"/>
+      <c r="L77" s="179" t="n"/>
+      <c r="M77" s="179" t="n"/>
+      <c r="N77" s="179" t="n"/>
+      <c r="O77" s="179" t="n"/>
+      <c r="P77" s="179" t="n"/>
+      <c r="Q77" s="179" t="n"/>
+      <c r="R77" s="180" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="S77" s="179" t="n"/>
+      <c r="T77" s="179" t="n"/>
+      <c r="U77" s="179" t="n"/>
+      <c r="V77" s="179" t="n"/>
+      <c r="W77" s="179" t="n"/>
       <c r="X77" s="84" t="n"/>
       <c r="Y77" s="84" t="n"/>
       <c r="Z77" s="84" t="n"/>
@@ -5053,29 +5058,53 @@
       <c r="AF77" s="84" t="n"/>
     </row>
     <row r="78" ht="19.5" customHeight="1" s="80">
-      <c r="A78" s="125" t="n"/>
-      <c r="B78" s="84" t="n"/>
-      <c r="C78" s="84" t="n"/>
-      <c r="D78" s="84" t="n"/>
-      <c r="E78" s="84" t="n"/>
-      <c r="F78" s="84" t="n"/>
-      <c r="G78" s="84" t="n"/>
-      <c r="H78" s="84" t="n"/>
-      <c r="I78" s="84" t="n"/>
-      <c r="J78" s="84" t="n"/>
-      <c r="K78" s="84" t="n"/>
-      <c r="L78" s="84" t="n"/>
-      <c r="M78" s="84" t="n"/>
-      <c r="N78" s="84" t="n"/>
-      <c r="O78" s="84" t="n"/>
-      <c r="P78" s="84" t="n"/>
-      <c r="Q78" s="84" t="n"/>
-      <c r="R78" s="84" t="n"/>
-      <c r="S78" s="84" t="n"/>
-      <c r="T78" s="84" t="n"/>
-      <c r="U78" s="84" t="n"/>
-      <c r="V78" s="84" t="n"/>
-      <c r="W78" s="84" t="n"/>
+      <c r="A78" s="174" t="inlineStr">
+        <is>
+          <t>M-4</t>
+        </is>
+      </c>
+      <c r="B78" s="175" t="inlineStr">
+        <is>
+          <t>6月分コスト確認（7/1〜7/3実施）</t>
+        </is>
+      </c>
+      <c r="C78" s="176" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="D78" s="176" t="n"/>
+      <c r="E78" s="177" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
+      <c r="F78" s="178" t="inlineStr">
+        <is>
+          <t>monthly_cost_check.sh実行・結果保存</t>
+        </is>
+      </c>
+      <c r="G78" s="179" t="n"/>
+      <c r="H78" s="179" t="n"/>
+      <c r="I78" s="179" t="n"/>
+      <c r="J78" s="179" t="n"/>
+      <c r="K78" s="179" t="n"/>
+      <c r="L78" s="179" t="n"/>
+      <c r="M78" s="179" t="n"/>
+      <c r="N78" s="179" t="n"/>
+      <c r="O78" s="179" t="n"/>
+      <c r="P78" s="179" t="n"/>
+      <c r="Q78" s="179" t="n"/>
+      <c r="R78" s="179" t="n"/>
+      <c r="S78" s="179" t="n"/>
+      <c r="T78" s="179" t="n"/>
+      <c r="U78" s="179" t="n"/>
+      <c r="V78" s="179" t="n"/>
+      <c r="W78" s="180" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
       <c r="X78" s="84" t="n"/>
       <c r="Y78" s="84" t="n"/>
       <c r="Z78" s="84" t="n"/>
@@ -5087,29 +5116,11 @@
       <c r="AF78" s="84" t="n"/>
     </row>
     <row r="79" ht="16.5" customHeight="1" s="80">
-      <c r="A79" s="125" t="n"/>
-      <c r="B79" s="84" t="n"/>
-      <c r="C79" s="84" t="n"/>
-      <c r="D79" s="84" t="n"/>
-      <c r="E79" s="84" t="n"/>
-      <c r="F79" s="84" t="n"/>
-      <c r="G79" s="84" t="n"/>
-      <c r="H79" s="84" t="n"/>
-      <c r="I79" s="84" t="n"/>
-      <c r="J79" s="84" t="n"/>
-      <c r="K79" s="84" t="n"/>
-      <c r="L79" s="84" t="n"/>
-      <c r="M79" s="84" t="n"/>
-      <c r="N79" s="84" t="n"/>
-      <c r="O79" s="84" t="n"/>
-      <c r="P79" s="84" t="n"/>
-      <c r="Q79" s="84" t="n"/>
-      <c r="R79" s="84" t="n"/>
-      <c r="S79" s="84" t="n"/>
-      <c r="T79" s="84" t="n"/>
-      <c r="U79" s="84" t="n"/>
-      <c r="V79" s="84" t="n"/>
-      <c r="W79" s="84" t="n"/>
+      <c r="A79" s="173" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  確認項目: ①月間合計 ②サービス別内訳 ③RDS CPU/接続数 ④Lambda実行回数・エラー ⑤S3使用量 ⑥前月比</t>
+        </is>
+      </c>
       <c r="X79" s="84" t="n"/>
       <c r="Y79" s="84" t="n"/>
       <c r="Z79" s="84" t="n"/>
@@ -5259,8 +5270,8 @@
     <row r="84" ht="16.5" customHeight="1" s="80">
       <c r="A84" s="125" t="n"/>
       <c r="B84" s="84" t="n"/>
-      <c r="C84" s="126" t="n"/>
-      <c r="D84" s="126" t="n"/>
+      <c r="C84" s="84" t="n"/>
+      <c r="D84" s="84" t="n"/>
       <c r="E84" s="84" t="n"/>
       <c r="F84" s="84" t="n"/>
       <c r="G84" s="84" t="n"/>
@@ -5293,8 +5304,8 @@
     <row r="85" ht="24" customHeight="1" s="80">
       <c r="A85" s="125" t="n"/>
       <c r="B85" s="84" t="n"/>
-      <c r="C85" s="126" t="n"/>
-      <c r="D85" s="126" t="n"/>
+      <c r="C85" s="84" t="n"/>
+      <c r="D85" s="84" t="n"/>
       <c r="E85" s="84" t="n"/>
       <c r="F85" s="84" t="n"/>
       <c r="G85" s="84" t="n"/>
@@ -5361,8 +5372,8 @@
     <row r="87" ht="15.75" customHeight="1" s="80">
       <c r="A87" s="125" t="n"/>
       <c r="B87" s="84" t="n"/>
-      <c r="C87" s="84" t="n"/>
-      <c r="D87" s="84" t="n"/>
+      <c r="C87" s="126" t="n"/>
+      <c r="D87" s="126" t="n"/>
       <c r="E87" s="84" t="n"/>
       <c r="F87" s="84" t="n"/>
       <c r="G87" s="84" t="n"/>
@@ -5565,8 +5576,8 @@
     <row r="93" ht="16.5" customHeight="1" s="80">
       <c r="A93" s="125" t="n"/>
       <c r="B93" s="84" t="n"/>
-      <c r="C93" s="126" t="n"/>
-      <c r="D93" s="126" t="n"/>
+      <c r="C93" s="84" t="n"/>
+      <c r="D93" s="84" t="n"/>
       <c r="E93" s="84" t="n"/>
       <c r="F93" s="84" t="n"/>
       <c r="G93" s="84" t="n"/>
@@ -5701,8 +5712,8 @@
     <row r="97" ht="15.75" customHeight="1" s="80">
       <c r="A97" s="125" t="n"/>
       <c r="B97" s="84" t="n"/>
-      <c r="C97" s="84" t="n"/>
-      <c r="D97" s="84" t="n"/>
+      <c r="C97" s="126" t="n"/>
+      <c r="D97" s="126" t="n"/>
       <c r="E97" s="84" t="n"/>
       <c r="F97" s="84" t="n"/>
       <c r="G97" s="84" t="n"/>
@@ -5905,8 +5916,8 @@
     <row r="103" ht="16.5" customHeight="1" s="80">
       <c r="A103" s="125" t="n"/>
       <c r="B103" s="84" t="n"/>
-      <c r="C103" s="126" t="n"/>
-      <c r="D103" s="126" t="n"/>
+      <c r="C103" s="84" t="n"/>
+      <c r="D103" s="84" t="n"/>
       <c r="E103" s="84" t="n"/>
       <c r="F103" s="84" t="n"/>
       <c r="G103" s="84" t="n"/>
@@ -6041,8 +6052,8 @@
     <row r="107" ht="15.75" customHeight="1" s="80">
       <c r="A107" s="125" t="n"/>
       <c r="B107" s="84" t="n"/>
-      <c r="C107" s="84" t="n"/>
-      <c r="D107" s="84" t="n"/>
+      <c r="C107" s="126" t="n"/>
+      <c r="D107" s="126" t="n"/>
       <c r="E107" s="84" t="n"/>
       <c r="F107" s="84" t="n"/>
       <c r="G107" s="84" t="n"/>
@@ -6245,8 +6256,8 @@
     <row r="113" ht="16.5" customHeight="1" s="80">
       <c r="A113" s="125" t="n"/>
       <c r="B113" s="84" t="n"/>
-      <c r="C113" s="126" t="n"/>
-      <c r="D113" s="126" t="n"/>
+      <c r="C113" s="84" t="n"/>
+      <c r="D113" s="84" t="n"/>
       <c r="E113" s="84" t="n"/>
       <c r="F113" s="84" t="n"/>
       <c r="G113" s="84" t="n"/>
@@ -6381,8 +6392,8 @@
     <row r="117" ht="15.75" customHeight="1" s="80">
       <c r="A117" s="125" t="n"/>
       <c r="B117" s="84" t="n"/>
-      <c r="C117" s="84" t="n"/>
-      <c r="D117" s="84" t="n"/>
+      <c r="C117" s="126" t="n"/>
+      <c r="D117" s="126" t="n"/>
       <c r="E117" s="84" t="n"/>
       <c r="F117" s="84" t="n"/>
       <c r="G117" s="84" t="n"/>
@@ -6585,8 +6596,8 @@
     <row r="123" ht="16.5" customHeight="1" s="80">
       <c r="A123" s="125" t="n"/>
       <c r="B123" s="84" t="n"/>
-      <c r="C123" s="126" t="n"/>
-      <c r="D123" s="126" t="n"/>
+      <c r="C123" s="84" t="n"/>
+      <c r="D123" s="84" t="n"/>
       <c r="E123" s="84" t="n"/>
       <c r="F123" s="84" t="n"/>
       <c r="G123" s="84" t="n"/>
@@ -6721,8 +6732,8 @@
     <row r="127" ht="15.75" customHeight="1" s="80">
       <c r="A127" s="125" t="n"/>
       <c r="B127" s="84" t="n"/>
-      <c r="C127" s="84" t="n"/>
-      <c r="D127" s="84" t="n"/>
+      <c r="C127" s="126" t="n"/>
+      <c r="D127" s="126" t="n"/>
       <c r="E127" s="84" t="n"/>
       <c r="F127" s="84" t="n"/>
       <c r="G127" s="84" t="n"/>
@@ -6925,8 +6936,8 @@
     <row r="133" ht="16.5" customHeight="1" s="80">
       <c r="A133" s="125" t="n"/>
       <c r="B133" s="84" t="n"/>
-      <c r="C133" s="126" t="n"/>
-      <c r="D133" s="126" t="n"/>
+      <c r="C133" s="84" t="n"/>
+      <c r="D133" s="84" t="n"/>
       <c r="E133" s="84" t="n"/>
       <c r="F133" s="84" t="n"/>
       <c r="G133" s="84" t="n"/>
@@ -7061,8 +7072,8 @@
     <row r="137" ht="15.75" customHeight="1" s="80">
       <c r="A137" s="125" t="n"/>
       <c r="B137" s="84" t="n"/>
-      <c r="C137" s="84" t="n"/>
-      <c r="D137" s="84" t="n"/>
+      <c r="C137" s="126" t="n"/>
+      <c r="D137" s="126" t="n"/>
       <c r="E137" s="84" t="n"/>
       <c r="F137" s="84" t="n"/>
       <c r="G137" s="84" t="n"/>
@@ -7265,8 +7276,8 @@
     <row r="143" ht="16.5" customHeight="1" s="80">
       <c r="A143" s="125" t="n"/>
       <c r="B143" s="84" t="n"/>
-      <c r="C143" s="126" t="n"/>
-      <c r="D143" s="126" t="n"/>
+      <c r="C143" s="84" t="n"/>
+      <c r="D143" s="84" t="n"/>
       <c r="E143" s="84" t="n"/>
       <c r="F143" s="84" t="n"/>
       <c r="G143" s="84" t="n"/>
@@ -7401,8 +7412,8 @@
     <row r="147" ht="15.75" customHeight="1" s="80">
       <c r="A147" s="125" t="n"/>
       <c r="B147" s="84" t="n"/>
-      <c r="C147" s="84" t="n"/>
-      <c r="D147" s="84" t="n"/>
+      <c r="C147" s="126" t="n"/>
+      <c r="D147" s="126" t="n"/>
       <c r="E147" s="84" t="n"/>
       <c r="F147" s="84" t="n"/>
       <c r="G147" s="84" t="n"/>
@@ -7605,8 +7616,8 @@
     <row r="153" ht="16.5" customHeight="1" s="80">
       <c r="A153" s="125" t="n"/>
       <c r="B153" s="84" t="n"/>
-      <c r="C153" s="126" t="n"/>
-      <c r="D153" s="126" t="n"/>
+      <c r="C153" s="84" t="n"/>
+      <c r="D153" s="84" t="n"/>
       <c r="E153" s="84" t="n"/>
       <c r="F153" s="84" t="n"/>
       <c r="G153" s="84" t="n"/>
@@ -7741,8 +7752,8 @@
     <row r="157" ht="15.75" customHeight="1" s="80">
       <c r="A157" s="125" t="n"/>
       <c r="B157" s="84" t="n"/>
-      <c r="C157" s="84" t="n"/>
-      <c r="D157" s="84" t="n"/>
+      <c r="C157" s="126" t="n"/>
+      <c r="D157" s="126" t="n"/>
       <c r="E157" s="84" t="n"/>
       <c r="F157" s="84" t="n"/>
       <c r="G157" s="84" t="n"/>
@@ -7945,8 +7956,8 @@
     <row r="163" ht="16.5" customHeight="1" s="80">
       <c r="A163" s="125" t="n"/>
       <c r="B163" s="84" t="n"/>
-      <c r="C163" s="126" t="n"/>
-      <c r="D163" s="126" t="n"/>
+      <c r="C163" s="84" t="n"/>
+      <c r="D163" s="84" t="n"/>
       <c r="E163" s="84" t="n"/>
       <c r="F163" s="84" t="n"/>
       <c r="G163" s="84" t="n"/>
@@ -8081,8 +8092,8 @@
     <row r="167" ht="15.75" customHeight="1" s="80">
       <c r="A167" s="125" t="n"/>
       <c r="B167" s="84" t="n"/>
-      <c r="C167" s="84" t="n"/>
-      <c r="D167" s="84" t="n"/>
+      <c r="C167" s="126" t="n"/>
+      <c r="D167" s="126" t="n"/>
       <c r="E167" s="84" t="n"/>
       <c r="F167" s="84" t="n"/>
       <c r="G167" s="84" t="n"/>
@@ -8285,8 +8296,8 @@
     <row r="173" ht="16.5" customHeight="1" s="80">
       <c r="A173" s="125" t="n"/>
       <c r="B173" s="84" t="n"/>
-      <c r="C173" s="126" t="n"/>
-      <c r="D173" s="126" t="n"/>
+      <c r="C173" s="84" t="n"/>
+      <c r="D173" s="84" t="n"/>
       <c r="E173" s="84" t="n"/>
       <c r="F173" s="84" t="n"/>
       <c r="G173" s="84" t="n"/>
@@ -8421,8 +8432,8 @@
     <row r="177" ht="15.75" customHeight="1" s="80">
       <c r="A177" s="125" t="n"/>
       <c r="B177" s="84" t="n"/>
-      <c r="C177" s="84" t="n"/>
-      <c r="D177" s="84" t="n"/>
+      <c r="C177" s="126" t="n"/>
+      <c r="D177" s="126" t="n"/>
       <c r="E177" s="84" t="n"/>
       <c r="F177" s="84" t="n"/>
       <c r="G177" s="84" t="n"/>
@@ -8625,8 +8636,8 @@
     <row r="183" ht="16.5" customHeight="1" s="80">
       <c r="A183" s="125" t="n"/>
       <c r="B183" s="84" t="n"/>
-      <c r="C183" s="126" t="n"/>
-      <c r="D183" s="126" t="n"/>
+      <c r="C183" s="84" t="n"/>
+      <c r="D183" s="84" t="n"/>
       <c r="E183" s="84" t="n"/>
       <c r="F183" s="84" t="n"/>
       <c r="G183" s="84" t="n"/>
@@ -8761,8 +8772,8 @@
     <row r="187" ht="15.75" customHeight="1" s="80">
       <c r="A187" s="125" t="n"/>
       <c r="B187" s="84" t="n"/>
-      <c r="C187" s="84" t="n"/>
-      <c r="D187" s="84" t="n"/>
+      <c r="C187" s="126" t="n"/>
+      <c r="D187" s="126" t="n"/>
       <c r="E187" s="84" t="n"/>
       <c r="F187" s="84" t="n"/>
       <c r="G187" s="84" t="n"/>
@@ -8965,8 +8976,8 @@
     <row r="193" ht="16.5" customHeight="1" s="80">
       <c r="A193" s="125" t="n"/>
       <c r="B193" s="84" t="n"/>
-      <c r="C193" s="126" t="n"/>
-      <c r="D193" s="126" t="n"/>
+      <c r="C193" s="84" t="n"/>
+      <c r="D193" s="84" t="n"/>
       <c r="E193" s="84" t="n"/>
       <c r="F193" s="84" t="n"/>
       <c r="G193" s="84" t="n"/>
@@ -9101,8 +9112,8 @@
     <row r="197" ht="15.75" customHeight="1" s="80">
       <c r="A197" s="125" t="n"/>
       <c r="B197" s="84" t="n"/>
-      <c r="C197" s="84" t="n"/>
-      <c r="D197" s="84" t="n"/>
+      <c r="C197" s="126" t="n"/>
+      <c r="D197" s="126" t="n"/>
       <c r="E197" s="84" t="n"/>
       <c r="F197" s="84" t="n"/>
       <c r="G197" s="84" t="n"/>
@@ -9305,8 +9316,8 @@
     <row r="203" ht="16.5" customHeight="1" s="80">
       <c r="A203" s="125" t="n"/>
       <c r="B203" s="84" t="n"/>
-      <c r="C203" s="126" t="n"/>
-      <c r="D203" s="126" t="n"/>
+      <c r="C203" s="84" t="n"/>
+      <c r="D203" s="84" t="n"/>
       <c r="E203" s="84" t="n"/>
       <c r="F203" s="84" t="n"/>
       <c r="G203" s="84" t="n"/>
@@ -9441,8 +9452,8 @@
     <row r="207" ht="15.75" customHeight="1" s="80">
       <c r="A207" s="125" t="n"/>
       <c r="B207" s="84" t="n"/>
-      <c r="C207" s="84" t="n"/>
-      <c r="D207" s="84" t="n"/>
+      <c r="C207" s="126" t="n"/>
+      <c r="D207" s="126" t="n"/>
       <c r="E207" s="84" t="n"/>
       <c r="F207" s="84" t="n"/>
       <c r="G207" s="84" t="n"/>
@@ -9645,8 +9656,8 @@
     <row r="213" ht="16.5" customHeight="1" s="80">
       <c r="A213" s="125" t="n"/>
       <c r="B213" s="84" t="n"/>
-      <c r="C213" s="126" t="n"/>
-      <c r="D213" s="126" t="n"/>
+      <c r="C213" s="84" t="n"/>
+      <c r="D213" s="84" t="n"/>
       <c r="E213" s="84" t="n"/>
       <c r="F213" s="84" t="n"/>
       <c r="G213" s="84" t="n"/>
@@ -9781,8 +9792,8 @@
     <row r="217" ht="15.75" customHeight="1" s="80">
       <c r="A217" s="125" t="n"/>
       <c r="B217" s="84" t="n"/>
-      <c r="C217" s="84" t="n"/>
-      <c r="D217" s="84" t="n"/>
+      <c r="C217" s="126" t="n"/>
+      <c r="D217" s="126" t="n"/>
       <c r="E217" s="84" t="n"/>
       <c r="F217" s="84" t="n"/>
       <c r="G217" s="84" t="n"/>
@@ -9985,8 +9996,8 @@
     <row r="223" ht="16.5" customHeight="1" s="80">
       <c r="A223" s="125" t="n"/>
       <c r="B223" s="84" t="n"/>
-      <c r="C223" s="126" t="n"/>
-      <c r="D223" s="126" t="n"/>
+      <c r="C223" s="84" t="n"/>
+      <c r="D223" s="84" t="n"/>
       <c r="E223" s="84" t="n"/>
       <c r="F223" s="84" t="n"/>
       <c r="G223" s="84" t="n"/>
@@ -10087,8 +10098,8 @@
     <row r="226" ht="16.5" customHeight="1" s="80">
       <c r="A226" s="125" t="n"/>
       <c r="B226" s="84" t="n"/>
-      <c r="C226" s="84" t="n"/>
-      <c r="D226" s="84" t="n"/>
+      <c r="C226" s="126" t="n"/>
+      <c r="D226" s="126" t="n"/>
       <c r="E226" s="84" t="n"/>
       <c r="F226" s="84" t="n"/>
       <c r="G226" s="84" t="n"/>
@@ -10121,8 +10132,8 @@
     <row r="227" ht="16.5" customHeight="1" s="80">
       <c r="A227" s="125" t="n"/>
       <c r="B227" s="84" t="n"/>
-      <c r="C227" s="84" t="n"/>
-      <c r="D227" s="84" t="n"/>
+      <c r="C227" s="126" t="n"/>
+      <c r="D227" s="126" t="n"/>
       <c r="E227" s="84" t="n"/>
       <c r="F227" s="84" t="n"/>
       <c r="G227" s="84" t="n"/>
@@ -10223,8 +10234,8 @@
     <row r="230" ht="19.5" customHeight="1" s="80">
       <c r="A230" s="125" t="n"/>
       <c r="B230" s="84" t="n"/>
-      <c r="C230" s="84" t="n"/>
-      <c r="D230" s="84" t="n"/>
+      <c r="C230" s="126" t="n"/>
+      <c r="D230" s="126" t="n"/>
       <c r="E230" s="84" t="n"/>
       <c r="F230" s="84" t="n"/>
       <c r="G230" s="84" t="n"/>
@@ -10257,8 +10268,8 @@
     <row r="231" ht="19.5" customHeight="1" s="80">
       <c r="A231" s="125" t="n"/>
       <c r="B231" s="84" t="n"/>
-      <c r="C231" s="84" t="n"/>
-      <c r="D231" s="84" t="n"/>
+      <c r="C231" s="126" t="n"/>
+      <c r="D231" s="126" t="n"/>
       <c r="E231" s="84" t="n"/>
       <c r="F231" s="84" t="n"/>
       <c r="G231" s="84" t="n"/>
@@ -10291,8 +10302,8 @@
     <row r="232" ht="16.5" customHeight="1" s="80">
       <c r="A232" s="125" t="n"/>
       <c r="B232" s="84" t="n"/>
-      <c r="C232" s="126" t="n"/>
-      <c r="D232" s="126" t="n"/>
+      <c r="C232" s="84" t="n"/>
+      <c r="D232" s="84" t="n"/>
       <c r="E232" s="84" t="n"/>
       <c r="F232" s="84" t="n"/>
       <c r="G232" s="84" t="n"/>
@@ -10325,8 +10336,8 @@
     <row r="233" ht="16.5" customHeight="1" s="80">
       <c r="A233" s="125" t="n"/>
       <c r="B233" s="84" t="n"/>
-      <c r="C233" s="126" t="n"/>
-      <c r="D233" s="126" t="n"/>
+      <c r="C233" s="84" t="n"/>
+      <c r="D233" s="84" t="n"/>
       <c r="E233" s="84" t="n"/>
       <c r="F233" s="84" t="n"/>
       <c r="G233" s="84" t="n"/>
@@ -10427,8 +10438,8 @@
     <row r="236" ht="16.5" customHeight="1" s="80">
       <c r="A236" s="125" t="n"/>
       <c r="B236" s="84" t="n"/>
-      <c r="C236" s="126" t="n"/>
-      <c r="D236" s="126" t="n"/>
+      <c r="C236" s="84" t="n"/>
+      <c r="D236" s="84" t="n"/>
       <c r="E236" s="84" t="n"/>
       <c r="F236" s="84" t="n"/>
       <c r="G236" s="84" t="n"/>
@@ -10665,8 +10676,8 @@
     <row r="243" ht="16.5" customHeight="1" s="80">
       <c r="A243" s="125" t="n"/>
       <c r="B243" s="84" t="n"/>
-      <c r="C243" s="126" t="n"/>
-      <c r="D243" s="126" t="n"/>
+      <c r="C243" s="84" t="n"/>
+      <c r="D243" s="84" t="n"/>
       <c r="E243" s="84" t="n"/>
       <c r="F243" s="84" t="n"/>
       <c r="G243" s="84" t="n"/>
@@ -10699,8 +10710,8 @@
     <row r="244" ht="16.5" customHeight="1" s="80">
       <c r="A244" s="125" t="n"/>
       <c r="B244" s="84" t="n"/>
-      <c r="C244" s="84" t="n"/>
-      <c r="D244" s="84" t="n"/>
+      <c r="C244" s="126" t="n"/>
+      <c r="D244" s="126" t="n"/>
       <c r="E244" s="84" t="n"/>
       <c r="F244" s="84" t="n"/>
       <c r="G244" s="84" t="n"/>
@@ -10903,8 +10914,8 @@
     <row r="250" ht="15.75" customHeight="1" s="80">
       <c r="A250" s="125" t="n"/>
       <c r="B250" s="84" t="n"/>
-      <c r="C250" s="126" t="n"/>
-      <c r="D250" s="126" t="n"/>
+      <c r="C250" s="84" t="n"/>
+      <c r="D250" s="84" t="n"/>
       <c r="E250" s="84" t="n"/>
       <c r="F250" s="84" t="n"/>
       <c r="G250" s="84" t="n"/>
@@ -11005,8 +11016,8 @@
     <row r="253" ht="16.5" customHeight="1" s="80">
       <c r="A253" s="125" t="n"/>
       <c r="B253" s="84" t="n"/>
-      <c r="C253" s="84" t="n"/>
-      <c r="D253" s="84" t="n"/>
+      <c r="C253" s="126" t="n"/>
+      <c r="D253" s="126" t="n"/>
       <c r="E253" s="84" t="n"/>
       <c r="F253" s="84" t="n"/>
       <c r="G253" s="84" t="n"/>
@@ -11175,8 +11186,8 @@
     <row r="258" ht="16.5" customHeight="1" s="80">
       <c r="A258" s="125" t="n"/>
       <c r="B258" s="84" t="n"/>
-      <c r="C258" s="84" t="n"/>
-      <c r="D258" s="84" t="n"/>
+      <c r="C258" s="126" t="n"/>
+      <c r="D258" s="126" t="n"/>
       <c r="E258" s="84" t="n"/>
       <c r="F258" s="84" t="n"/>
       <c r="G258" s="84" t="n"/>
@@ -11209,8 +11220,8 @@
     <row r="259" ht="16.5" customHeight="1" s="80">
       <c r="A259" s="125" t="n"/>
       <c r="B259" s="84" t="n"/>
-      <c r="C259" s="126" t="n"/>
-      <c r="D259" s="126" t="n"/>
+      <c r="C259" s="84" t="n"/>
+      <c r="D259" s="84" t="n"/>
       <c r="E259" s="84" t="n"/>
       <c r="F259" s="84" t="n"/>
       <c r="G259" s="84" t="n"/>
@@ -11379,8 +11390,8 @@
     <row r="264" ht="16.5" customHeight="1" s="80">
       <c r="A264" s="125" t="n"/>
       <c r="B264" s="84" t="n"/>
-      <c r="C264" s="126" t="n"/>
-      <c r="D264" s="126" t="n"/>
+      <c r="C264" s="84" t="n"/>
+      <c r="D264" s="84" t="n"/>
       <c r="E264" s="84" t="n"/>
       <c r="F264" s="84" t="n"/>
       <c r="G264" s="84" t="n"/>
@@ -11549,8 +11560,8 @@
     <row r="269" ht="16.5" customHeight="1" s="80">
       <c r="A269" s="125" t="n"/>
       <c r="B269" s="84" t="n"/>
-      <c r="C269" s="84" t="n"/>
-      <c r="D269" s="84" t="n"/>
+      <c r="C269" s="126" t="n"/>
+      <c r="D269" s="126" t="n"/>
       <c r="E269" s="84" t="n"/>
       <c r="F269" s="84" t="n"/>
       <c r="G269" s="84" t="n"/>
@@ -11685,8 +11696,8 @@
     <row r="273" ht="16.5" customHeight="1" s="80">
       <c r="A273" s="125" t="n"/>
       <c r="B273" s="84" t="n"/>
-      <c r="C273" s="84" t="n"/>
-      <c r="D273" s="84" t="n"/>
+      <c r="C273" s="126" t="n"/>
+      <c r="D273" s="126" t="n"/>
       <c r="E273" s="84" t="n"/>
       <c r="F273" s="84" t="n"/>
       <c r="G273" s="84" t="n"/>
@@ -11753,8 +11764,8 @@
     <row r="275" ht="16.5" customHeight="1" s="80">
       <c r="A275" s="125" t="n"/>
       <c r="B275" s="84" t="n"/>
-      <c r="C275" s="126" t="n"/>
-      <c r="D275" s="126" t="n"/>
+      <c r="C275" s="84" t="n"/>
+      <c r="D275" s="84" t="n"/>
       <c r="E275" s="84" t="n"/>
       <c r="F275" s="84" t="n"/>
       <c r="G275" s="84" t="n"/>
@@ -11855,8 +11866,8 @@
     <row r="278" ht="16.5" customHeight="1" s="80">
       <c r="A278" s="125" t="n"/>
       <c r="B278" s="84" t="n"/>
-      <c r="C278" s="84" t="n"/>
-      <c r="D278" s="84" t="n"/>
+      <c r="C278" s="126" t="n"/>
+      <c r="D278" s="126" t="n"/>
       <c r="E278" s="84" t="n"/>
       <c r="F278" s="84" t="n"/>
       <c r="G278" s="84" t="n"/>
@@ -11889,8 +11900,8 @@
     <row r="279" ht="16.5" customHeight="1" s="80">
       <c r="A279" s="125" t="n"/>
       <c r="B279" s="84" t="n"/>
-      <c r="C279" s="126" t="n"/>
-      <c r="D279" s="126" t="n"/>
+      <c r="C279" s="84" t="n"/>
+      <c r="D279" s="84" t="n"/>
       <c r="E279" s="84" t="n"/>
       <c r="F279" s="84" t="n"/>
       <c r="G279" s="84" t="n"/>
@@ -12059,8 +12070,8 @@
     <row r="284" ht="16.5" customHeight="1" s="80">
       <c r="A284" s="125" t="n"/>
       <c r="B284" s="84" t="n"/>
-      <c r="C284" s="126" t="n"/>
-      <c r="D284" s="126" t="n"/>
+      <c r="C284" s="84" t="n"/>
+      <c r="D284" s="84" t="n"/>
       <c r="E284" s="84" t="n"/>
       <c r="F284" s="84" t="n"/>
       <c r="G284" s="84" t="n"/>
@@ -12093,8 +12104,8 @@
     <row r="285" ht="19.5" customHeight="1" s="80">
       <c r="A285" s="125" t="n"/>
       <c r="B285" s="84" t="n"/>
-      <c r="C285" s="84" t="n"/>
-      <c r="D285" s="84" t="n"/>
+      <c r="C285" s="126" t="n"/>
+      <c r="D285" s="126" t="n"/>
       <c r="E285" s="84" t="n"/>
       <c r="F285" s="84" t="n"/>
       <c r="G285" s="84" t="n"/>
@@ -12297,8 +12308,8 @@
     <row r="291" ht="16.5" customHeight="1" s="80">
       <c r="A291" s="125" t="n"/>
       <c r="B291" s="84" t="n"/>
-      <c r="C291" s="126" t="n"/>
-      <c r="D291" s="126" t="n"/>
+      <c r="C291" s="84" t="n"/>
+      <c r="D291" s="84" t="n"/>
       <c r="E291" s="84" t="n"/>
       <c r="F291" s="84" t="n"/>
       <c r="G291" s="84" t="n"/>
@@ -12501,8 +12512,8 @@
     <row r="297" ht="19.5" customHeight="1" s="80">
       <c r="A297" s="125" t="n"/>
       <c r="B297" s="84" t="n"/>
-      <c r="C297" s="84" t="n"/>
-      <c r="D297" s="84" t="n"/>
+      <c r="C297" s="126" t="n"/>
+      <c r="D297" s="126" t="n"/>
       <c r="E297" s="84" t="n"/>
       <c r="F297" s="84" t="n"/>
       <c r="G297" s="84" t="n"/>
@@ -12671,8 +12682,8 @@
     <row r="302" ht="19.5" customHeight="1" s="80">
       <c r="A302" s="125" t="n"/>
       <c r="B302" s="84" t="n"/>
-      <c r="C302" s="84" t="n"/>
-      <c r="D302" s="84" t="n"/>
+      <c r="C302" s="126" t="n"/>
+      <c r="D302" s="126" t="n"/>
       <c r="E302" s="84" t="n"/>
       <c r="F302" s="84" t="n"/>
       <c r="G302" s="84" t="n"/>
@@ -12705,8 +12716,8 @@
     <row r="303" ht="16.5" customHeight="1" s="80">
       <c r="A303" s="125" t="n"/>
       <c r="B303" s="84" t="n"/>
-      <c r="C303" s="126" t="n"/>
-      <c r="D303" s="126" t="n"/>
+      <c r="C303" s="84" t="n"/>
+      <c r="D303" s="84" t="n"/>
       <c r="E303" s="84" t="n"/>
       <c r="F303" s="84" t="n"/>
       <c r="G303" s="84" t="n"/>
@@ -12838,12 +12849,216 @@
       <c r="AE306" s="84" t="n"/>
       <c r="AF306" s="84" t="n"/>
     </row>
+    <row r="307">
+      <c r="A307" s="125" t="n"/>
+      <c r="B307" s="84" t="n"/>
+      <c r="C307" s="126" t="n"/>
+      <c r="D307" s="126" t="n"/>
+      <c r="E307" s="84" t="n"/>
+      <c r="F307" s="84" t="n"/>
+      <c r="G307" s="84" t="n"/>
+      <c r="H307" s="84" t="n"/>
+      <c r="I307" s="84" t="n"/>
+      <c r="J307" s="84" t="n"/>
+      <c r="K307" s="84" t="n"/>
+      <c r="L307" s="84" t="n"/>
+      <c r="M307" s="84" t="n"/>
+      <c r="N307" s="84" t="n"/>
+      <c r="O307" s="84" t="n"/>
+      <c r="P307" s="84" t="n"/>
+      <c r="Q307" s="84" t="n"/>
+      <c r="R307" s="84" t="n"/>
+      <c r="S307" s="84" t="n"/>
+      <c r="T307" s="84" t="n"/>
+      <c r="U307" s="84" t="n"/>
+      <c r="V307" s="84" t="n"/>
+      <c r="W307" s="84" t="n"/>
+      <c r="X307" s="84" t="n"/>
+      <c r="Y307" s="84" t="n"/>
+      <c r="Z307" s="84" t="n"/>
+      <c r="AA307" s="84" t="n"/>
+      <c r="AB307" s="84" t="n"/>
+      <c r="AC307" s="84" t="n"/>
+      <c r="AD307" s="84" t="n"/>
+      <c r="AE307" s="84" t="n"/>
+      <c r="AF307" s="84" t="n"/>
+    </row>
+    <row r="308">
+      <c r="A308" s="125" t="n"/>
+      <c r="B308" s="84" t="n"/>
+      <c r="C308" s="84" t="n"/>
+      <c r="D308" s="84" t="n"/>
+      <c r="E308" s="84" t="n"/>
+      <c r="F308" s="84" t="n"/>
+      <c r="G308" s="84" t="n"/>
+      <c r="H308" s="84" t="n"/>
+      <c r="I308" s="84" t="n"/>
+      <c r="J308" s="84" t="n"/>
+      <c r="K308" s="84" t="n"/>
+      <c r="L308" s="84" t="n"/>
+      <c r="M308" s="84" t="n"/>
+      <c r="N308" s="84" t="n"/>
+      <c r="O308" s="84" t="n"/>
+      <c r="P308" s="84" t="n"/>
+      <c r="Q308" s="84" t="n"/>
+      <c r="R308" s="84" t="n"/>
+      <c r="S308" s="84" t="n"/>
+      <c r="T308" s="84" t="n"/>
+      <c r="U308" s="84" t="n"/>
+      <c r="V308" s="84" t="n"/>
+      <c r="W308" s="84" t="n"/>
+      <c r="X308" s="84" t="n"/>
+      <c r="Y308" s="84" t="n"/>
+      <c r="Z308" s="84" t="n"/>
+      <c r="AA308" s="84" t="n"/>
+      <c r="AB308" s="84" t="n"/>
+      <c r="AC308" s="84" t="n"/>
+      <c r="AD308" s="84" t="n"/>
+      <c r="AE308" s="84" t="n"/>
+      <c r="AF308" s="84" t="n"/>
+    </row>
+    <row r="309">
+      <c r="A309" s="125" t="n"/>
+      <c r="B309" s="84" t="n"/>
+      <c r="C309" s="126" t="n"/>
+      <c r="D309" s="126" t="n"/>
+      <c r="E309" s="84" t="n"/>
+      <c r="F309" s="84" t="n"/>
+      <c r="G309" s="84" t="n"/>
+      <c r="H309" s="84" t="n"/>
+      <c r="I309" s="84" t="n"/>
+      <c r="J309" s="84" t="n"/>
+      <c r="K309" s="84" t="n"/>
+      <c r="L309" s="84" t="n"/>
+      <c r="M309" s="84" t="n"/>
+      <c r="N309" s="84" t="n"/>
+      <c r="O309" s="84" t="n"/>
+      <c r="P309" s="84" t="n"/>
+      <c r="Q309" s="84" t="n"/>
+      <c r="R309" s="84" t="n"/>
+      <c r="S309" s="84" t="n"/>
+      <c r="T309" s="84" t="n"/>
+      <c r="U309" s="84" t="n"/>
+      <c r="V309" s="84" t="n"/>
+      <c r="W309" s="84" t="n"/>
+      <c r="X309" s="84" t="n"/>
+      <c r="Y309" s="84" t="n"/>
+      <c r="Z309" s="84" t="n"/>
+      <c r="AA309" s="84" t="n"/>
+      <c r="AB309" s="84" t="n"/>
+      <c r="AC309" s="84" t="n"/>
+      <c r="AD309" s="84" t="n"/>
+      <c r="AE309" s="84" t="n"/>
+      <c r="AF309" s="84" t="n"/>
+    </row>
+    <row r="310">
+      <c r="A310" s="125" t="n"/>
+      <c r="B310" s="84" t="n"/>
+      <c r="C310" s="126" t="n"/>
+      <c r="D310" s="126" t="n"/>
+      <c r="E310" s="84" t="n"/>
+      <c r="F310" s="84" t="n"/>
+      <c r="G310" s="84" t="n"/>
+      <c r="H310" s="84" t="n"/>
+      <c r="I310" s="84" t="n"/>
+      <c r="J310" s="84" t="n"/>
+      <c r="K310" s="84" t="n"/>
+      <c r="L310" s="84" t="n"/>
+      <c r="M310" s="84" t="n"/>
+      <c r="N310" s="84" t="n"/>
+      <c r="O310" s="84" t="n"/>
+      <c r="P310" s="84" t="n"/>
+      <c r="Q310" s="84" t="n"/>
+      <c r="R310" s="84" t="n"/>
+      <c r="S310" s="84" t="n"/>
+      <c r="T310" s="84" t="n"/>
+      <c r="U310" s="84" t="n"/>
+      <c r="V310" s="84" t="n"/>
+      <c r="W310" s="84" t="n"/>
+      <c r="X310" s="84" t="n"/>
+      <c r="Y310" s="84" t="n"/>
+      <c r="Z310" s="84" t="n"/>
+      <c r="AA310" s="84" t="n"/>
+      <c r="AB310" s="84" t="n"/>
+      <c r="AC310" s="84" t="n"/>
+      <c r="AD310" s="84" t="n"/>
+      <c r="AE310" s="84" t="n"/>
+      <c r="AF310" s="84" t="n"/>
+    </row>
+    <row r="311">
+      <c r="A311" s="125" t="n"/>
+      <c r="B311" s="84" t="n"/>
+      <c r="C311" s="126" t="n"/>
+      <c r="D311" s="126" t="n"/>
+      <c r="E311" s="84" t="n"/>
+      <c r="F311" s="84" t="n"/>
+      <c r="G311" s="84" t="n"/>
+      <c r="H311" s="84" t="n"/>
+      <c r="I311" s="84" t="n"/>
+      <c r="J311" s="84" t="n"/>
+      <c r="K311" s="84" t="n"/>
+      <c r="L311" s="84" t="n"/>
+      <c r="M311" s="84" t="n"/>
+      <c r="N311" s="84" t="n"/>
+      <c r="O311" s="84" t="n"/>
+      <c r="P311" s="84" t="n"/>
+      <c r="Q311" s="84" t="n"/>
+      <c r="R311" s="84" t="n"/>
+      <c r="S311" s="84" t="n"/>
+      <c r="T311" s="84" t="n"/>
+      <c r="U311" s="84" t="n"/>
+      <c r="V311" s="84" t="n"/>
+      <c r="W311" s="84" t="n"/>
+      <c r="X311" s="84" t="n"/>
+      <c r="Y311" s="84" t="n"/>
+      <c r="Z311" s="84" t="n"/>
+      <c r="AA311" s="84" t="n"/>
+      <c r="AB311" s="84" t="n"/>
+      <c r="AC311" s="84" t="n"/>
+      <c r="AD311" s="84" t="n"/>
+      <c r="AE311" s="84" t="n"/>
+      <c r="AF311" s="84" t="n"/>
+    </row>
+    <row r="312">
+      <c r="A312" s="125" t="n"/>
+      <c r="B312" s="84" t="n"/>
+      <c r="C312" s="126" t="n"/>
+      <c r="D312" s="126" t="n"/>
+      <c r="E312" s="84" t="n"/>
+      <c r="F312" s="84" t="n"/>
+      <c r="G312" s="84" t="n"/>
+      <c r="H312" s="84" t="n"/>
+      <c r="I312" s="84" t="n"/>
+      <c r="J312" s="84" t="n"/>
+      <c r="K312" s="84" t="n"/>
+      <c r="L312" s="84" t="n"/>
+      <c r="M312" s="84" t="n"/>
+      <c r="N312" s="84" t="n"/>
+      <c r="O312" s="84" t="n"/>
+      <c r="P312" s="84" t="n"/>
+      <c r="Q312" s="84" t="n"/>
+      <c r="R312" s="84" t="n"/>
+      <c r="S312" s="84" t="n"/>
+      <c r="T312" s="84" t="n"/>
+      <c r="U312" s="84" t="n"/>
+      <c r="V312" s="84" t="n"/>
+      <c r="W312" s="84" t="n"/>
+      <c r="X312" s="84" t="n"/>
+      <c r="Y312" s="84" t="n"/>
+      <c r="Z312" s="84" t="n"/>
+      <c r="AA312" s="84" t="n"/>
+      <c r="AB312" s="84" t="n"/>
+      <c r="AC312" s="84" t="n"/>
+      <c r="AD312" s="84" t="n"/>
+      <c r="AE312" s="84" t="n"/>
+      <c r="AF312" s="84" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="24">
-    <mergeCell ref="A68:W68"/>
+  <mergeCells count="23">
     <mergeCell ref="A67:W67"/>
     <mergeCell ref="A30:W30"/>
     <mergeCell ref="O2:R2"/>
+    <mergeCell ref="A59:W59"/>
     <mergeCell ref="A24:W24"/>
     <mergeCell ref="A73:W73"/>
     <mergeCell ref="A11:W11"/>
@@ -12851,7 +13066,6 @@
     <mergeCell ref="A1:W1"/>
     <mergeCell ref="A45:W45"/>
     <mergeCell ref="S2:W2"/>
-    <mergeCell ref="A61:W61"/>
     <mergeCell ref="A16:W16"/>
     <mergeCell ref="G2:J2"/>
     <mergeCell ref="A41:W41"/>

--- a/00_スケジュール/AWS改修スケジュール.xlsx
+++ b/00_スケジュール/AWS改修スケジュール.xlsx
@@ -7314,7 +7314,7 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>

--- a/00_スケジュール/AWS改修スケジュール.xlsx
+++ b/00_スケジュール/AWS改修スケジュール.xlsx
@@ -7314,7 +7314,7 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
